--- a/data/metadata/met_revision_manual_v2.xlsx
+++ b/data/metadata/met_revision_manual_v2.xlsx
@@ -11,7 +11,7 @@
     <sheet name="listas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'revision_met_v2'!$A$1:$Z$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'revision_met_v2'!$A$1:$Z$221</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z212"/>
+  <dimension ref="A1:Z221"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19917,13 +19917,1017 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>315691</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>recuperado_por_filtro_corregido</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/315691</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>https://images.metmuseum.org/CRDImages/ao/original/DP18465.jpg</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>Dominio público / Open Access según metadata de The Met</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>recuperado_filtro_corregido</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>315692</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>recuperado_por_filtro_corregido</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/315692</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>https://images.metmuseum.org/CRDImages/ao/original/DP18467.jpg</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>Dominio público / Open Access según metadata de The Met</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>recuperado_filtro_corregido</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>315693</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>recuperado_por_filtro_corregido</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/315693</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>https://images.metmuseum.org/CRDImages/ao/original/DP18470.jpg</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>Dominio público / Open Access según metadata de The Met</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>recuperado_filtro_corregido</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>315694</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>recuperado_por_filtro_corregido</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/315694</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>https://images.metmuseum.org/CRDImages/ao/original/DP18471.jpg</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>Dominio público / Open Access según metadata de The Met</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>recuperado_filtro_corregido</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>315695</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>recuperado_por_filtro_corregido</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/315695</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>https://images.metmuseum.org/CRDImages/ao/original/DP18473.jpg</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>Dominio público / Open Access según metadata de The Met</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>recuperado_filtro_corregido</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>315696</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>recuperado_por_filtro_corregido</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/315696</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>https://images.metmuseum.org/CRDImages/ao/original/DP18475.jpg</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>Dominio público / Open Access según metadata de The Met</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>recuperado_filtro_corregido</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>315703</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>recuperado_por_filtro_corregido</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como revision_manual (puntaje 5). Pendiente de revision visual.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Feathered Crown</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Chimú</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>1200 – 1400 CE</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>tipo_no_determinado</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>revision_morfologica</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Feathers (Paradise Tanager, Macaw), cotton, skin, cane, copper</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>material contiene fibras o soporte textil: ['cotton'] | evidencia cultural/geográfica andina: ['peru', 'chimú', 'chimu'] | material mixto con fibras textiles, sin penalización: ['copper']</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/315703</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>https://images.metmuseum.org/CRDImages/ao/original/DP230213.jpg</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr"/>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>Dominio público / Open Access según metadata de The Met</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>recuperado_filtro_corregido</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>316914</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>recuperado_por_filtro_corregido</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 10). Pendiente de revision visual.</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Feathered Ornament</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Objeto textil</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Peruvian</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>14th–early 16th century</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>objeto_textil</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>superficie_amplia</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Cotton, feathers</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['cotton'] | evidencia cultural/geográfica andina: ['peru', 'peruvian'] | título con término no textil, sin penalización por evidencia textil: ['ornament']</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/316914</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>https://images.metmuseum.org/CRDImages/ao/original/DP101345b.jpg</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr"/>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>Dominio público / Open Access según metadata de The Met</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>recuperado_filtro_corregido</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>316938</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>recuperado_por_filtro_corregido</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 10). Pendiente de revision visual.</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Serpent ornament</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Objeto textil</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Inca (?)</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>1450–1532 CE</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>objeto_textil</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>revision_morfologica</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Cotton, camelid hair</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['cotton', 'camelid'] | evidencia cultural/geográfica andina: ['peru', 'inca'] | título con término no textil, sin penalización por evidencia textil: ['ornament']</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>https://www.metmuseum.org/art/collection/search/316938</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>https://images.metmuseum.org/CRDImages/ao/original/1994.35.113_d.JPG</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr"/>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>Dominio público / Open Access según metadata de The Met</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>recuperado_filtro_corregido</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z212"/>
+  <autoFilter ref="A1:Z221"/>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C2:C221" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"principal,secundario,descartados,revisar"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="D2:D221" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"mantener,mover,descartar,recuperar,revisar"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/metadata/met_revision_manual_v2.xlsx
+++ b/data/metadata/met_revision_manual_v2.xlsx
@@ -9804,12 +9804,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>mantener</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Anotación de la validación ciega del 2026-10-19 (data/metadata/validacion_met_cma_v2.xlsx, orden 4): descartados. Decisión anterior: principal (corpus_principal; superficie_textil_util). Queda en revisar: la anotación contradice su propio motivo según el criterio del 2026-10-19.</t>
+          <t>Anotación de la validación ciega del 2026-10-19 (data/metadata/validacion_met_cma_v2.xlsx, orden 4): descartados. Decisión anterior: principal (corpus_principal; superficie_textil_util). Queda en revisar: la anotación contradice su propio motivo según el criterio del 2026-10-19. Resuelto por el revisor el 2026-10-19: principal, porque sus colores y figuras se identifican (criterio v2).</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">

--- a/data/metadata/met_revision_manual_v2.xlsx
+++ b/data/metadata/met_revision_manual_v2.xlsx
@@ -1742,18 +1742,34 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>descartados</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>descartar</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
+          <t>mantener</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 38): principal. Decisión anterior: descartados (corpus_principal; superficie amplia o composición visual útil detectada: ['tunic']).</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Tunic</t>
@@ -1837,7 +1853,7 @@
       </c>
       <c r="Z9" s="4" t="inlineStr">
         <is>
-          <t>corpus_principal_preliminar</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA9" s="4" t="n">
@@ -1872,18 +1888,34 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>mover</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
+          <t>mantener</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 26): principal. Decisión anterior: secundario (corpus_principal; sombrero/cap Wari-Huari conservado por potencial iconográfico: ['hat', 'four-cornered hat']).</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -1967,7 +1999,7 @@
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>corpus_principal_preliminar</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA10" s="4" t="n">
@@ -2416,18 +2448,34 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>mover</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
+          <t>mantener</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 9): principal. Decisión anterior: secundario (corpus_principal; sombrero/cap Wari-Huari conservado por potencial iconográfico: ['hat', 'four-cornered hat']).</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -2511,7 +2559,7 @@
       </c>
       <c r="Z14" s="4" t="inlineStr">
         <is>
-          <t>corpus_principal_preliminar</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA14" s="4" t="n">
@@ -2546,18 +2594,34 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>mover</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
+          <t>mantener</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 19): principal. Decisión anterior: secundario (corpus_principal; sombrero/cap Wari-Huari conservado por potencial iconográfico: ['hat', 'four-cornered hat']).</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -2645,7 +2709,7 @@
       </c>
       <c r="Z15" s="4" t="inlineStr">
         <is>
-          <t>corpus_principal_preliminar</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA15" s="4" t="n">
@@ -7042,10 +7106,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Textil con colores y formas visibles</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 60): principal. Decisión anterior: principal (corpus_principal; fragmento_textil_util).</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
           <t>Embroidered Fragment</t>
@@ -7101,7 +7181,7 @@
       </c>
       <c r="Z51" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA51" s="4" t="n">
@@ -7960,10 +8040,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="n"/>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Textil con colores y formas visibles</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 58): principal. Decisión anterior: principal (corpus_principal; superficie_textil_util).</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>Embroidered Mantle Fragment</t>
@@ -8019,7 +8115,7 @@
       </c>
       <c r="Z60" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA60" s="4" t="n">
@@ -8062,10 +8158,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Textil con colores y formas visibles</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 61): principal. Decisión anterior: principal (corpus_principal; superficie_textil_util).</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
           <t>Embroidered Mantle Fragment</t>
@@ -8121,7 +8233,7 @@
       </c>
       <c r="Z61" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA61" s="4" t="n">
@@ -8996,10 +9108,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
-      <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Textil con colores y formas visibles</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 59): principal. Decisión anterior: principal (corpus_principal; superficie_textil_util).</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
           <t>Embroidered Mantle Fragment</t>
@@ -9055,7 +9183,7 @@
       </c>
       <c r="Z70" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA70" s="4" t="n">
@@ -18486,10 +18614,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E153" s="4" t="n"/>
-      <c r="F153" s="4" t="n"/>
-      <c r="G153" s="4" t="n"/>
-      <c r="H153" s="4" t="n"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con figura visible</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 4): secundario. Decisión anterior: secundario (corpus_secundario; faja_o_banda_util_secundario).</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
           <t>Woven Sling Shot</t>
@@ -18545,7 +18689,7 @@
       </c>
       <c r="Z153" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA153" s="4" t="n">
@@ -18588,10 +18732,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E154" s="4" t="n"/>
-      <c r="F154" s="4" t="n"/>
-      <c r="G154" s="4" t="n"/>
-      <c r="H154" s="4" t="n"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores visibles</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 33): secundario. Decisión anterior: secundario (corpus_secundario; faja_o_banda_util_secundario).</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
           <t>Sling</t>
@@ -18647,7 +18807,7 @@
       </c>
       <c r="Z154" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA154" s="4" t="n">
@@ -18690,10 +18850,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E155" s="4" t="n"/>
-      <c r="F155" s="4" t="n"/>
-      <c r="G155" s="4" t="n"/>
-      <c r="H155" s="4" t="n"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con figura visible</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 24): secundario. Decisión anterior: secundario (corpus_secundario; faja_o_banda_util_secundario).</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
           <t>Woven Sling Shot</t>
@@ -18749,7 +18925,7 @@
       </c>
       <c r="Z155" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA155" s="4" t="n">
@@ -18792,10 +18968,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E156" s="4" t="n"/>
-      <c r="F156" s="4" t="n"/>
-      <c r="G156" s="4" t="n"/>
-      <c r="H156" s="4" t="n"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con figura visible</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 28): secundario. Decisión anterior: secundario (corpus_secundario; faja_o_banda_util_secundario).</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
           <t>Woven Sling Shot</t>
@@ -18851,7 +19043,7 @@
       </c>
       <c r="Z156" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA156" s="4" t="n">
@@ -18894,10 +19086,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E157" s="4" t="n"/>
-      <c r="F157" s="4" t="n"/>
-      <c r="G157" s="4" t="n"/>
-      <c r="H157" s="4" t="n"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con figura visible</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 23): secundario. Decisión anterior: secundario (corpus_secundario; faja_o_banda_util_secundario).</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
           <t>Sling Shot</t>
@@ -18953,7 +19161,7 @@
       </c>
       <c r="Z157" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA157" s="4" t="n">
@@ -19106,18 +19314,34 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E159" s="4" t="n"/>
-      <c r="F159" s="4" t="n"/>
-      <c r="G159" s="4" t="n"/>
-      <c r="H159" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 1): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -19173,7 +19397,7 @@
       </c>
       <c r="Z159" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA159" s="4" t="n">
@@ -19208,18 +19432,34 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E160" s="4" t="n"/>
-      <c r="F160" s="4" t="n"/>
-      <c r="G160" s="4" t="n"/>
-      <c r="H160" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 18): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -19275,7 +19515,7 @@
       </c>
       <c r="Z160" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA160" s="4" t="n">
@@ -19310,18 +19550,34 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="n"/>
-      <c r="F161" s="4" t="n"/>
-      <c r="G161" s="4" t="n"/>
-      <c r="H161" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 14): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -19377,7 +19633,7 @@
       </c>
       <c r="Z161" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA161" s="4" t="n">
@@ -19412,18 +19668,34 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E162" s="4" t="n"/>
-      <c r="F162" s="4" t="n"/>
-      <c r="G162" s="4" t="n"/>
-      <c r="H162" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 32): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -19479,7 +19751,7 @@
       </c>
       <c r="Z162" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA162" s="4" t="n">
@@ -19514,18 +19786,34 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="n"/>
-      <c r="F163" s="4" t="n"/>
-      <c r="G163" s="4" t="n"/>
-      <c r="H163" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 6): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -19581,7 +19869,7 @@
       </c>
       <c r="Z163" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA163" s="4" t="n">
@@ -19616,18 +19904,34 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E164" s="4" t="n"/>
-      <c r="F164" s="4" t="n"/>
-      <c r="G164" s="4" t="n"/>
-      <c r="H164" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 17): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -19683,7 +19987,7 @@
       </c>
       <c r="Z164" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA164" s="4" t="n">
@@ -19718,18 +20022,34 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="n"/>
-      <c r="F165" s="4" t="n"/>
-      <c r="G165" s="4" t="n"/>
-      <c r="H165" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 11): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -19785,7 +20105,7 @@
       </c>
       <c r="Z165" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA165" s="4" t="n">
@@ -19820,18 +20140,34 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="n"/>
-      <c r="F166" s="4" t="n"/>
-      <c r="G166" s="4" t="n"/>
-      <c r="H166" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 5): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -19887,7 +20223,7 @@
       </c>
       <c r="Z166" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA166" s="4" t="n">
@@ -19922,18 +20258,34 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="n"/>
-      <c r="F167" s="4" t="n"/>
-      <c r="G167" s="4" t="n"/>
-      <c r="H167" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 21): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -19989,7 +20341,7 @@
       </c>
       <c r="Z167" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA167" s="4" t="n">
@@ -20024,18 +20376,34 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="n"/>
-      <c r="F168" s="4" t="n"/>
-      <c r="G168" s="4" t="n"/>
-      <c r="H168" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 8): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -20091,7 +20459,7 @@
       </c>
       <c r="Z168" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA168" s="4" t="n">
@@ -20126,18 +20494,34 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E169" s="4" t="n"/>
-      <c r="F169" s="4" t="n"/>
-      <c r="G169" s="4" t="n"/>
-      <c r="H169" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 3): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -20193,7 +20577,7 @@
       </c>
       <c r="Z169" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA169" s="4" t="n">
@@ -20228,18 +20612,34 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="n"/>
-      <c r="F170" s="4" t="n"/>
-      <c r="G170" s="4" t="n"/>
-      <c r="H170" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 29): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -20295,7 +20695,7 @@
       </c>
       <c r="Z170" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA170" s="4" t="n">
@@ -20330,18 +20730,34 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E171" s="4" t="n"/>
-      <c r="F171" s="4" t="n"/>
-      <c r="G171" s="4" t="n"/>
-      <c r="H171" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 12): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -20397,7 +20813,7 @@
       </c>
       <c r="Z171" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA171" s="4" t="n">
@@ -20432,18 +20848,34 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="n"/>
-      <c r="F172" s="4" t="n"/>
-      <c r="G172" s="4" t="n"/>
-      <c r="H172" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 7): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -20499,7 +20931,7 @@
       </c>
       <c r="Z172" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA172" s="4" t="n">
@@ -20534,18 +20966,34 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="n"/>
-      <c r="F173" s="4" t="n"/>
-      <c r="G173" s="4" t="n"/>
-      <c r="H173" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 13): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -20601,7 +21049,7 @@
       </c>
       <c r="Z173" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA173" s="4" t="n">
@@ -20636,18 +21084,34 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E174" s="4" t="n"/>
-      <c r="F174" s="4" t="n"/>
-      <c r="G174" s="4" t="n"/>
-      <c r="H174" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 31): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -20703,7 +21167,7 @@
       </c>
       <c r="Z174" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA174" s="4" t="n">
@@ -20738,18 +21202,34 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E175" s="4" t="n"/>
-      <c r="F175" s="4" t="n"/>
-      <c r="G175" s="4" t="n"/>
-      <c r="H175" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 2): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -20805,7 +21285,7 @@
       </c>
       <c r="Z175" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA175" s="4" t="n">
@@ -20840,18 +21320,34 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="n"/>
-      <c r="F176" s="4" t="n"/>
-      <c r="G176" s="4" t="n"/>
-      <c r="H176" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 15): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -20907,7 +21403,7 @@
       </c>
       <c r="Z176" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA176" s="4" t="n">
@@ -20942,18 +21438,34 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E177" s="4" t="n"/>
-      <c r="F177" s="4" t="n"/>
-      <c r="G177" s="4" t="n"/>
-      <c r="H177" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 27): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -21009,7 +21521,7 @@
       </c>
       <c r="Z177" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA177" s="4" t="n">
@@ -21044,18 +21556,34 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="n"/>
-      <c r="F178" s="4" t="n"/>
-      <c r="G178" s="4" t="n"/>
-      <c r="H178" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 30): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -21111,7 +21639,7 @@
       </c>
       <c r="Z178" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA178" s="4" t="n">
@@ -21146,18 +21674,34 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="n"/>
-      <c r="F179" s="4" t="n"/>
-      <c r="G179" s="4" t="n"/>
-      <c r="H179" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 10): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -21213,7 +21757,7 @@
       </c>
       <c r="Z179" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA179" s="4" t="n">
@@ -21248,18 +21792,34 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>secundario</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="n"/>
-      <c r="F180" s="4" t="n"/>
-      <c r="G180" s="4" t="n"/>
-      <c r="H180" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores y figura visible</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 22): principal. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
           <t>Four-Cornered Hat</t>
@@ -21315,7 +21875,7 @@
       </c>
       <c r="Z180" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA180" s="4" t="n">
@@ -21358,10 +21918,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E181" s="4" t="n"/>
-      <c r="F181" s="4" t="n"/>
-      <c r="G181" s="4" t="n"/>
-      <c r="H181" s="4" t="n"/>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores visibles</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 25): secundario. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
           <t>Cap</t>
@@ -21417,7 +21993,7 @@
       </c>
       <c r="Z181" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA181" s="4" t="n">
@@ -21460,10 +22036,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E182" s="4" t="n"/>
-      <c r="F182" s="4" t="n"/>
-      <c r="G182" s="4" t="n"/>
-      <c r="H182" s="4" t="n"/>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores visibles</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 20): secundario. Decisión anterior: secundario (corpus_secundario; prenda_tridimensional_util).</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
           <t>Cap Woven with Human Hair</t>
@@ -21519,7 +22111,7 @@
       </c>
       <c r="Z182" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA182" s="4" t="n">
@@ -21562,10 +22154,26 @@
           <t>mantener</t>
         </is>
       </c>
-      <c r="E183" s="4" t="n"/>
-      <c r="F183" s="4" t="n"/>
-      <c r="G183" s="4" t="n"/>
-      <c r="H183" s="4" t="n"/>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>textil completo con colores visibles</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 16): secundario. Decisión anterior: secundario (corpus_secundario; faja_o_banda_util_secundario).</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
           <t>Headband</t>
@@ -21621,7 +22229,7 @@
       </c>
       <c r="Z183" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA183" s="4" t="n">
@@ -22837,13 +23445,29 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E196" s="4" t="n"/>
-      <c r="F196" s="4" t="n"/>
-      <c r="G196" s="4" t="n"/>
-      <c r="H196" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>textil sin colores visibles</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 36): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
           <t>Embroidered Fragment</t>
@@ -22895,7 +23519,7 @@
       <c r="Y196" s="4" t="n"/>
       <c r="Z196" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA196" s="4" t="n">
@@ -22935,13 +23559,29 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="n"/>
-      <c r="F197" s="4" t="n"/>
-      <c r="G197" s="4" t="n"/>
-      <c r="H197" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>textil sin figuras visibles</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 34): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
           <t>Mantle</t>
@@ -22993,7 +23633,7 @@
       <c r="Y197" s="4" t="n"/>
       <c r="Z197" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA197" s="4" t="n">
@@ -23033,13 +23673,29 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E198" s="4" t="n"/>
-      <c r="F198" s="4" t="n"/>
-      <c r="G198" s="4" t="n"/>
-      <c r="H198" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>textil incompleto</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 45): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
           <t>Border Fragments</t>
@@ -23091,7 +23747,7 @@
       <c r="Y198" s="4" t="n"/>
       <c r="Z198" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA198" s="4" t="n">
@@ -23245,13 +23901,29 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E200" s="4" t="n"/>
-      <c r="F200" s="4" t="n"/>
-      <c r="G200" s="4" t="n"/>
-      <c r="H200" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>textil incompleto sin colores ni figura visible</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 39): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
           <t>Dress Fragment</t>
@@ -23303,7 +23975,7 @@
       <c r="Y200" s="4" t="n"/>
       <c r="Z200" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA200" s="4" t="n">
@@ -23343,13 +24015,29 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="n"/>
-      <c r="F201" s="4" t="n"/>
-      <c r="G201" s="4" t="n"/>
-      <c r="H201" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>textil incompleto</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 43): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I201" s="4" t="inlineStr">
         <is>
           <t>Border Fragment</t>
@@ -23401,7 +24089,7 @@
       <c r="Y201" s="4" t="n"/>
       <c r="Z201" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA201" s="4" t="n">
@@ -23436,18 +24124,34 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>descartados</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E202" s="4" t="n"/>
-      <c r="F202" s="4" t="n"/>
-      <c r="G202" s="4" t="n"/>
-      <c r="H202" s="4" t="n"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>textil incompleto con colores y figuras visibles</t>
+        </is>
+      </c>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 47): principal. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
           <t>Tunic Fragment</t>
@@ -23499,7 +24203,7 @@
       <c r="Y202" s="4" t="n"/>
       <c r="Z202" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA202" s="4" t="n">
@@ -23539,13 +24243,29 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E203" s="4" t="n"/>
-      <c r="F203" s="4" t="n"/>
-      <c r="G203" s="4" t="n"/>
-      <c r="H203" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>textil incompleto sin colores ni figura visible</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 40): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I203" s="4" t="inlineStr">
         <is>
           <t>Hanging</t>
@@ -23597,7 +24317,7 @@
       <c r="Y203" s="4" t="n"/>
       <c r="Z203" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA203" s="4" t="n">
@@ -23637,13 +24357,29 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E204" s="4" t="n"/>
-      <c r="F204" s="4" t="n"/>
-      <c r="G204" s="4" t="n"/>
-      <c r="H204" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>textil sin colores visibles</t>
+        </is>
+      </c>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 35): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G204" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
           <t>Openwork Headband</t>
@@ -23695,7 +24431,7 @@
       <c r="Y204" s="4" t="n"/>
       <c r="Z204" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA204" s="4" t="n">
@@ -23735,13 +24471,29 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E205" s="4" t="n"/>
-      <c r="F205" s="4" t="n"/>
-      <c r="G205" s="4" t="n"/>
-      <c r="H205" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>textil sin colores visibles</t>
+        </is>
+      </c>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 37): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H205" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I205" s="4" t="inlineStr">
         <is>
           <t>Openweave Cap</t>
@@ -23793,7 +24545,7 @@
       <c r="Y205" s="4" t="n"/>
       <c r="Z205" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA205" s="4" t="n">
@@ -23833,13 +24585,29 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E206" s="4" t="n"/>
-      <c r="F206" s="4" t="n"/>
-      <c r="G206" s="4" t="n"/>
-      <c r="H206" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>textil incompleto sin colores ni figura visible</t>
+        </is>
+      </c>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 41): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I206" s="4" t="inlineStr">
         <is>
           <t>Openweave Cap with Tassels</t>
@@ -23891,7 +24659,7 @@
       <c r="Y206" s="4" t="n"/>
       <c r="Z206" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA206" s="4" t="n">
@@ -23931,13 +24699,29 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E207" s="4" t="n"/>
-      <c r="F207" s="4" t="n"/>
-      <c r="G207" s="4" t="n"/>
-      <c r="H207" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>textil incompleto sin colores ni figura visible</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 46): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I207" s="4" t="inlineStr">
         <is>
           <t>Hat</t>
@@ -23989,7 +24773,7 @@
       <c r="Y207" s="4" t="n"/>
       <c r="Z207" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA207" s="4" t="n">
@@ -24029,13 +24813,29 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E208" s="4" t="n"/>
-      <c r="F208" s="4" t="n"/>
-      <c r="G208" s="4" t="n"/>
-      <c r="H208" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>textil incompleto sin colores ni figura visible</t>
+        </is>
+      </c>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 42): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I208" s="4" t="inlineStr">
         <is>
           <t>Hat</t>
@@ -24087,7 +24887,7 @@
       <c r="Y208" s="4" t="n"/>
       <c r="Z208" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA208" s="4" t="n">
@@ -24127,13 +24927,29 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E209" s="4" t="n"/>
-      <c r="F209" s="4" t="n"/>
-      <c r="G209" s="4" t="n"/>
-      <c r="H209" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>No es textil</t>
+        </is>
+      </c>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 50): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I209" s="4" t="inlineStr">
         <is>
           <t>Headband</t>
@@ -24185,7 +25001,7 @@
       <c r="Y209" s="4" t="n"/>
       <c r="Z209" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA209" s="4" t="n">
@@ -24225,13 +25041,29 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E210" s="4" t="n"/>
-      <c r="F210" s="4" t="n"/>
-      <c r="G210" s="4" t="n"/>
-      <c r="H210" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>textil sin figuras visibles</t>
+        </is>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 49): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
           <t>Sash Fragment</t>
@@ -24283,7 +25115,7 @@
       <c r="Y210" s="4" t="n"/>
       <c r="Z210" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA210" s="4" t="n">
@@ -24323,13 +25155,29 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E211" s="4" t="n"/>
-      <c r="F211" s="4" t="n"/>
-      <c r="G211" s="4" t="n"/>
-      <c r="H211" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>textil sin figuras visibles</t>
+        </is>
+      </c>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 48): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H211" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I211" s="4" t="inlineStr">
         <is>
           <t>Sash Fragment</t>
@@ -24381,7 +25229,7 @@
       <c r="Y211" s="4" t="n"/>
       <c r="Z211" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA211" s="4" t="n">
@@ -24421,13 +25269,29 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>mantener</t>
-        </is>
-      </c>
-      <c r="E212" s="4" t="n"/>
-      <c r="F212" s="4" t="n"/>
-      <c r="G212" s="4" t="n"/>
-      <c r="H212" s="4" t="n"/>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>textil incompleto</t>
+        </is>
+      </c>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 44): descartados. Decisión anterior: descartados (descartado; fragmento_no_legible).</t>
+        </is>
+      </c>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
           <t>Sash Fragment</t>
@@ -24479,7 +25343,7 @@
       <c r="Y212" s="4" t="n"/>
       <c r="Z212" s="4" t="inlineStr">
         <is>
-          <t>auditoria_aceptados_no_piloto</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA212" s="4" t="n">
@@ -24514,74 +25378,84 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
+          <t>descartados</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>es muñeco</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 54): descartados. Decisión anterior: revisar (pendiente_revision; clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']; recuperado_por_filtro_corregido).</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>recuperado_por_filtro_corregido</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>Border Fragment, Figure</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>Fragmento textil</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>Nasca</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>2nd century BCE</t>
-        </is>
-      </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>borde_textil</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr">
-        <is>
-          <t>borde_o_fragmento_lineal</t>
-        </is>
-      </c>
-      <c r="P213" t="inlineStr">
-        <is>
-          <t>Camelid hair</t>
-        </is>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>pendiente_revision</t>
-        </is>
-      </c>
-      <c r="T213" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
       <c r="U213" t="inlineStr">
         <is>
           <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
@@ -24604,7 +25478,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>recuperado_filtro_corregido</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA213" s="4" t="n">
@@ -24639,74 +25513,84 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
+          <t>descartados</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>es muñeco</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 55): descartados. Decisión anterior: revisar (pendiente_revision; clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']; recuperado_por_filtro_corregido).</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>recuperado_por_filtro_corregido</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>Border Fragment, Figure</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>Fragmento textil</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Nasca</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>2nd century BCE</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>borde_textil</t>
-        </is>
-      </c>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>borde_o_fragmento_lineal</t>
-        </is>
-      </c>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>Camelid hair</t>
-        </is>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>pendiente_revision</t>
-        </is>
-      </c>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
       <c r="U214" t="inlineStr">
         <is>
           <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
@@ -24729,7 +25613,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>recuperado_filtro_corregido</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA214" s="4" t="n">
@@ -24764,74 +25648,84 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
+          <t>descartados</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>es muñeco</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 56): descartados. Decisión anterior: revisar (pendiente_revision; clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']; recuperado_por_filtro_corregido).</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>recuperado_por_filtro_corregido</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>Border Fragment, Figure</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>Fragmento textil</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>Nasca</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>2nd century BCE</t>
-        </is>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>borde_textil</t>
-        </is>
-      </c>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>borde_o_fragmento_lineal</t>
-        </is>
-      </c>
-      <c r="P215" t="inlineStr">
-        <is>
-          <t>Camelid hair</t>
-        </is>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>pendiente_revision</t>
-        </is>
-      </c>
-      <c r="T215" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
       <c r="U215" t="inlineStr">
         <is>
           <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
@@ -24854,7 +25748,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>recuperado_filtro_corregido</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA215" s="4" t="n">
@@ -24889,74 +25783,84 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
+          <t>descartados</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>es muñeco</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 57): descartados. Decisión anterior: revisar (pendiente_revision; clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']; recuperado_por_filtro_corregido).</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>recuperado_por_filtro_corregido</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>Border Fragment, Figure</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>Fragmento textil</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>Nasca</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>2nd century BCE</t>
-        </is>
-      </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>borde_textil</t>
-        </is>
-      </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>borde_o_fragmento_lineal</t>
-        </is>
-      </c>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>Camelid hair</t>
-        </is>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>pendiente_revision</t>
-        </is>
-      </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
       <c r="U216" t="inlineStr">
         <is>
           <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
@@ -24979,7 +25883,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>recuperado_filtro_corregido</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA216" s="4" t="n">
@@ -25014,74 +25918,84 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
+          <t>descartados</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>es muñeco</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 52): descartados. Decisión anterior: revisar (pendiente_revision; clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']; recuperado_por_filtro_corregido).</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>recuperado_por_filtro_corregido</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>Border Fragment, Figure</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>Fragmento textil</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>Nasca</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>2nd century BCE</t>
-        </is>
-      </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>borde_textil</t>
-        </is>
-      </c>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>borde_o_fragmento_lineal</t>
-        </is>
-      </c>
-      <c r="P217" t="inlineStr">
-        <is>
-          <t>Camelid hair</t>
-        </is>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>pendiente_revision</t>
-        </is>
-      </c>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
       <c r="U217" t="inlineStr">
         <is>
           <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
@@ -25104,7 +26018,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>recuperado_filtro_corregido</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA217" s="4" t="n">
@@ -25139,74 +26053,84 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
+          <t>descartados</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>descartar</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>es muñeco</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 53): descartados. Decisión anterior: revisar (pendiente_revision; clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']; recuperado_por_filtro_corregido).</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Border Fragment, Figure</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Fragmento textil</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Nasca</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2nd century BCE</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>borde_textil</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>borde_o_fragmento_lineal</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Camelid hair</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>recuperado_por_filtro_corregido</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 11). Pendiente de revision visual.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>Border Fragment, Figure</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>Fragmento textil</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>Nasca</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>2nd century BCE</t>
-        </is>
-      </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>borde_textil</t>
-        </is>
-      </c>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>borde_o_fragmento_lineal</t>
-        </is>
-      </c>
-      <c r="P218" t="inlineStr">
-        <is>
-          <t>Camelid hair</t>
-        </is>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>pendiente_revision</t>
-        </is>
-      </c>
-      <c r="T218" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
       <c r="U218" t="inlineStr">
         <is>
           <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['camelid'] | título contiene términos débiles asociados a fragmentos o paneles: ['fragment', 'border'] | evidencia cultural/geográfica andina: ['peru', 'nasca'] | clasificación mixta textil/no textil, sin penalización: ['sculpture'] | título con término no textil, sin penalización por evidencia textil: ['figure']</t>
@@ -25229,7 +26153,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>recuperado_filtro_corregido</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA218" s="4" t="n">
@@ -25529,74 +26453,84 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
+          <t>secundario</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Textil con colores visibles</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Revisión con el criterio v2 del 2026-10-20 (data/metadata/revision_criterio_v2_met_cma.xlsx, orden 51): secundario. Decisión anterior: revisar (pendiente_revision; clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['cotton', 'camelid'] | evidencia cultural/geográfica andina: ['peru', 'inca'] | título con término no textil, sin penalización por evidencia textil: ['ornament']; recuperado_por_filtro_corregido).</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Henry Sánchez</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Serpent ornament</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Objeto textil</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Inca (?)</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>1450–1532 CE</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>objeto_textil</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>revision_morfologica</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Cotton, camelid hair</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>pendiente_revision</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>recuperado_por_filtro_corregido</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>Excluido por el filtro v1 (excluido_no_textil); el filtro corregido del 2026-10-05 lo clasifica como aceptado_textil (puntaje 10). Pendiente de revision visual.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>Serpent ornament</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>Objeto textil</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>Inca (?)</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>1450–1532 CE</t>
-        </is>
-      </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>objeto_textil</t>
-        </is>
-      </c>
-      <c r="O221" t="inlineStr">
-        <is>
-          <t>revision_morfologica</t>
-        </is>
-      </c>
-      <c r="P221" t="inlineStr">
-        <is>
-          <t>Cotton, camelid hair</t>
-        </is>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>pendiente_revision</t>
-        </is>
-      </c>
-      <c r="T221" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
       <c r="U221" t="inlineStr">
         <is>
           <t>clasificación contiene evidencia textil: ['textiles'] | material contiene fibras o soporte textil: ['cotton', 'camelid'] | evidencia cultural/geográfica andina: ['peru', 'inca'] | título con término no textil, sin penalización por evidencia textil: ['ornament']</t>
@@ -25619,7 +26553,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>recuperado_filtro_corregido</t>
+          <t>revision_criterio_v2</t>
         </is>
       </c>
       <c r="AA221" s="4" t="n">

--- a/data/metadata/met_revision_manual_v2.xlsx
+++ b/data/metadata/met_revision_manual_v2.xlsx
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>72.5</v>
+        <v>96</v>
       </c>
       <c r="AB2" s="4" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="AD2" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,04; textil de 3480 px de lado); colores identificables (probabilidad 0,96; 4 colores claramente distintos, 3 tonos, colorido 70); formas visibles (probabilidad 0,94; bordes cromáticos en el 35 % del textil); textil completo (probabilidad 0,83; compacidad 0,90, lagunas 0,0 %); estructura no evidente. Puntaje 73.</t>
+          <t>Fotografía regular (nitidez 1,04; textil de 3480 px de lado); colores identificables (probabilidad 0,98; 4 colores claramente distintos, 3 tonos, colorido 70); formas visibles (probabilidad 0,98; bordes cromáticos en el 35 % del textil); textil completo (probabilidad 0,95; compacidad 0,90, lagunas 0,0 %); estructura no evidente. Puntaje 96 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>78.2</v>
+        <v>97.8</v>
       </c>
       <c r="AB3" s="4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="AD3" s="4" t="inlineStr">
         <is>
-          <t>Fecha de inicio posterior a 1532: el estudio abarca textiles incas y anteriores. Fotografía regular (nitidez 1,23; textil de 2863 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,98; bordes cromáticos en el 37 % del textil); textil completo (probabilidad 0,93; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 78.</t>
+          <t>Fecha de inicio posterior a 1532: el estudio abarca textiles incas y anteriores. Fotografía regular (nitidez 1,23; textil de 2863 px de lado); colores identificables (probabilidad 1,00; 4 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,99; bordes cromáticos en el 37 % del textil); textil completo (probabilidad 0,98; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 98.</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>76.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AB4" s="4" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,19; textil de 1889 px de lado); colores identificables (probabilidad 0,96; 4 colores claramente distintos, 3 tonos, colorido 97); formas visibles (probabilidad 0,90; bordes cromáticos en el 36 % del textil); textil completo (probabilidad 0,88; compacidad 0,66, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 77.</t>
+          <t>Fotografía regular (nitidez 1,19; textil de 1889 px de lado); colores identificables (probabilidad 0,98; 4 colores claramente distintos, 3 tonos, colorido 97); formas visibles (probabilidad 0,94; bordes cromáticos en el 36 % del textil); textil completo (probabilidad 0,96; compacidad 0,66, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 95 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>32.9</v>
+        <v>41.1</v>
       </c>
       <c r="AB5" s="4" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AD5" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,90; textil de 2507 px de lado); colores no identificables (probabilidad 0,38; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 19 % del textil); textil incompleto (probabilidad 0,14; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura no evidente. Puntaje 33.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,90; textil de 2507 px de lado); colores no identificables (probabilidad 0,51; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,66; bordes cromáticos en el 19 % del textil); textil incompleto (probabilidad 0,18; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura no evidente. Puntaje 41.</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,29; textil de 1255 px de lado); colores identificables (probabilidad 0,97; 3 colores claramente distintos, 2 tonos, colorido 61); formas visibles (probabilidad 0,95; bordes cromáticos en el 39 % del textil); textil completo (probabilidad 0,86; compacidad 0,93, lagunas 0,0 %); estructura simétrica. Puntaje 75.</t>
+          <t>Fotografía regular (nitidez 1,29; textil de 1255 px de lado); colores identificables (probabilidad 0,98; 3 colores claramente distintos, 2 tonos, colorido 61); formas visibles (probabilidad 0,96; bordes cromáticos en el 39 % del textil); textil completo (probabilidad 0,94; compacidad 0,93, lagunas 0,0 %); estructura simétrica. Puntaje 94 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>70</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AB8" s="4" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,60; textil de 2632 px de lado); colores identificables (probabilidad 0,88; 3 colores claramente distintos, 3 tonos, colorido 71); formas visibles (probabilidad 0,88; bordes cromáticos en el 19 % del textil); textil completo (probabilidad 0,83; compacidad 0,81, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 70.</t>
+          <t>Fotografía deficiente (nitidez 0,60; textil de 2632 px de lado); colores identificables (probabilidad 0,97; 3 colores claramente distintos, 3 tonos, colorido 71); formas visibles (probabilidad 0,97; bordes cromáticos en el 19 % del textil); textil completo (probabilidad 0,95; compacidad 0,81, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 94 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AB9" s="4" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AD9" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,55; textil de 2971 px de lado); colores identificables (probabilidad 0,95; 3 colores claramente distintos, 2 tonos, colorido 67); formas visibles (probabilidad 0,94; bordes cromáticos en el 17 % del textil); textil completo (probabilidad 0,92; compacidad 0,85, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 75.</t>
+          <t>Fotografía deficiente (nitidez 0,55; textil de 2971 px de lado); colores identificables (probabilidad 0,99; 3 colores claramente distintos, 2 tonos, colorido 67); formas visibles (probabilidad 0,98; bordes cromáticos en el 17 % del textil); textil completo (probabilidad 0,98; compacidad 0,85, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 96 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>58.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC10" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD10" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,69; textil de 3620 px de lado); colores identificables (probabilidad 0,83; 6 colores claramente distintos, 3 tonos, colorido 55); formas parcialmente visibles (probabilidad 0,69; bordes cromáticos en el 21 % del textil); completitud incierta (probabilidad 0,42; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 58.</t>
+          <t>Fotografía deficiente (nitidez 0,69; textil de 3620 px de lado); colores identificables (probabilidad 0,96; 6 colores claramente distintos, 3 tonos, colorido 55); formas visibles (probabilidad 0,93; bordes cromáticos en el 21 % del textil); textil completo (probabilidad 0,86; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 88 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>77.2</v>
+        <v>96.7</v>
       </c>
       <c r="AB11" s="4" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AD11" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,32; textil de 2883 px de lado); colores identificables (probabilidad 0,99; 3 colores claramente distintos, 3 tonos, colorido 65); formas visibles (probabilidad 0,98; bordes cromáticos en el 61 % del textil); textil completo (probabilidad 0,92; compacidad 0,95, lagunas 0,0 %); estructura repetitiva. Puntaje 77 (imagen de referencia sugerida).</t>
+          <t>Fotografía regular (nitidez 1,32; textil de 2883 px de lado); colores identificables (probabilidad 0,99; 3 colores claramente distintos, 3 tonos, colorido 65); formas visibles (probabilidad 0,99; bordes cromáticos en el 61 % del textil); textil completo (probabilidad 0,96; compacidad 0,95, lagunas 0,0 %); estructura repetitiva. Puntaje 97 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>69.5</v>
+        <v>93.8</v>
       </c>
       <c r="AB12" s="4" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,01; textil de 3151 px de lado); colores identificables (probabilidad 0,94; 3 colores claramente distintos, 2 tonos, colorido 46); formas visibles (probabilidad 0,93; bordes cromáticos en el 31 % del textil); textil completo (probabilidad 0,81; compacidad 0,94, lagunas 0,0 %); estructura repetitiva. Puntaje 69.</t>
+          <t>Fotografía regular (nitidez 1,01; textil de 3151 px de lado); colores identificables (probabilidad 0,97; 3 colores claramente distintos, 2 tonos, colorido 46); formas visibles (probabilidad 0,97; bordes cromáticos en el 31 % del textil); textil completo (probabilidad 0,92; compacidad 0,94, lagunas 0,0 %); estructura repetitiva. Puntaje 94 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>59</v>
+        <v>88.3</v>
       </c>
       <c r="AB13" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,89; textil de 3898 px de lado); colores identificables (probabilidad 0,86; 5 colores claramente distintos, 3 tonos, colorido 57); formas visibles (probabilidad 0,75; bordes cromáticos en el 20 % del textil); completitud incierta (probabilidad 0,48; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 59.</t>
+          <t>Fotografía deficiente (nitidez 0,89; textil de 3898 px de lado); colores identificables (probabilidad 0,96; 5 colores claramente distintos, 3 tonos, colorido 57); formas visibles (probabilidad 0,92; bordes cromáticos en el 20 % del textil); textil completo (probabilidad 0,86; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 88 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>63.2</v>
+        <v>89.8</v>
       </c>
       <c r="AB14" s="4" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,60; textil de 3580 px de lado); colores identificables (probabilidad 0,87; 5 colores claramente distintos, 3 tonos, colorido 63); formas visibles (probabilidad 0,75; bordes cromáticos en el 22 % del textil); completitud incierta (probabilidad 0,55; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 63.</t>
+          <t>Fotografía deficiente (nitidez 0,60; textil de 3580 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 3 tonos, colorido 63); formas visibles (probabilidad 0,93; bordes cromáticos en el 22 % del textil); textil completo (probabilidad 0,89; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 90 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>61.5</v>
+        <v>93.2</v>
       </c>
       <c r="AB15" s="4" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,67; textil de 3897 px de lado); colores identificables (probabilidad 0,88; 7 colores claramente distintos, 3 tonos, colorido 67); formas visibles (probabilidad 0,72; bordes cromáticos en el 15 % del textil); completitud incierta (probabilidad 0,51; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 61.</t>
+          <t>Fotografía deficiente (nitidez 0,67; textil de 3897 px de lado); colores identificables (probabilidad 0,98; 7 colores claramente distintos, 3 tonos, colorido 67); formas visibles (probabilidad 0,95; bordes cromáticos en el 15 % del textil); textil completo (probabilidad 0,93; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 93 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="AB16" s="4" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,44; textil de 3696 px de lado); colores identificables (probabilidad 0,97; 6 colores claramente distintos, 3 tonos, colorido 65); formas visibles (probabilidad 0,91; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,81; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 74.</t>
+          <t>Fotografía buena (nitidez 1,44; textil de 3696 px de lado); colores identificables (probabilidad 0,99; 6 colores claramente distintos, 3 tonos, colorido 65); formas visibles (probabilidad 0,97; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,97; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 97 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="AB17" s="4" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,67; textil de 2029 px de lado); colores identificables (probabilidad 0,98; 5 colores claramente distintos, 3 tonos, colorido 79); formas visibles (probabilidad 0,93; bordes cromáticos en el 61 % del textil); textil completo (probabilidad 0,85; compacidad 0,77, lagunas 0,0 %); estructura no evidente. Puntaje 84 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 1,67; textil de 2029 px de lado); colores identificables (probabilidad 0,98; 5 colores claramente distintos, 3 tonos, colorido 79); formas visibles (probabilidad 0,97; bordes cromáticos en el 61 % del textil); textil completo (probabilidad 0,95; compacidad 0,77, lagunas 0,0 %); estructura no evidente. Puntaje 96 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AB18" s="4" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,57; textil de 2108 px de lado); colores identificables (probabilidad 0,94; 4 colores claramente distintos, 2 tonos, colorido 42); formas visibles (probabilidad 0,89; bordes cromáticos en el 44 % del textil); completitud incierta (probabilidad 0,63; compacidad 0,76, lagunas 0,0 %); estructura repetitiva. Puntaje 70.</t>
+          <t>Fotografía buena (nitidez 1,57; textil de 2108 px de lado); colores identificables (probabilidad 0,94; 4 colores claramente distintos, 2 tonos, colorido 42); formas visibles (probabilidad 0,91; bordes cromáticos en el 44 % del textil); textil completo (probabilidad 0,81; compacidad 0,76, lagunas 0,0 %); estructura repetitiva. Puntaje 86 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>75.7</v>
+        <v>94.5</v>
       </c>
       <c r="AB19" s="4" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AD19" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,93; textil de 2240 px de lado); colores identificables (probabilidad 0,96; 5 colores claramente distintos, 2 tonos, colorido 49); formas visibles (probabilidad 0,91; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,80; compacidad 0,88, lagunas 0,0 %); estructura repetitiva. Puntaje 76.</t>
+          <t>Fotografía deficiente (nitidez 0,93; textil de 2240 px de lado); colores identificables (probabilidad 0,98; 5 colores claramente distintos, 2 tonos, colorido 49); formas visibles (probabilidad 0,96; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,94; compacidad 0,88, lagunas 0,0 %); estructura repetitiva. Puntaje 95 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>80.3</v>
+        <v>97.3</v>
       </c>
       <c r="AB20" s="4" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t>Fecha de inicio posterior a 1532: el estudio abarca textiles incas y anteriores. Fotografía buena (nitidez 1,93; textil de 1528 px de lado); colores identificables (probabilidad 1,00; 3 colores claramente distintos, 2 tonos, colorido 60); formas visibles (probabilidad 0,99; bordes cromáticos en el 55 % del textil); textil completo (probabilidad 0,96; compacidad 0,93, lagunas 0,0 %); estructura repetitiva. Puntaje 80.</t>
+          <t>Fecha de inicio posterior a 1532: el estudio abarca textiles incas y anteriores. Fotografía buena (nitidez 1,93; textil de 1528 px de lado); colores identificables (probabilidad 0,99; 3 colores claramente distintos, 2 tonos, colorido 60); formas visibles (probabilidad 0,99; bordes cromáticos en el 55 % del textil); textil completo (probabilidad 0,97; compacidad 0,93, lagunas 0,0 %); estructura repetitiva. Puntaje 97.</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AB21" s="4" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AD21" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,39; textil de 2342 px de lado); colores identificables (probabilidad 0,92; 2 colores claramente distintos, 2 tonos, colorido 68); formas visibles (probabilidad 0,87; bordes cromáticos en el 38 % del textil); textil completo (probabilidad 0,91; compacidad 0,70, lagunas 0,0 %); estructura no evidente. Puntaje 72.</t>
+          <t>Fotografía buena (nitidez 1,39; textil de 2342 px de lado); colores identificables (probabilidad 0,94; 2 colores claramente distintos, 2 tonos, colorido 68); formas visibles (probabilidad 0,90; bordes cromáticos en el 38 % del textil); textil completo (probabilidad 0,96; compacidad 0,70, lagunas 0,0 %); estructura no evidente. Puntaje 94 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>71</v>
+        <v>72.8</v>
       </c>
       <c r="AB22" s="4" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t>Fecha de inicio posterior a 1532: el estudio abarca textiles incas y anteriores. Fotografía regular (nitidez 1,40; textil de 1431 px de lado); colores identificables (probabilidad 0,93; 3 colores claramente distintos, 3 tonos, colorido 42); formas visibles (probabilidad 0,89; bordes cromáticos en el 49 % del textil); completitud incierta (probabilidad 0,44; compacidad 0,71, lagunas 0,7 %); estructura no evidente. Puntaje 71.</t>
+          <t>Fecha de inicio posterior a 1532: el estudio abarca textiles incas y anteriores. Fotografía regular (nitidez 1,40; textil de 1431 px de lado); colores identificables (probabilidad 0,91; 3 colores claramente distintos, 3 tonos, colorido 42); formas visibles (probabilidad 0,88; bordes cromáticos en el 49 % del textil); completitud incierta (probabilidad 0,56; compacidad 0,71, lagunas 0,7 %); estructura no evidente. Puntaje 73.</t>
         </is>
       </c>
     </row>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="AA23" s="4" t="n">
-        <v>85.7</v>
+        <v>61.7</v>
       </c>
       <c r="AB23" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC23" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD23" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,04; textil de 344 px de lado); colores identificables (probabilidad 0,99; 5 colores claramente distintos, 6 tonos, colorido 58); formas visibles (probabilidad 0,96; bordes cromáticos en el 56 % del textil); textil incompleto (probabilidad 0,25; compacidad 0,54, lagunas 1,6 %); estructura no evidente. Puntaje 86 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 2,04; textil de 344 px de lado); colores identificables (probabilidad 0,98; 5 colores claramente distintos, 6 tonos, colorido 58); formas visibles (probabilidad 0,95; bordes cromáticos en el 56 % del textil); textil incompleto (probabilidad 0,34; compacidad 0,54, lagunas 1,6 %); estructura no evidente. Puntaje 62.</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="AA24" s="4" t="n">
-        <v>72.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="AB24" s="4" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="AD24" s="4" t="inlineStr">
         <is>
-          <t>Fecha de inicio posterior a 1532: el estudio abarca textiles incas y anteriores. Fotografía buena (nitidez 2,22; textil de 2133 px de lado); colores identificables (probabilidad 0,98; 3 colores claramente distintos, 3 tonos, colorido 58); formas visibles (probabilidad 0,98; bordes cromáticos en el 52 % del textil); textil completo (probabilidad 0,81; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 73.</t>
+          <t>Fecha de inicio posterior a 1532: el estudio abarca textiles incas y anteriores. Fotografía buena (nitidez 2,22; textil de 2133 px de lado); colores identificables (probabilidad 0,99; 3 colores claramente distintos, 3 tonos, colorido 58); formas visibles (probabilidad 0,99; bordes cromáticos en el 52 % del textil); textil completo (probabilidad 0,82; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 90.</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="AA25" s="4" t="n">
-        <v>79.40000000000001</v>
+        <v>30.5</v>
       </c>
       <c r="AB25" s="4" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AD25" s="4" t="inlineStr">
         <is>
-          <t>El textil mide 136 px de lado en la imagen institucional (mínimo 300). Fotografía deficiente (nitidez 0,35; textil de 136 px de lado); colores identificables (probabilidad 0,96; 6 colores claramente distintos, 4 tonos, colorido 51); formas visibles (probabilidad 0,83; bordes cromáticos en el 69 % del textil); textil incompleto (probabilidad 0,01; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura repetitiva. Puntaje 79.</t>
+          <t>El textil mide 136 px de lado en la imagen institucional (mínimo 300). Fotografía deficiente (nitidez 0,35; textil de 136 px de lado); colores identificables (probabilidad 0,86; 6 colores claramente distintos, 4 tonos, colorido 51); formas parcialmente visibles (probabilidad 0,70; bordes cromáticos en el 69 % del textil); textil incompleto (probabilidad 0,01; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura repetitiva. Puntaje 30.</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="AA26" s="4" t="n">
-        <v>79</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AB26" s="4" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AD26" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,64; textil de 3125 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 4 tonos, colorido 71); formas visibles (probabilidad 0,99; bordes cromáticos en el 69 % del textil); textil completo (probabilidad 0,91; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 79 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 1,64; textil de 3125 px de lado); colores identificables (probabilidad 1,00; 4 colores claramente distintos, 4 tonos, colorido 71); formas visibles (probabilidad 1,00; bordes cromáticos en el 69 % del textil); textil completo (probabilidad 0,97; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 97 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>72</v>
+        <v>93.2</v>
       </c>
       <c r="AB27" s="4" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AD27" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,03; textil de 3076 px de lado); colores no identificables (probabilidad 0,91; 1 color claramente distinto, 0 tonos, colorido 0); formas visibles (probabilidad 0,95; bordes cromáticos en el 42 % del textil); textil completo (probabilidad 0,92; compacidad 0,89, lagunas 0,5 %); estructura repetitiva. Puntaje 72.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,03; textil de 3076 px de lado); colores no identificables (probabilidad 0,87; 1 color claramente distinto, 0 tonos, colorido 0); formas visibles (probabilidad 0,96; bordes cromáticos en el 42 % del textil); textil completo (probabilidad 0,92; compacidad 0,89, lagunas 0,5 %); estructura repetitiva. Puntaje 93.</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>64.8</v>
+        <v>86.5</v>
       </c>
       <c r="AB28" s="4" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="AD28" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,73; textil de 2822 px de lado); colores identificables (probabilidad 0,85; 3 colores claramente distintos, 4 tonos, colorido 69); formas visibles (probabilidad 0,85; bordes cromáticos en el 19 % del textil); completitud incierta (probabilidad 0,61; toma cerrada, el contorno de la pieza no se ve); estructura repetitiva y simétrica. Puntaje 65.</t>
+          <t>Fotografía deficiente (nitidez 0,73; textil de 2822 px de lado); colores identificables (probabilidad 0,97; 3 colores claramente distintos, 4 tonos, colorido 69); formas visibles (probabilidad 0,97; bordes cromáticos en el 19 % del textil); textil completo (probabilidad 0,85; toma cerrada, el contorno de la pieza no se ve); estructura repetitiva y simétrica. Puntaje 87 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>64.7</v>
+        <v>76.8</v>
       </c>
       <c r="AB29" s="4" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="AD29" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,33; textil de 1405 px de lado); colores identificables (probabilidad 0,89; 1 color claramente distinto, 2 tonos, colorido 41); formas visibles (probabilidad 0,92; bordes cromáticos en el 13 % del textil); completitud incierta (probabilidad 0,69; compacidad 0,94, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 65.</t>
+          <t>Fotografía regular (nitidez 1,33; textil de 1405 px de lado); colores identificables (probabilidad 0,88; 1 color claramente distinto, 2 tonos, colorido 41); formas visibles (probabilidad 0,91; bordes cromáticos en el 13 % del textil); completitud incierta (probabilidad 0,62; compacidad 0,94, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 77.</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="AA30" s="4" t="n">
-        <v>66.5</v>
+        <v>89.7</v>
       </c>
       <c r="AB30" s="4" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="AD30" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,87; textil de 2210 px de lado); colores no identificables (probabilidad 0,93; 2 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,94; bordes cromáticos en el 13 % del textil); textil completo (probabilidad 0,77; compacidad 0,94, lagunas 0,2 %); estructura no evidente. Puntaje 67.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,87; textil de 2210 px de lado); colores no identificables (probabilidad 0,92; 2 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,94; bordes cromáticos en el 13 % del textil); textil completo (probabilidad 0,87; compacidad 0,94, lagunas 0,2 %); estructura no evidente. Puntaje 90.</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>79.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AB31" s="4" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AD31" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,88; textil de 3211 px de lado); colores identificables (probabilidad 1,00; 4 colores claramente distintos, 4 tonos, colorido 70); formas visibles (probabilidad 0,99; bordes cromáticos en el 68 % del textil); textil completo (probabilidad 0,95; compacidad 0,87, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 79 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 1,88; textil de 3211 px de lado); colores identificables (probabilidad 1,00; 4 colores claramente distintos, 4 tonos, colorido 70); formas visibles (probabilidad 1,00; bordes cromáticos en el 68 % del textil); textil completo (probabilidad 0,98; compacidad 0,87, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 98 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="AA32" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AB32" s="4" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AD32" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,81; textil de 2762 px de lado); colores identificables (probabilidad 1,00; 5 colores claramente distintos, 4 tonos, colorido 59); formas visibles (probabilidad 0,99; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,91; compacidad 0,97, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 79 (imagen de referencia sugerida).</t>
+          <t>Fotografía deficiente (nitidez 0,81; textil de 2762 px de lado); colores identificables (probabilidad 1,00; 5 colores claramente distintos, 4 tonos, colorido 59); formas visibles (probabilidad 0,99; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,97; compacidad 0,97, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 97 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>56.7</v>
+        <v>44.3</v>
       </c>
       <c r="AB33" s="4" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="AD33" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,07; textil de 1255 px de lado); colores identificables (probabilidad 0,89; 3 colores claramente distintos, 3 tonos, colorido 68); formas visibles (probabilidad 0,81; bordes cromáticos en el 50 % del textil); textil incompleto (probabilidad 0,12; compacidad 0,82, lagunas 0,0 %); estructura no evidente. Puntaje 57.</t>
+          <t>Fotografía deficiente (nitidez 1,07; textil de 1255 px de lado); colores identificables (probabilidad 0,82; 3 colores claramente distintos, 3 tonos, colorido 68); formas parcialmente visibles (probabilidad 0,69; bordes cromáticos en el 50 % del textil); textil incompleto (probabilidad 0,25; compacidad 0,82, lagunas 0,0 %); estructura no evidente. Puntaje 44.</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="AA34" s="4" t="n">
-        <v>78.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AB34" s="4" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="AD34" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,82; textil de 1350 px de lado); colores identificables (probabilidad 0,98; 3 colores claramente distintos, 4 tonos, colorido 54); formas visibles (probabilidad 0,97; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,84; compacidad 0,92, lagunas 0,0 %); estructura simétrica. Puntaje 79 (imagen de referencia sugerida).</t>
+          <t>Fotografía deficiente (nitidez 0,82; textil de 1350 px de lado); colores identificables (probabilidad 0,98; 3 colores claramente distintos, 4 tonos, colorido 54); formas visibles (probabilidad 0,98; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,92; compacidad 0,92, lagunas 0,0 %); estructura simétrica. Puntaje 93 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="AA35" s="4" t="n">
-        <v>61.5</v>
+        <v>89.5</v>
       </c>
       <c r="AB35" s="4" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AD35" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,70; textil de 3548 px de lado); colores identificables (probabilidad 0,82; 2 colores claramente distintos, 1 tono, colorido 32); formas visibles (probabilidad 0,80; bordes cromáticos en el 5 % del textil); textil completo (probabilidad 0,79; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 62.</t>
+          <t>Fotografía deficiente (nitidez 0,70; textil de 3548 px de lado); colores identificables (probabilidad 0,94; 2 colores claramente distintos, 1 tono, colorido 32); formas visibles (probabilidad 0,90; bordes cromáticos en el 5 % del textil); textil completo (probabilidad 0,91; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 90 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="AA36" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="AB36" s="4" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AD36" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,04; textil de 1221 px de lado); colores identificables (probabilidad 0,88; 3 colores claramente distintos, 3 tonos, colorido 78); formas visibles (probabilidad 0,78; bordes cromáticos en el 31 % del textil); completitud incierta (probabilidad 0,56; compacidad 0,63, lagunas 0,4 %); estructura no evidente. Puntaje 66.</t>
+          <t>Fotografía regular (nitidez 1,04; textil de 1221 px de lado); colores identificables (probabilidad 0,93; 3 colores claramente distintos, 3 tonos, colorido 78); formas visibles (probabilidad 0,82; bordes cromáticos en el 31 % del textil); textil completo (probabilidad 0,77; compacidad 0,63, lagunas 0,4 %); estructura no evidente. Puntaje 82.</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="AA37" s="4" t="n">
-        <v>77.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AB37" s="4" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="AD37" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,83; textil de 1738 px de lado); colores identificables (probabilidad 0,98; 4 colores claramente distintos, 3 tonos, colorido 65); formas visibles (probabilidad 0,96; bordes cromáticos en el 27 % del textil); textil completo (probabilidad 0,84; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura simétrica. Puntaje 78 (imagen de referencia sugerida).</t>
+          <t>Fotografía deficiente (nitidez 0,83; textil de 1738 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 3 tonos, colorido 65); formas visibles (probabilidad 0,98; bordes cromáticos en el 27 % del textil); textil completo (probabilidad 0,90; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura simétrica. Puntaje 92 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="AA38" s="4" t="n">
-        <v>71.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AB38" s="4" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="AD38" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,42; textil de 892 px de lado); colores identificables (probabilidad 0,93; 2 colores claramente distintos, 2 tonos, colorido 39); formas visibles (probabilidad 0,92; bordes cromáticos en el 42 % del textil); completitud incierta (probabilidad 0,65; compacidad 0,91, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 72.</t>
+          <t>Fotografía regular (nitidez 1,42; textil de 892 px de lado); colores identificables (probabilidad 0,92; 2 colores claramente distintos, 2 tonos, colorido 39); formas visibles (probabilidad 0,92; bordes cromáticos en el 42 % del textil); completitud incierta (probabilidad 0,54; compacidad 0,91, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 73.</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="AA39" s="4" t="n">
-        <v>69.8</v>
+        <v>78.3</v>
       </c>
       <c r="AB39" s="4" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AD39" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,75; textil de 1285 px de lado); colores identificables (probabilidad 0,94; 1 color claramente distinto, 2 tonos, colorido 30); formas visibles (probabilidad 0,95; bordes cromáticos en el 33 % del textil); textil completo (probabilidad 0,73; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 70.</t>
+          <t>Fotografía buena (nitidez 1,75; textil de 1285 px de lado); colores identificables (probabilidad 0,92; 1 color claramente distinto, 2 tonos, colorido 30); formas visibles (probabilidad 0,94; bordes cromáticos en el 33 % del textil); completitud incierta (probabilidad 0,61; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 78.</t>
         </is>
       </c>
     </row>
@@ -6031,21 +6031,21 @@
         </is>
       </c>
       <c r="AA40" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="AB40" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC40" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD40" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,96; textil de 1129 px de lado); colores identificables (probabilidad 0,95; 4 colores claramente distintos, 3 tonos, colorido 51); formas visibles (probabilidad 0,89; bordes cromáticos en el 47 % del textil); textil incompleto (probabilidad 0,28; compacidad 0,81, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 67.</t>
+          <t>Fotografía deficiente (nitidez 0,96; textil de 1129 px de lado); colores identificables (probabilidad 0,95; 4 colores claramente distintos, 3 tonos, colorido 51); formas visibles (probabilidad 0,92; bordes cromáticos en el 47 % del textil); textil incompleto (probabilidad 0,33; compacidad 0,81, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 60.</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="AA41" s="4" t="n">
-        <v>40.6</v>
+        <v>10.4</v>
       </c>
       <c r="AB41" s="4" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="AD41" s="4" t="inlineStr">
         <is>
-          <t>El textil mide 276 px de lado en la imagen institucional (mínimo 300). Fotografía regular (nitidez 1,73; textil de 276 px de lado); colores no identificables (probabilidad 0,66; 4 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,52; bordes cromáticos en el 44 % del textil); textil incompleto (probabilidad 0,02; compacidad 0,60, lagunas 0,2 %, el título dice «fragment»); estructura no evidente. Puntaje 41.</t>
+          <t>El textil mide 276 px de lado en la imagen institucional (mínimo 300). Fotografía regular (nitidez 1,73; textil de 276 px de lado); colores no identificables (probabilidad 0,26; 4 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,20; bordes cromáticos en el 44 % del textil); textil incompleto (probabilidad 0,01; compacidad 0,60, lagunas 0,2 %, el título dice «fragment»); estructura no evidente. Puntaje 10.</t>
         </is>
       </c>
     </row>
@@ -6251,21 +6251,21 @@
         </is>
       </c>
       <c r="AA42" s="4" t="n">
-        <v>62.2</v>
+        <v>60.8</v>
       </c>
       <c r="AB42" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC42" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD42" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,83; textil de 823 px de lado); colores identificables (probabilidad 0,85; 3 colores claramente distintos, 2 tonos, colorido 37); formas visibles (probabilidad 0,79; bordes cromáticos en el 36 % del textil); textil incompleto (probabilidad 0,37; compacidad 0,70, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 62.</t>
+          <t>Fotografía buena (nitidez 1,83; textil de 823 px de lado); colores identificables (probabilidad 0,84; 3 colores claramente distintos, 2 tonos, colorido 37); formas visibles (probabilidad 0,80; bordes cromáticos en el 36 % del textil); textil incompleto (probabilidad 0,35; compacidad 0,70, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 61.</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="AA43" s="4" t="n">
-        <v>80.7</v>
+        <v>90.2</v>
       </c>
       <c r="AB43" s="4" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="AD43" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,14; textil de 1576 px de lado); colores identificables (probabilidad 0,98; 3 colores claramente distintos, 3 tonos, colorido 44); formas visibles (probabilidad 0,97; bordes cromáticos en el 48 % del textil); textil completo (probabilidad 0,87; compacidad 0,92, lagunas 0,0 %, el título dice «fragment»); estructura simétrica. Puntaje 81 (imagen de referencia sugerida).</t>
+          <t>Fotografía regular (nitidez 1,14; textil de 1576 px de lado); colores identificables (probabilidad 0,99; 3 colores claramente distintos, 3 tonos, colorido 44); formas visibles (probabilidad 0,98; bordes cromáticos en el 48 % del textil); textil completo (probabilidad 0,87; compacidad 0,92, lagunas 0,0 %, el título dice «fragment»); estructura simétrica. Puntaje 90 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="AA44" s="4" t="n">
-        <v>63</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AB44" s="4" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="AD44" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,40; textil de 3002 px de lado); colores identificables (probabilidad 0,81; 3 colores claramente distintos, 3 tonos, colorido 36); formas visibles (probabilidad 0,87; bordes cromáticos en el 9 % del textil); completitud incierta (probabilidad 0,62; compacidad 0,96, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 63.</t>
+          <t>Fotografía deficiente (nitidez 0,40; textil de 3002 px de lado); colores identificables (probabilidad 0,95; 3 colores claramente distintos, 3 tonos, colorido 36); formas visibles (probabilidad 0,98; bordes cromáticos en el 9 % del textil); textil completo (probabilidad 0,88; compacidad 0,96, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 88 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -6557,21 +6557,21 @@
         </is>
       </c>
       <c r="AA45" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>49.7</v>
       </c>
       <c r="AB45" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC45" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD45" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,05; textil de 390 px de lado); colores identificables (probabilidad 0,97; 3 colores claramente distintos, 4 tonos, colorido 47); formas visibles (probabilidad 0,95; bordes cromáticos en el 40 % del textil); textil incompleto (probabilidad 0,22; compacidad 0,90, lagunas 0,8 %, el título dice «fragment»); estructura repetitiva. Puntaje 70.</t>
+          <t>Fotografía deficiente (nitidez 1,05; textil de 390 px de lado); colores identificables (probabilidad 0,96; 3 colores claramente distintos, 4 tonos, colorido 47); formas visibles (probabilidad 0,94; bordes cromáticos en el 40 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,90, lagunas 0,8 %, el título dice «fragment»); estructura repetitiva. Puntaje 50.</t>
         </is>
       </c>
     </row>
@@ -6659,21 +6659,21 @@
         </is>
       </c>
       <c r="AA46" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="AB46" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC46" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD46" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,26; textil de 683 px de lado); colores identificables (probabilidad 0,92; 3 colores claramente distintos, 3 tonos, colorido 103); formas visibles (probabilidad 0,80; bordes cromáticos en el 9 % del textil); completitud incierta (probabilidad 0,43; toma cerrada, el contorno de la pieza no se ve); estructura repetitiva y simétrica. Puntaje 67.</t>
+          <t>Fotografía deficiente (nitidez 0,26; textil de 683 px de lado); colores identificables (probabilidad 0,95; 3 colores claramente distintos, 3 tonos, colorido 103); formas visibles (probabilidad 0,79; bordes cromáticos en el 9 % del textil); completitud incierta (probabilidad 0,63; toma cerrada, el contorno de la pieza no se ve); estructura repetitiva y simétrica. Puntaje 66.</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="AA47" s="4" t="n">
-        <v>82.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AB47" s="4" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="AD47" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,14; textil de 977 px de lado); colores identificables (probabilidad 1,00; 3 colores claramente distintos, 7 tonos, colorido 59); formas visibles (probabilidad 0,99; bordes cromáticos en el 74 % del textil); completitud incierta (probabilidad 0,59; compacidad 0,86, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 82 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 2,14; textil de 977 px de lado); colores identificables (probabilidad 1,00; 3 colores claramente distintos, 7 tonos, colorido 59); formas visibles (probabilidad 1,00; bordes cromáticos en el 74 % del textil); completitud incierta (probabilidad 0,52; compacidad 0,86, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 72.</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="AA48" s="4" t="n">
-        <v>83.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="AB48" s="4" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="AD48" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,93; textil de 432 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 2 tonos, colorido 74); formas visibles (probabilidad 0,98; bordes cromáticos en el 25 % del textil); textil completo (probabilidad 0,85; compacidad 0,96, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva y simétrica. Puntaje 84 (imagen de referencia sugerida).</t>
+          <t>Fotografía deficiente (nitidez 0,93; textil de 432 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 2 tonos, colorido 74); formas visibles (probabilidad 0,94; bordes cromáticos en el 25 % del textil); textil completo (probabilidad 0,83; compacidad 0,96, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva y simétrica. Puntaje 86 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -6965,21 +6965,21 @@
         </is>
       </c>
       <c r="AA49" s="4" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AB49" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC49" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD49" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,29; textil de 539 px de lado); colores identificables (probabilidad 0,95; 1 color claramente distinto, 3 tonos, colorido 22); formas visibles (probabilidad 0,97; bordes cromáticos en el 8 % del textil); completitud incierta (probabilidad 0,63; compacidad 0,95, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía buena (nitidez 2,29; textil de 539 px de lado); colores identificables (probabilidad 0,89; 1 color claramente distinto, 3 tonos, colorido 22); formas visibles (probabilidad 0,93; bordes cromáticos en el 8 % del textil); completitud incierta (probabilidad 0,44; compacidad 0,95, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 69.</t>
         </is>
       </c>
     </row>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="AA50" s="4" t="n">
-        <v>75</v>
+        <v>43.2</v>
       </c>
       <c r="AB50" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC50" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD50" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,15; textil de 405 px de lado); colores identificables (probabilidad 0,81; 1 color claramente distinto, 3 tonos, colorido 43); formas visibles (probabilidad 0,89; bordes cromáticos en el 39 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,75, lagunas 20,5 %, el título dice «fragment»); estructura no evidente. Puntaje 75.</t>
+          <t>Fotografía buena (nitidez 2,15; textil de 405 px de lado); colores identificables (probabilidad 0,76; 1 color claramente distinto, 3 tonos, colorido 43); formas visibles (probabilidad 0,81; bordes cromáticos en el 39 % del textil); textil incompleto (probabilidad 0,12; compacidad 0,75, lagunas 20,5 %, el título dice «fragment»); estructura no evidente. Puntaje 43.</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="AA51" s="4" t="n">
-        <v>20.7</v>
+        <v>17.3</v>
       </c>
       <c r="AB51" s="4" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="AD51" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,05; textil de 1389 px de lado); colores no identificables (probabilidad 0,31; 2 colores claramente distintos, 2 tonos, colorido 33); formas no visibles (probabilidad 0,28; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,02; compacidad 0,47, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 21.</t>
+          <t>Fotografía deficiente (nitidez 1,05; textil de 1389 px de lado); colores parcialmente identificables (probabilidad 0,41; 2 colores claramente distintos, 2 tonos, colorido 33); formas no visibles (probabilidad 0,32; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,03; compacidad 0,47, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 17.</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="AA52" s="4" t="n">
-        <v>53.9</v>
+        <v>43.3</v>
       </c>
       <c r="AB52" s="4" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="AD52" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,49; textil de 769 px de lado); colores identificables (probabilidad 0,74; 2 colores claramente distintos, 2 tonos, colorido 35); formas parcialmente visibles (probabilidad 0,68; bordes cromáticos en el 12 % del textil); textil incompleto (probabilidad 0,19; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura simétrica. Puntaje 54.</t>
+          <t>Fotografía deficiente (nitidez 0,49; textil de 769 px de lado); colores identificables (probabilidad 0,82; 2 colores claramente distintos, 2 tonos, colorido 35); formas parcialmente visibles (probabilidad 0,70; bordes cromáticos en el 12 % del textil); textil incompleto (probabilidad 0,20; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura simétrica. Puntaje 43.</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="AA53" s="4" t="n">
-        <v>58.3</v>
+        <v>60.7</v>
       </c>
       <c r="AB53" s="4" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AD53" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,84; textil de 1625 px de lado); colores identificables (probabilidad 0,87; 3 colores claramente distintos, 2 tonos, colorido 51); formas visibles (probabilidad 0,77; bordes cromáticos en el 43 % del textil); textil incompleto (probabilidad 0,32; compacidad 0,80, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 58.</t>
+          <t>Fotografía deficiente (nitidez 0,84; textil de 1625 px de lado); colores identificables (probabilidad 0,93; 3 colores claramente distintos, 2 tonos, colorido 51); formas visibles (probabilidad 0,86; bordes cromáticos en el 43 % del textil); textil incompleto (probabilidad 0,35; compacidad 0,80, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 61.</t>
         </is>
       </c>
     </row>
@@ -7491,11 +7491,11 @@
         </is>
       </c>
       <c r="AA54" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>32.1</v>
       </c>
       <c r="AB54" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>descartar</t>
         </is>
       </c>
       <c r="AC54" s="4" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AD54" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,17; textil de 335 px de lado); colores identificables (probabilidad 0,77; 2 colores claramente distintos, 3 tonos, colorido 43); formas visibles (probabilidad 0,79; bordes cromáticos en el 39 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,41, lagunas 14,9 %, el título dice «fragment»); estructura no evidente. Puntaje 70.</t>
+          <t>Fotografía buena (nitidez 2,17; textil de 335 px de lado); colores identificables (probabilidad 0,74; 2 colores claramente distintos, 3 tonos, colorido 43); formas parcialmente visibles (probabilidad 0,66; bordes cromáticos en el 39 % del textil); textil incompleto (probabilidad 0,05; compacidad 0,41, lagunas 14,9 %, el título dice «fragment»); estructura no evidente. Puntaje 32.</t>
         </is>
       </c>
     </row>
@@ -7593,21 +7593,21 @@
         </is>
       </c>
       <c r="AA55" s="4" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AB55" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC55" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD55" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,63; textil de 534 px de lado); colores identificables (probabilidad 0,93; 2 colores claramente distintos, 2 tonos, colorido 28); formas visibles (probabilidad 0,93; bordes cromáticos en el 29 % del textil); textil incompleto (probabilidad 0,38; compacidad 0,91, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 68.</t>
+          <t>Fotografía regular (nitidez 1,63; textil de 534 px de lado); colores identificables (probabilidad 0,87; 2 colores claramente distintos, 2 tonos, colorido 28); formas visibles (probabilidad 0,90; bordes cromáticos en el 29 % del textil); textil incompleto (probabilidad 0,26; compacidad 0,91, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva. Puntaje 56.</t>
         </is>
       </c>
     </row>
@@ -7695,21 +7695,21 @@
         </is>
       </c>
       <c r="AA56" s="4" t="n">
-        <v>69</v>
+        <v>52.9</v>
       </c>
       <c r="AB56" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD56" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,95; textil de 482 px de lado); colores identificables (probabilidad 0,96; 1 color claramente distinto, 3 tonos, colorido 43); formas visibles (probabilidad 0,96; bordes cromáticos en el 36 % del textil); completitud incierta (probabilidad 0,40; compacidad 0,92, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía buena (nitidez 1,95; textil de 482 px de lado); colores identificables (probabilidad 0,92; 1 color claramente distinto, 3 tonos, colorido 43); formas visibles (probabilidad 0,90; bordes cromáticos en el 36 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,92, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 53.</t>
         </is>
       </c>
     </row>
@@ -7797,21 +7797,21 @@
         </is>
       </c>
       <c r="AA57" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="AB57" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC57" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD57" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,49; textil de 1269 px de lado); colores identificables (probabilidad 0,82; 2 colores claramente distintos, 2 tonos, colorido 37); formas visibles (probabilidad 0,90; bordes cromáticos en el 32 % del textil); textil incompleto (probabilidad 0,36; compacidad 0,91, lagunas 17,1 %, el título dice «fragment»); estructura no evidente. Puntaje 67.</t>
+          <t>Fotografía buena (nitidez 2,49; textil de 1269 px de lado); colores identificables (probabilidad 0,82; 2 colores claramente distintos, 2 tonos, colorido 37); formas visibles (probabilidad 0,91; bordes cromáticos en el 32 % del textil); textil incompleto (probabilidad 0,38; compacidad 0,91, lagunas 17,1 %, el título dice «fragment»); estructura no evidente. Puntaje 64.</t>
         </is>
       </c>
     </row>
@@ -7899,21 +7899,21 @@
         </is>
       </c>
       <c r="AA58" s="4" t="n">
-        <v>68</v>
+        <v>49.8</v>
       </c>
       <c r="AB58" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC58" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD58" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,78; textil de 481 px de lado); colores identificables (probabilidad 0,93; 3 colores claramente distintos, 3 tonos, colorido 50); formas visibles (probabilidad 0,87; bordes cromáticos en el 26 % del textil); textil incompleto (probabilidad 0,24; compacidad 0,82, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 68.</t>
+          <t>Fotografía deficiente (nitidez 0,78; textil de 481 px de lado); colores identificables (probabilidad 0,90; 3 colores claramente distintos, 3 tonos, colorido 50); formas visibles (probabilidad 0,81; bordes cromáticos en el 26 % del textil); textil incompleto (probabilidad 0,22; compacidad 0,82, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 50.</t>
         </is>
       </c>
     </row>
@@ -8001,21 +8001,21 @@
         </is>
       </c>
       <c r="AA59" s="4" t="n">
-        <v>62.5</v>
+        <v>58.2</v>
       </c>
       <c r="AB59" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC59" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD59" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,54; textil de 1391 px de lado); colores identificables (probabilidad 0,71; 1 color claramente distinto, 2 tonos, colorido 35); formas visibles (probabilidad 0,86; bordes cromáticos en el 34 % del textil); textil incompleto (probabilidad 0,37; compacidad 0,80, lagunas 16,4 %, el título dice «fragment»); estructura no evidente. Puntaje 63.</t>
+          <t>Fotografía buena (nitidez 2,54; textil de 1391 px de lado); colores identificables (probabilidad 0,70; 1 color claramente distinto, 2 tonos, colorido 35); formas visibles (probabilidad 0,86; bordes cromáticos en el 34 % del textil); textil incompleto (probabilidad 0,29; compacidad 0,80, lagunas 16,4 %, el título dice «fragment»); estructura no evidente. Puntaje 58.</t>
         </is>
       </c>
     </row>
@@ -8119,21 +8119,21 @@
         </is>
       </c>
       <c r="AA60" s="4" t="n">
-        <v>57.9</v>
+        <v>31.8</v>
       </c>
       <c r="AB60" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>descartar</t>
         </is>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD60" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,33; textil de 594 px de lado); colores identificables (probabilidad 0,75; 2 colores claramente distintos, 2 tonos, colorido 38); formas visibles (probabilidad 0,74; bordes cromáticos en el 26 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,51, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 58.</t>
+          <t>Fotografía regular (nitidez 1,33; textil de 594 px de lado); colores identificables (probabilidad 0,77; 2 colores claramente distintos, 2 tonos, colorido 38); formas parcialmente visibles (probabilidad 0,68; bordes cromáticos en el 26 % del textil); textil incompleto (probabilidad 0,04; compacidad 0,51, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 32.</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="AA61" s="4" t="n">
-        <v>20.7</v>
+        <v>17.3</v>
       </c>
       <c r="AB61" s="4" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="AD61" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,05; textil de 1389 px de lado); colores no identificables (probabilidad 0,31; 2 colores claramente distintos, 2 tonos, colorido 33); formas no visibles (probabilidad 0,28; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,02; compacidad 0,47, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 21.</t>
+          <t>Fotografía deficiente (nitidez 1,05; textil de 1389 px de lado); colores parcialmente identificables (probabilidad 0,41; 2 colores claramente distintos, 2 tonos, colorido 33); formas no visibles (probabilidad 0,32; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,03; compacidad 0,47, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 17.</t>
         </is>
       </c>
     </row>
@@ -8339,21 +8339,21 @@
         </is>
       </c>
       <c r="AA62" s="4" t="n">
-        <v>62.3</v>
+        <v>45.8</v>
       </c>
       <c r="AB62" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC62" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD62" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,10; textil de 1292 px de lado); colores identificables (probabilidad 0,82; 2 colores claramente distintos, 2 tonos, colorido 34); formas visibles (probabilidad 0,85; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,18; compacidad 0,58, lagunas 7,2 %, el título dice «fragment»); estructura no evidente. Puntaje 62.</t>
+          <t>Fotografía buena (nitidez 2,10; textil de 1292 px de lado); colores identificables (probabilidad 0,88; 2 colores claramente distintos, 2 tonos, colorido 34); formas visibles (probabilidad 0,87; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,14; compacidad 0,58, lagunas 7,2 %, el título dice «fragment»); estructura no evidente. Puntaje 46.</t>
         </is>
       </c>
     </row>
@@ -8441,21 +8441,21 @@
         </is>
       </c>
       <c r="AA63" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>57.8</v>
       </c>
       <c r="AB63" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC63" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD63" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,57; textil de 402 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 2 tonos, colorido 56); formas visibles (probabilidad 0,93; bordes cromáticos en el 42 % del textil); completitud incierta (probabilidad 0,47; compacidad 0,87, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 70.</t>
+          <t>Fotografía regular (nitidez 1,57; textil de 402 px de lado); colores identificables (probabilidad 0,93; 2 colores claramente distintos, 2 tonos, colorido 56); formas visibles (probabilidad 0,85; bordes cromáticos en el 42 % del textil); textil incompleto (probabilidad 0,33; compacidad 0,87, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 58.</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="AA64" s="4" t="n">
-        <v>47.6</v>
+        <v>49</v>
       </c>
       <c r="AB64" s="4" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="AD64" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,98; textil de 1532 px de lado); colores parcialmente identificables (probabilidad 0,55; 2 colores claramente distintos, 2 tonos, colorido 33); formas visibles (probabilidad 0,71; bordes cromáticos en el 21 % del textil); textil incompleto (probabilidad 0,12; compacidad 0,83, lagunas 14,9 %, el título dice «fragment»); estructura no evidente. Puntaje 48.</t>
+          <t>Fotografía buena (nitidez 1,98; textil de 1532 px de lado); colores identificables (probabilidad 0,71; 2 colores claramente distintos, 2 tonos, colorido 33); formas visibles (probabilidad 0,81; bordes cromáticos en el 21 % del textil); textil incompleto (probabilidad 0,19; compacidad 0,83, lagunas 14,9 %, el título dice «fragment»); estructura no evidente. Puntaje 49.</t>
         </is>
       </c>
     </row>
@@ -8645,21 +8645,21 @@
         </is>
       </c>
       <c r="AA65" s="4" t="n">
-        <v>68.8</v>
+        <v>63.7</v>
       </c>
       <c r="AB65" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC65" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD65" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,39; textil de 1388 px de lado); colores identificables (probabilidad 0,77; 1 color claramente distinto, 2 tonos, colorido 36); formas visibles (probabilidad 0,91; bordes cromáticos en el 34 % del textil); completitud incierta (probabilidad 0,45; compacidad 0,88, lagunas 19,3 %, el título dice «fragment»); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía buena (nitidez 2,39; textil de 1388 px de lado); colores identificables (probabilidad 0,78; 1 color claramente distinto, 2 tonos, colorido 36); formas visibles (probabilidad 0,91; bordes cromáticos en el 34 % del textil); textil incompleto (probabilidad 0,38; compacidad 0,88, lagunas 19,3 %, el título dice «fragment»); estructura no evidente. Puntaje 64.</t>
         </is>
       </c>
     </row>
@@ -8747,21 +8747,21 @@
         </is>
       </c>
       <c r="AA66" s="4" t="n">
-        <v>79.2</v>
+        <v>61.2</v>
       </c>
       <c r="AB66" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD66" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,42; textil de 405 px de lado); colores identificables (probabilidad 0,99; 2 colores claramente distintos, 6 tonos, colorido 32); formas visibles (probabilidad 0,99; bordes cromáticos en el 31 % del textil); completitud incierta (probabilidad 0,54; compacidad 0,95, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 79 (imagen de referencia sugerida).</t>
+          <t>Fotografía regular (nitidez 1,42; textil de 405 px de lado); colores identificables (probabilidad 0,99; 2 colores claramente distintos, 6 tonos, colorido 32); formas visibles (probabilidad 0,99; bordes cromáticos en el 31 % del textil); textil incompleto (probabilidad 0,37; compacidad 0,95, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 61.</t>
         </is>
       </c>
     </row>
@@ -8849,21 +8849,21 @@
         </is>
       </c>
       <c r="AA67" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>60.5</v>
       </c>
       <c r="AB67" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC67" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD67" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,10; textil de 541 px de lado); colores identificables (probabilidad 0,97; 2 colores claramente distintos, 2 tonos, colorido 20); formas visibles (probabilidad 0,96; bordes cromáticos en el 18 % del textil); completitud incierta (probabilidad 0,52; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía buena (nitidez 2,10; textil de 541 px de lado); colores identificables (probabilidad 0,89; 2 colores claramente distintos, 2 tonos, colorido 20); formas visibles (probabilidad 0,90; bordes cromáticos en el 18 % del textil); textil incompleto (probabilidad 0,32; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 61.</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="AA68" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>34.9</v>
       </c>
       <c r="AB68" s="4" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="AD68" s="4" t="inlineStr">
         <is>
-          <t>El textil mide 259 px de lado en la imagen institucional (mínimo 300). Fotografía deficiente (nitidez 0,85; textil de 259 px de lado); colores identificables (probabilidad 0,90; 2 colores claramente distintos, 3 tonos, colorido 38); formas visibles (probabilidad 0,85; bordes cromáticos en el 40 % del textil); textil incompleto (probabilidad 0,14; compacidad 0,89, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 64.</t>
+          <t>El textil mide 259 px de lado en la imagen institucional (mínimo 300). Fotografía deficiente (nitidez 0,85; textil de 259 px de lado); colores identificables (probabilidad 0,81; 2 colores claramente distintos, 3 tonos, colorido 38); formas visibles (probabilidad 0,71; bordes cromáticos en el 40 % del textil); textil incompleto (probabilidad 0,06; compacidad 0,89, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 35.</t>
         </is>
       </c>
     </row>
@@ -9069,21 +9069,21 @@
         </is>
       </c>
       <c r="AA69" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>48.1</v>
       </c>
       <c r="AB69" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC69" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD69" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,68; textil de 355 px de lado); colores identificables (probabilidad 0,98; 2 colores claramente distintos, 5 tonos, colorido 43); formas visibles (probabilidad 0,98; bordes cromáticos en el 52 % del textil); textil incompleto (probabilidad 0,29; compacidad 0,90, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 76.</t>
+          <t>Fotografía regular (nitidez 1,68; textil de 355 px de lado); colores identificables (probabilidad 0,97; 2 colores claramente distintos, 5 tonos, colorido 43); formas visibles (probabilidad 0,95; bordes cromáticos en el 52 % del textil); textil incompleto (probabilidad 0,12; compacidad 0,90, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 48.</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="AA70" s="4" t="n">
-        <v>45.7</v>
+        <v>27.4</v>
       </c>
       <c r="AB70" s="4" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AD70" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,93; textil de 670 px de lado); colores parcialmente identificables (probabilidad 0,53; 2 colores claramente distintos, 2 tonos, colorido 34); formas parcialmente visibles (probabilidad 0,50; bordes cromáticos en el 31 % del textil); textil incompleto (probabilidad 0,07; compacidad 0,28, lagunas 4,7 %, el título dice «fragment»); estructura no evidente. Puntaje 46.</t>
+          <t>Fotografía buena (nitidez 1,93; textil de 670 px de lado); colores parcialmente identificables (probabilidad 0,62; 2 colores claramente distintos, 2 tonos, colorido 34); formas parcialmente visibles (probabilidad 0,46; bordes cromáticos en el 31 % del textil); textil incompleto (probabilidad 0,05; compacidad 0,28, lagunas 4,7 %, el título dice «fragment»); estructura no evidente. Puntaje 27.</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="AA71" s="4" t="n">
-        <v>54</v>
+        <v>49.7</v>
       </c>
       <c r="AB71" s="4" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AD71" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,86; textil de 1434 px de lado); colores parcialmente identificables (probabilidad 0,69; 2 colores claramente distintos, 2 tonos, colorido 31); formas visibles (probabilidad 0,79; bordes cromáticos en el 24 % del textil); textil incompleto (probabilidad 0,12; compacidad 0,90, lagunas 15,0 %, el título dice «fragment»); estructura no evidente. Puntaje 54.</t>
+          <t>Fotografía buena (nitidez 1,86; textil de 1434 px de lado); colores identificables (probabilidad 0,81; 2 colores claramente distintos, 2 tonos, colorido 31); formas visibles (probabilidad 0,85; bordes cromáticos en el 24 % del textil); textil incompleto (probabilidad 0,19; compacidad 0,90, lagunas 15,0 %, el título dice «fragment»); estructura no evidente. Puntaje 50.</t>
         </is>
       </c>
     </row>
@@ -9391,21 +9391,21 @@
         </is>
       </c>
       <c r="AA72" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="AB72" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD72" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,53; textil de 516 px de lado); colores identificables (probabilidad 0,90; 2 colores claramente distintos, 2 tonos, colorido 27); formas visibles (probabilidad 0,90; bordes cromáticos en el 23 % del textil); textil incompleto (probabilidad 0,27; compacidad 0,90, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 64.</t>
+          <t>Fotografía regular (nitidez 1,53; textil de 516 px de lado); colores identificables (probabilidad 0,79; 2 colores claramente distintos, 2 tonos, colorido 27); formas visibles (probabilidad 0,81; bordes cromáticos en el 23 % del textil); textil incompleto (probabilidad 0,18; compacidad 0,90, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 48.</t>
         </is>
       </c>
     </row>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="AA73" s="4" t="n">
-        <v>66.5</v>
+        <v>49.8</v>
       </c>
       <c r="AB73" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC73" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD73" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,47; textil de 479 px de lado); colores identificables (probabilidad 0,95; 2 colores claramente distintos, 3 tonos, colorido 49); formas visibles (probabilidad 0,94; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,28; compacidad 0,90, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 67.</t>
+          <t>Fotografía regular (nitidez 1,47; textil de 479 px de lado); colores identificables (probabilidad 0,90; 2 colores claramente distintos, 3 tonos, colorido 49); formas visibles (probabilidad 0,86; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,90, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 50.</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="AA74" s="4" t="n">
-        <v>50.9</v>
+        <v>60.7</v>
       </c>
       <c r="AB74" s="4" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="AD74" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,55; textil de 1968 px de lado); colores identificables (probabilidad 0,77; 3 colores claramente distintos, 2 tonos, colorido 55); formas parcialmente visibles (probabilidad 0,68; bordes cromáticos en el 22 % del textil); textil incompleto (probabilidad 0,28; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura no evidente. Puntaje 51.</t>
+          <t>Fotografía buena (nitidez 1,55; textil de 1968 px de lado); colores identificables (probabilidad 0,86; 3 colores claramente distintos, 2 tonos, colorido 55); formas visibles (probabilidad 0,76; bordes cromáticos en el 22 % del textil); textil incompleto (probabilidad 0,35; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura no evidente. Puntaje 61.</t>
         </is>
       </c>
     </row>
@@ -9697,21 +9697,21 @@
         </is>
       </c>
       <c r="AA75" s="4" t="n">
-        <v>70.8</v>
+        <v>56</v>
       </c>
       <c r="AB75" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC75" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD75" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,93; textil de 527 px de lado); colores identificables (probabilidad 0,97; 2 colores claramente distintos, 3 tonos, colorido 27); formas visibles (probabilidad 0,97; bordes cromáticos en el 36 % del textil); textil incompleto (probabilidad 0,39; compacidad 0,92, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 71.</t>
+          <t>Fotografía buena (nitidez 1,93; textil de 527 px de lado); colores identificables (probabilidad 0,93; 2 colores claramente distintos, 3 tonos, colorido 27); formas visibles (probabilidad 0,94; bordes cromáticos en el 36 % del textil); textil incompleto (probabilidad 0,24; compacidad 0,92, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 56.</t>
         </is>
       </c>
     </row>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="AA76" s="4" t="n">
-        <v>62.9</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AB76" s="4" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="AD76" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,26; textil de 1550 px de lado); colores identificables (probabilidad 0,84; 1 color claramente distinto, 1 tono, colorido 33); formas visibles (probabilidad 0,90; bordes cromáticos en el 17 % del textil); completitud incierta (probabilidad 0,66; compacidad 0,92, lagunas 4,8 %, el título dice «fragment»); estructura no evidente. Puntaje 63.</t>
+          <t>Fotografía buena (nitidez 2,26; textil de 1550 px de lado); colores identificables (probabilidad 0,81; 1 color claramente distinto, 1 tono, colorido 33); formas visibles (probabilidad 0,89; bordes cromáticos en el 17 % del textil); completitud incierta (probabilidad 0,59; compacidad 0,92, lagunas 4,8 %, el título dice «fragment»); estructura no evidente. Puntaje 76.</t>
         </is>
       </c>
     </row>
@@ -9901,21 +9901,21 @@
         </is>
       </c>
       <c r="AA77" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="AB77" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC77" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD77" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,69; textil de 1310 px de lado); colores identificables (probabilidad 0,84; 1 color claramente distinto, 3 tonos, colorido 36); formas visibles (probabilidad 0,93; bordes cromáticos en el 32 % del textil); completitud incierta (probabilidad 0,41; compacidad 0,86, lagunas 16,7 %, el título dice «fragment»); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía buena (nitidez 2,69; textil de 1310 px de lado); colores identificables (probabilidad 0,84; 1 color claramente distinto, 3 tonos, colorido 36); formas visibles (probabilidad 0,93; bordes cromáticos en el 32 % del textil); textil incompleto (probabilidad 0,33; compacidad 0,86, lagunas 16,7 %, el título dice «fragment»); estructura no evidente. Puntaje 63.</t>
         </is>
       </c>
     </row>
@@ -10019,21 +10019,21 @@
         </is>
       </c>
       <c r="AA78" s="4" t="n">
-        <v>41.3</v>
+        <v>39.8</v>
       </c>
       <c r="AB78" s="4" t="inlineStr">
         <is>
-          <t>descartar</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD78" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,04; textil de 1531 px de lado); colores parcialmente identificables (probabilidad 0,67; 4 colores claramente distintos, 2 tonos, colorido 46); formas parcialmente visibles (probabilidad 0,55; bordes cromáticos en el 41 % del textil); textil incompleto (probabilidad 0,06; compacidad 0,70, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 41.</t>
+          <t>Fotografía deficiente (nitidez 1,04; textil de 1531 px de lado); colores identificables (probabilidad 0,76; 4 colores claramente distintos, 2 tonos, colorido 46); formas parcialmente visibles (probabilidad 0,68; bordes cromáticos en el 41 % del textil); textil incompleto (probabilidad 0,13; compacidad 0,70, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 40.</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="AA79" s="4" t="n">
-        <v>67.90000000000001</v>
+        <v>36.1</v>
       </c>
       <c r="AB79" s="4" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="AD79" s="4" t="inlineStr">
         <is>
-          <t>El textil mide 283 px de lado en la imagen institucional (mínimo 300). Fotografía deficiente (nitidez 0,95; textil de 283 px de lado); colores identificables (probabilidad 0,95; 2 colores claramente distintos, 4 tonos, colorido 40); formas visibles (probabilidad 0,91; bordes cromáticos en el 52 % del textil); textil incompleto (probabilidad 0,09; compacidad 0,89, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 68.</t>
+          <t>El textil mide 283 px de lado en la imagen institucional (mínimo 300). Fotografía deficiente (nitidez 0,95; textil de 283 px de lado); colores identificables (probabilidad 0,90; 2 colores claramente distintos, 4 tonos, colorido 40); formas visibles (probabilidad 0,80; bordes cromáticos en el 52 % del textil); textil incompleto (probabilidad 0,03; compacidad 0,89, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="AA80" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="AB80" s="4" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
       </c>
       <c r="AD80" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,96; textil de 1229 px de lado); colores identificables (probabilidad 0,93; 4 colores claramente distintos, 1 tono, colorido 73); formas visibles (probabilidad 0,88; bordes cromáticos en el 49 % del textil); completitud incierta (probabilidad 0,66; compacidad 0,88, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía buena (nitidez 1,96; textil de 1229 px de lado); colores identificables (probabilidad 0,94; 4 colores claramente distintos, 1 tono, colorido 73); formas visibles (probabilidad 0,89; bordes cromáticos en el 49 % del textil); textil completo (probabilidad 0,76; compacidad 0,88, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 85.</t>
         </is>
       </c>
     </row>
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="AA81" s="4" t="n">
-        <v>71</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AB81" s="4" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="AD81" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,66; textil de 2744 px de lado); colores identificables (probabilidad 0,95; 2 colores claramente distintos, 2 tonos, colorido 45); formas visibles (probabilidad 0,93; bordes cromáticos en el 23 % del textil); textil completo (probabilidad 0,91; compacidad 0,73, lagunas 0,1 %); estructura no evidente. Puntaje 71.</t>
+          <t>Fotografía buena (nitidez 1,66; textil de 2744 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 2 tonos, colorido 45); formas visibles (probabilidad 0,94; bordes cromáticos en el 23 % del textil); textil completo (probabilidad 0,94; compacidad 0,73, lagunas 0,1 %); estructura no evidente. Puntaje 94 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="AA82" s="4" t="n">
-        <v>64.2</v>
+        <v>86.8</v>
       </c>
       <c r="AB82" s="4" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="AD82" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía regular (nitidez 1,14; textil de 3399 px de lado); colores no identificables (probabilidad 0,87; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,90; bordes cromáticos en el 32 % del textil); completitud incierta (probabilidad 0,64; compacidad 0,96, lagunas 0,1 %); estructura no evidente. Puntaje 64.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía regular (nitidez 1,14; textil de 3399 px de lado); colores no identificables (probabilidad 0,88; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,95; bordes cromáticos en el 32 % del textil); textil completo (probabilidad 0,82; compacidad 0,96, lagunas 0,1 %); estructura no evidente. Puntaje 87.</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="AA83" s="4" t="n">
-        <v>76.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AB83" s="4" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="AD83" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,62; textil de 2572 px de lado); colores no identificables (probabilidad 0,97; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,97; bordes cromáticos en el 56 % del textil); textil completo (probabilidad 0,90; compacidad 0,98, lagunas 0,0 %); estructura no evidente. Puntaje 76.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,62; textil de 2572 px de lado); colores no identificables (probabilidad 0,97; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,98; bordes cromáticos en el 56 % del textil); textil completo (probabilidad 0,94; compacidad 0,98, lagunas 0,0 %); estructura no evidente. Puntaje 95.</t>
         </is>
       </c>
     </row>
@@ -10683,17 +10683,17 @@
       </c>
       <c r="AB84" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD84" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,23; textil de 1038 px de lado); colores identificables (probabilidad 0,92; 6 colores claramente distintos, 3 tonos, colorido 71); formas visibles (probabilidad 0,78; bordes cromáticos en el 45 % del textil); textil incompleto (probabilidad 0,15; compacidad 0,82, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 61.</t>
+          <t>Fotografía regular (nitidez 1,23; textil de 1038 px de lado); colores identificables (probabilidad 0,95; 6 colores claramente distintos, 3 tonos, colorido 71); formas visibles (probabilidad 0,88; bordes cromáticos en el 45 % del textil); textil incompleto (probabilidad 0,35; compacidad 0,82, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 61.</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="AA85" s="4" t="n">
-        <v>82.7</v>
+        <v>90.3</v>
       </c>
       <c r="AB85" s="4" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="AD85" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,48; textil de 829 px de lado); colores identificables (probabilidad 0,99; 3 colores claramente distintos, 2 tonos, colorido 41); formas visibles (probabilidad 0,98; bordes cromáticos en el 34 % del textil); textil completo (probabilidad 0,91; compacidad 0,86, lagunas 0,0 %, el título dice «fragment»); estructura simétrica. Puntaje 83 (imagen de referencia sugerida).</t>
+          <t>Fotografía regular (nitidez 1,48; textil de 829 px de lado); colores identificables (probabilidad 0,99; 3 colores claramente distintos, 2 tonos, colorido 41); formas visibles (probabilidad 0,96; bordes cromáticos en el 34 % del textil); textil completo (probabilidad 0,88; compacidad 0,86, lagunas 0,0 %, el título dice «fragment»); estructura simétrica. Puntaje 90 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
         </is>
       </c>
       <c r="AA86" s="4" t="n">
-        <v>66.8</v>
+        <v>73.2</v>
       </c>
       <c r="AB86" s="4" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="AD86" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,58; textil de 1481 px de lado); colores identificables (probabilidad 0,90; 2 colores claramente distintos, 2 tonos, colorido 37); formas visibles (probabilidad 0,91; bordes cromáticos en el 48 % del textil); completitud incierta (probabilidad 0,52; compacidad 0,89, lagunas 0,7 %, el título dice «fragment»); estructura no evidente. Puntaje 67.</t>
+          <t>Fotografía buena (nitidez 1,58; textil de 1481 px de lado); colores identificables (probabilidad 0,91; 2 colores claramente distintos, 2 tonos, colorido 37); formas visibles (probabilidad 0,93; bordes cromáticos en el 48 % del textil); completitud incierta (probabilidad 0,54; compacidad 0,89, lagunas 0,7 %, el título dice «fragment»); estructura no evidente. Puntaje 73.</t>
         </is>
       </c>
     </row>
@@ -10985,21 +10985,21 @@
         </is>
       </c>
       <c r="AA87" s="4" t="n">
-        <v>62.4</v>
+        <v>63.6</v>
       </c>
       <c r="AB87" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC87" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD87" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,40; textil de 1498 px de lado); colores identificables (probabilidad 0,83; 1 color claramente distinto, 3 tonos, colorido 34); formas visibles (probabilidad 0,89; bordes cromáticos en el 31 % del textil); completitud incierta (probabilidad 0,42; compacidad 0,81, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 62.</t>
+          <t>Fotografía regular (nitidez 1,40; textil de 1498 px de lado); colores identificables (probabilidad 0,86; 1 color claramente distinto, 3 tonos, colorido 34); formas visibles (probabilidad 0,91; bordes cromáticos en el 31 % del textil); textil incompleto (probabilidad 0,36; compacidad 0,81, lagunas 0,8 %, el título dice «fragment»); estructura no evidente. Puntaje 64.</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="AA88" s="4" t="n">
-        <v>75.3</v>
+        <v>91.3</v>
       </c>
       <c r="AB88" s="4" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AD88" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,64; textil de 1136 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 3 tonos, colorido 43); formas visibles (probabilidad 0,95; bordes cromáticos en el 33 % del textil); textil completo (probabilidad 0,85; compacidad 0,86, lagunas 0,1 %); estructura no evidente. Puntaje 75.</t>
+          <t>Fotografía buena (nitidez 1,64; textil de 1136 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 3 tonos, colorido 43); formas visibles (probabilidad 0,96; bordes cromáticos en el 33 % del textil); textil completo (probabilidad 0,88; compacidad 0,86, lagunas 0,1 %); estructura no evidente. Puntaje 91 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="AA89" s="4" t="n">
-        <v>68.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="AB89" s="4" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
       </c>
       <c r="AD89" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,70; textil de 1125 px de lado); colores identificables (probabilidad 0,88; 1 color claramente distinto, 2 tonos, colorido 35); formas visibles (probabilidad 0,88; bordes cromáticos en el 31 % del textil); textil completo (probabilidad 0,71; compacidad 0,72, lagunas 0,5 %); estructura no evidente. Puntaje 68.</t>
+          <t>Fotografía buena (nitidez 1,70; textil de 1125 px de lado); colores identificables (probabilidad 0,84; 1 color claramente distinto, 2 tonos, colorido 35); formas visibles (probabilidad 0,84; bordes cromáticos en el 31 % del textil); completitud incierta (probabilidad 0,69; compacidad 0,72, lagunas 0,5 %); estructura no evidente. Puntaje 79.</t>
         </is>
       </c>
     </row>
@@ -11291,21 +11291,21 @@
         </is>
       </c>
       <c r="AA90" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="AB90" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD90" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,48; textil de 856 px de lado); colores identificables (probabilidad 0,94; 6 colores claramente distintos, 4 tonos, colorido 93); formas visibles (probabilidad 0,80; bordes cromáticos en el 54 % del textil); textil incompleto (probabilidad 0,14; compacidad 0,65, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 66.</t>
+          <t>Fotografía regular (nitidez 1,48; textil de 856 px de lado); colores identificables (probabilidad 0,95; 6 colores claramente distintos, 4 tonos, colorido 93); formas visibles (probabilidad 0,84; bordes cromáticos en el 54 % del textil); textil incompleto (probabilidad 0,24; compacidad 0,65, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 54.</t>
         </is>
       </c>
     </row>
@@ -11393,21 +11393,21 @@
         </is>
       </c>
       <c r="AA91" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>46</v>
       </c>
       <c r="AB91" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC91" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD91" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,22; textil de 914 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 4 tonos, colorido 89); formas visibles (probabilidad 0,92; bordes cromáticos en el 53 % del textil); textil incompleto (probabilidad 0,12; compacidad 0,73, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía regular (nitidez 1,22; textil de 914 px de lado); colores identificables (probabilidad 0,98; 5 colores claramente distintos, 4 tonos, colorido 89); formas visibles (probabilidad 0,93; bordes cromáticos en el 53 % del textil); textil incompleto (probabilidad 0,13; compacidad 0,73, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 46.</t>
         </is>
       </c>
     </row>
@@ -11495,21 +11495,21 @@
         </is>
       </c>
       <c r="AA92" s="4" t="n">
-        <v>81</v>
+        <v>47.5</v>
       </c>
       <c r="AB92" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD92" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,83; textil de 531 px de lado); colores identificables (probabilidad 0,94; 2 colores claramente distintos, 3 tonos, colorido 37); formas visibles (probabilidad 0,92; bordes cromáticos en el 54 % del textil); textil incompleto (probabilidad 0,36; compacidad 0,62, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva y simétrica. Puntaje 81 (imagen de referencia sugerida).</t>
+          <t>Fotografía deficiente (nitidez 0,83; textil de 531 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 3 tonos, colorido 37); formas visibles (probabilidad 0,93; bordes cromáticos en el 54 % del textil); textil incompleto (probabilidad 0,18; compacidad 0,62, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva y simétrica. Puntaje 48.</t>
         </is>
       </c>
     </row>
@@ -11597,21 +11597,21 @@
         </is>
       </c>
       <c r="AA93" s="4" t="n">
-        <v>81</v>
+        <v>47.5</v>
       </c>
       <c r="AB93" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC93" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD93" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,83; textil de 531 px de lado); colores identificables (probabilidad 0,94; 2 colores claramente distintos, 3 tonos, colorido 37); formas visibles (probabilidad 0,92; bordes cromáticos en el 54 % del textil); textil incompleto (probabilidad 0,36; compacidad 0,62, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva y simétrica. Puntaje 81 (imagen de referencia sugerida).</t>
+          <t>Fotografía deficiente (nitidez 0,83; textil de 531 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 3 tonos, colorido 37); formas visibles (probabilidad 0,93; bordes cromáticos en el 54 % del textil); textil incompleto (probabilidad 0,18; compacidad 0,62, lagunas 0,0 %, el título dice «fragment»); estructura repetitiva y simétrica. Puntaje 48.</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="AA94" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AB94" s="4" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
       </c>
       <c r="AD94" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,46; textil de 1096 px de lado); colores identificables (probabilidad 0,96; 3 colores claramente distintos, 3 tonos, colorido 47); formas visibles (probabilidad 0,93; bordes cromáticos en el 45 % del textil); completitud incierta (probabilidad 0,50; compacidad 0,84, lagunas 1,4 %); estructura no evidente. Puntaje 70.</t>
+          <t>Fotografía regular (nitidez 1,46; textil de 1096 px de lado); colores identificables (probabilidad 0,94; 3 colores claramente distintos, 3 tonos, colorido 47); formas visibles (probabilidad 0,91; bordes cromáticos en el 45 % del textil); completitud incierta (probabilidad 0,63; compacidad 0,84, lagunas 1,4 %); estructura no evidente. Puntaje 74.</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="AA95" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AB95" s="4" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="AD95" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,63; textil de 1222 px de lado); colores identificables (probabilidad 0,92; 2 colores claramente distintos, 3 tonos, colorido 27); formas visibles (probabilidad 0,93; bordes cromáticos en el 18 % del textil); textil completo (probabilidad 0,73; compacidad 0,80, lagunas 1,3 %); estructura no evidente. Puntaje 71.</t>
+          <t>Fotografía buena (nitidez 1,63; textil de 1222 px de lado); colores identificables (probabilidad 0,92; 2 colores claramente distintos, 3 tonos, colorido 27); formas visibles (probabilidad 0,94; bordes cromáticos en el 18 % del textil); textil completo (probabilidad 0,80; compacidad 0,80, lagunas 1,3 %); estructura no evidente. Puntaje 87 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="AA96" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="AB96" s="4" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="AD96" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,95; textil de 947 px de lado); colores identificables (probabilidad 0,96; 1 color claramente distinto, 2 tonos, colorido 47); formas visibles (probabilidad 0,95; bordes cromáticos en el 33 % del textil); textil completo (probabilidad 0,91; compacidad 0,88, lagunas 0,2 %); estructura no evidente. Puntaje 75.</t>
+          <t>Fotografía buena (nitidez 1,95; textil de 947 px de lado); colores identificables (probabilidad 0,94; 1 color claramente distinto, 2 tonos, colorido 47); formas visibles (probabilidad 0,92; bordes cromáticos en el 33 % del textil); textil completo (probabilidad 0,89; compacidad 0,88, lagunas 0,2 %); estructura no evidente. Puntaje 91 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -12005,21 +12005,21 @@
         </is>
       </c>
       <c r="AA97" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>46</v>
       </c>
       <c r="AB97" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC97" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD97" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,22; textil de 914 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 4 tonos, colorido 89); formas visibles (probabilidad 0,92; bordes cromáticos en el 53 % del textil); textil incompleto (probabilidad 0,12; compacidad 0,73, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía regular (nitidez 1,22; textil de 914 px de lado); colores identificables (probabilidad 0,98; 5 colores claramente distintos, 4 tonos, colorido 89); formas visibles (probabilidad 0,93; bordes cromáticos en el 53 % del textil); textil incompleto (probabilidad 0,13; compacidad 0,73, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 46.</t>
         </is>
       </c>
     </row>
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="AA98" s="4" t="n">
-        <v>65.2</v>
+        <v>72.2</v>
       </c>
       <c r="AB98" s="4" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="AD98" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,51; textil de 1043 px de lado); colores identificables (probabilidad 0,84; 1 color claramente distinto, 2 tonos, colorido 34); formas visibles (probabilidad 0,81; bordes cromáticos en el 25 % del textil); completitud incierta (probabilidad 0,66; compacidad 0,57, lagunas 0,3 %); estructura no evidente. Puntaje 65.</t>
+          <t>Fotografía regular (nitidez 1,51; textil de 1043 px de lado); colores identificables (probabilidad 0,78; 1 color claramente distinto, 2 tonos, colorido 34); formas visibles (probabilidad 0,76; bordes cromáticos en el 25 % del textil); completitud incierta (probabilidad 0,63; compacidad 0,57, lagunas 0,3 %); estructura no evidente. Puntaje 72.</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="AA99" s="4" t="n">
-        <v>73.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="AB99" s="4" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
       </c>
       <c r="AD99" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,71; textil de 1182 px de lado); colores identificables (probabilidad 0,95; 2 colores claramente distintos, 2 tonos, colorido 48); formas visibles (probabilidad 0,93; bordes cromáticos en el 45 % del textil); textil completo (probabilidad 0,80; compacidad 0,85, lagunas 0,1 %); estructura no evidente. Puntaje 74.</t>
+          <t>Fotografía buena (nitidez 1,71; textil de 1182 px de lado); colores identificables (probabilidad 0,94; 2 colores claramente distintos, 2 tonos, colorido 48); formas visibles (probabilidad 0,93; bordes cromáticos en el 45 % del textil); textil completo (probabilidad 0,83; compacidad 0,85, lagunas 0,1 %); estructura no evidente. Puntaje 88 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         </is>
       </c>
       <c r="AA100" s="4" t="n">
-        <v>77.7</v>
+        <v>90.7</v>
       </c>
       <c r="AB100" s="4" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="AD100" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,13; textil de 1016 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 2 tonos, colorido 41); formas visibles (probabilidad 0,93; bordes cromáticos en el 38 % del textil); textil completo (probabilidad 0,88; compacidad 0,75, lagunas 1,2 %); estructura no evidente. Puntaje 78 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 2,13; textil de 1016 px de lado); colores identificables (probabilidad 0,94; 2 colores claramente distintos, 2 tonos, colorido 41); formas visibles (probabilidad 0,91; bordes cromáticos en el 38 % del textil); textil completo (probabilidad 0,88; compacidad 0,75, lagunas 1,2 %); estructura no evidente. Puntaje 91 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="AA101" s="4" t="n">
-        <v>72.8</v>
+        <v>86.2</v>
       </c>
       <c r="AB101" s="4" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="AD101" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,82; textil de 1012 px de lado); colores identificables (probabilidad 0,93; 1 color claramente distinto, 2 tonos, colorido 35); formas visibles (probabilidad 0,93; bordes cromáticos en el 32 % del textil); textil completo (probabilidad 0,84; compacidad 0,81, lagunas 0,5 %); estructura no evidente. Puntaje 73.</t>
+          <t>Fotografía buena (nitidez 1,82; textil de 1012 px de lado); colores identificables (probabilidad 0,90; 1 color claramente distinto, 2 tonos, colorido 35); formas visibles (probabilidad 0,89; bordes cromáticos en el 32 % del textil); textil completo (probabilidad 0,81; compacidad 0,81, lagunas 0,5 %); estructura no evidente. Puntaje 86 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12515,7 @@
         </is>
       </c>
       <c r="AA102" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="AB102" s="4" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="AD102" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,97; textil de 1173 px de lado); colores identificables (probabilidad 0,94; 1 color claramente distinto, 2 tonos, colorido 38); formas visibles (probabilidad 0,93; bordes cromáticos en el 37 % del textil); textil completo (probabilidad 0,87; compacidad 0,79, lagunas 0,9 %); estructura no evidente. Puntaje 74.</t>
+          <t>Fotografía buena (nitidez 1,97; textil de 1173 px de lado); colores identificables (probabilidad 0,92; 1 color claramente distinto, 2 tonos, colorido 38); formas visibles (probabilidad 0,91; bordes cromáticos en el 37 % del textil); textil completo (probabilidad 0,86; compacidad 0,79, lagunas 0,9 %); estructura no evidente. Puntaje 89 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -12617,7 +12617,7 @@
         </is>
       </c>
       <c r="AA103" s="4" t="n">
-        <v>79.7</v>
+        <v>72</v>
       </c>
       <c r="AB103" s="4" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="AD103" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,43; textil de 982 px de lado); colores identificables (probabilidad 0,85; 3 colores claramente distintos, 2 tonos, colorido 45); formas visibles (probabilidad 0,83; bordes cromáticos en el 42 % del textil); completitud incierta (probabilidad 0,45; compacidad 0,59, lagunas 21,4 %); estructura no evidente. Puntaje 80 (imagen de referencia sugerida).</t>
+          <t>Fotografía regular (nitidez 1,43; textil de 982 px de lado); colores identificables (probabilidad 0,87; 3 colores claramente distintos, 2 tonos, colorido 45); formas visibles (probabilidad 0,83; bordes cromáticos en el 42 % del textil); completitud incierta (probabilidad 0,63; compacidad 0,59, lagunas 21,4 %); estructura no evidente. Puntaje 72.</t>
         </is>
       </c>
     </row>
@@ -12719,7 +12719,7 @@
         </is>
       </c>
       <c r="AA104" s="4" t="n">
-        <v>85.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB104" s="4" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="AD104" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,16; textil de 966 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 2 tonos, colorido 82); formas visibles (probabilidad 0,98; bordes cromáticos en el 71 % del textil); textil completo (probabilidad 0,95; compacidad 0,82, lagunas 0,0 %); estructura repetitiva. Puntaje 85 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 2,16; textil de 966 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 2 tonos, colorido 82); formas visibles (probabilidad 0,98; bordes cromáticos en el 71 % del textil); textil completo (probabilidad 0,97; compacidad 0,82, lagunas 0,0 %); estructura repetitiva. Puntaje 97 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -12821,21 +12821,21 @@
         </is>
       </c>
       <c r="AA105" s="4" t="n">
-        <v>48</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="AB105" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC105" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD105" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 0,91; textil de 2761 px de lado); colores parcialmente identificables (probabilidad 0,68; 3 colores claramente distintos, 3 tonos, colorido 86); formas parcialmente visibles (probabilidad 0,61; bordes cromáticos en el 15 % del textil); completitud incierta (probabilidad 0,53; compacidad 0,76, lagunas 0,0 %); estructura no evidente. Puntaje 48.</t>
+          <t>Fotografía regular (nitidez 0,91; textil de 2761 px de lado); colores identificables (probabilidad 0,86; 3 colores claramente distintos, 3 tonos, colorido 86); formas visibles (probabilidad 0,81; bordes cromáticos en el 15 % del textil); textil completo (probabilidad 0,82; compacidad 0,76, lagunas 0,0 %); estructura no evidente. Puntaje 84.</t>
         </is>
       </c>
     </row>
@@ -12923,21 +12923,21 @@
         </is>
       </c>
       <c r="AA106" s="4" t="n">
-        <v>79.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="AB106" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD106" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,88; textil de 473 px de lado); colores identificables (probabilidad 0,89; 4 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,84; bordes cromáticos en el 19 % del textil); textil incompleto (probabilidad 0,31; compacidad 0,69, lagunas 11,8 %); estructura repetitiva. Puntaje 79 (imagen de referencia sugerida).</t>
+          <t>Fotografía deficiente (nitidez 0,88; textil de 473 px de lado); colores identificables (probabilidad 0,87; 4 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,83; bordes cromáticos en el 19 % del textil); completitud incierta (probabilidad 0,46; compacidad 0,69, lagunas 11,8 %); estructura repetitiva. Puntaje 61.</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="AA107" s="4" t="n">
-        <v>77.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="AB107" s="4" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="AD107" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,31; textil de 893 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 2 tonos, colorido 38); formas visibles (probabilidad 0,91; bordes cromáticos en el 53 % del textil); textil completo (probabilidad 0,71; compacidad 0,57, lagunas 0,1 %); estructura repetitiva. Puntaje 78 (imagen de referencia sugerida).</t>
+          <t>Fotografía regular (nitidez 1,31; textil de 893 px de lado); colores identificables (probabilidad 0,95; 2 colores claramente distintos, 2 tonos, colorido 38); formas visibles (probabilidad 0,87; bordes cromáticos en el 53 % del textil); completitud incierta (probabilidad 0,66; compacidad 0,57, lagunas 0,1 %); estructura repetitiva. Puntaje 75.</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="AA108" s="4" t="n">
-        <v>42</v>
+        <v>46.1</v>
       </c>
       <c r="AB108" s="4" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="AD108" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,59; textil de 1607 px de lado); colores no identificables (probabilidad 0,48; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,62; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,79, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 42.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,59; textil de 1607 px de lado); colores no identificables (probabilidad 0,46; 2 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,71; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,79, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 46.</t>
         </is>
       </c>
     </row>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="AA109" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="AB109" s="4" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="AD109" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,48; textil de 1540 px de lado); colores identificables (probabilidad 0,92; 1 color claramente distinto, 2 tonos, colorido 39); formas visibles (probabilidad 0,93; bordes cromáticos en el 31 % del textil); textil completo (probabilidad 0,82; compacidad 0,93, lagunas 0,0 %); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía buena (nitidez 1,48; textil de 1540 px de lado); colores identificables (probabilidad 0,91; 1 color claramente distinto, 2 tonos, colorido 39); formas visibles (probabilidad 0,93; bordes cromáticos en el 31 % del textil); textil completo (probabilidad 0,85; compacidad 0,93, lagunas 0,0 %); estructura no evidente. Puntaje 89 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -13347,7 +13347,7 @@
         </is>
       </c>
       <c r="AA110" s="4" t="n">
-        <v>68.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AB110" s="4" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="AD110" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,60; textil de 2204 px de lado); colores identificables (probabilidad 0,93; 3 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,94; bordes cromáticos en el 32 % del textil); completitud incierta (probabilidad 0,59; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 68.</t>
+          <t>Fotografía buena (nitidez 1,60; textil de 2204 px de lado); colores identificables (probabilidad 0,96; 3 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,97; bordes cromáticos en el 32 % del textil); completitud incierta (probabilidad 0,70; compacidad 0,93, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 83.</t>
         </is>
       </c>
     </row>
@@ -13449,7 +13449,7 @@
         </is>
       </c>
       <c r="AA111" s="4" t="n">
-        <v>77</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AB111" s="4" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="AD111" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,83; textil de 967 px de lado); colores identificables (probabilidad 0,93; 2 colores claramente distintos, 2 tonos, colorido 38); formas visibles (probabilidad 0,92; bordes cromáticos en el 28 % del textil); textil completo (probabilidad 0,78; compacidad 0,78, lagunas 6,6 %); estructura no evidente. Puntaje 77.</t>
+          <t>Fotografía buena (nitidez 1,83; textil de 967 px de lado); colores identificables (probabilidad 0,91; 2 colores claramente distintos, 2 tonos, colorido 38); formas visibles (probabilidad 0,90; bordes cromáticos en el 28 % del textil); textil completo (probabilidad 0,83; compacidad 0,78, lagunas 6,6 %); estructura no evidente. Puntaje 87 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -13551,7 +13551,7 @@
         </is>
       </c>
       <c r="AA112" s="4" t="n">
-        <v>73.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AB112" s="4" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="AD112" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,34; textil de 1577 px de lado); colores identificables (probabilidad 0,98; 5 colores claramente distintos, 4 tonos, colorido 87); formas visibles (probabilidad 0,96; bordes cromáticos en el 43 % del textil); completitud incierta (probabilidad 0,51; compacidad 0,92, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 73.</t>
+          <t>Fotografía regular (nitidez 1,34; textil de 1577 px de lado); colores identificables (probabilidad 0,99; 5 colores claramente distintos, 4 tonos, colorido 87); formas visibles (probabilidad 0,98; bordes cromáticos en el 43 % del textil); textil completo (probabilidad 0,71; compacidad 0,92, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 82.</t>
         </is>
       </c>
     </row>
@@ -13653,7 +13653,7 @@
         </is>
       </c>
       <c r="AA113" s="4" t="n">
-        <v>72.2</v>
+        <v>92.8</v>
       </c>
       <c r="AB113" s="4" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
       </c>
       <c r="AD113" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,29; textil de 1380 px de lado); colores identificables (probabilidad 0,94; 4 colores claramente distintos, 2 tonos, colorido 90); formas visibles (probabilidad 0,85; bordes cromáticos en el 38 % del textil); textil completo (probabilidad 0,81; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 72.</t>
+          <t>Fotografía regular (nitidez 1,29; textil de 1380 px de lado); colores identificables (probabilidad 0,97; 4 colores claramente distintos, 2 tonos, colorido 90); formas visibles (probabilidad 0,90; bordes cromáticos en el 38 % del textil); textil completo (probabilidad 0,94; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 93 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="AA114" s="4" t="n">
-        <v>70.8</v>
+        <v>96.5</v>
       </c>
       <c r="AB114" s="4" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="AD114" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,53; textil de 3480 px de lado); colores identificables (probabilidad 0,95; 2 colores claramente distintos, 2 tonos, colorido 51); formas visibles (probabilidad 0,95; bordes cromáticos en el 43 % del textil); textil completo (probabilidad 0,92; compacidad 0,97, lagunas 0,0 %); estructura repetitiva. Puntaje 71.</t>
+          <t>Fotografía buena (nitidez 1,53; textil de 3480 px de lado); colores identificables (probabilidad 0,97; 2 colores claramente distintos, 2 tonos, colorido 51); formas visibles (probabilidad 0,98; bordes cromáticos en el 43 % del textil); textil completo (probabilidad 0,96; compacidad 0,97, lagunas 0,0 %); estructura repetitiva. Puntaje 97 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13857,7 @@
         </is>
       </c>
       <c r="AA115" s="4" t="n">
-        <v>69.3</v>
+        <v>95.8</v>
       </c>
       <c r="AB115" s="4" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="AD115" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,03; textil de 2681 px de lado); colores identificables (probabilidad 0,94; 1 color claramente distinto, 1 tono, colorido 30); formas visibles (probabilidad 0,95; bordes cromáticos en el 6 % del textil); textil completo (probabilidad 0,97; compacidad 0,94, lagunas 0,0 %); estructura simétrica. Puntaje 69.</t>
+          <t>Fotografía buena (nitidez 2,03; textil de 2681 px de lado); colores identificables (probabilidad 0,93; 1 color claramente distinto, 1 tono, colorido 30); formas visibles (probabilidad 0,95; bordes cromáticos en el 6 % del textil); textil completo (probabilidad 0,97; compacidad 0,94, lagunas 0,0 %); estructura simétrica. Puntaje 96 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="AA116" s="4" t="n">
-        <v>49.6</v>
+        <v>31.3</v>
       </c>
       <c r="AB116" s="4" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
       </c>
       <c r="AD116" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 2,6): el color no es identificable. Fotografía regular (nitidez 1,55; textil de 1135 px de lado); colores no identificables (probabilidad 0,33; 2 colores claramente distintos, 0 tonos, colorido 3); formas parcialmente visibles (probabilidad 0,59; bordes cromáticos en el 50 % del textil); textil incompleto (probabilidad 0,07; compacidad 0,72, lagunas 26,3 %); estructura no evidente. Puntaje 50.</t>
+          <t>Fotografía en blanco y negro (croma 2,6): el color no es identificable. Fotografía regular (nitidez 1,55; textil de 1135 px de lado); colores no identificables (probabilidad 0,31; 2 colores claramente distintos, 0 tonos, colorido 3); formas parcialmente visibles (probabilidad 0,58; bordes cromáticos en el 50 % del textil); textil incompleto (probabilidad 0,13; compacidad 0,72, lagunas 26,3 %); estructura no evidente. Puntaje 31.</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="AA117" s="4" t="n">
-        <v>54.7</v>
+        <v>55.5</v>
       </c>
       <c r="AB117" s="4" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="AD117" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,38; textil de 1228 px de lado); colores identificables (probabilidad 0,73; 2 colores claramente distintos, 2 tonos, colorido 42); formas visibles (probabilidad 0,74; bordes cromáticos en el 39 % del textil); textil incompleto (probabilidad 0,30; compacidad 0,71, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 55.</t>
+          <t>Fotografía regular (nitidez 1,38; textil de 1228 px de lado); colores identificables (probabilidad 0,77; 2 colores claramente distintos, 2 tonos, colorido 42); formas visibles (probabilidad 0,79; bordes cromáticos en el 39 % del textil); textil incompleto (probabilidad 0,28; compacidad 0,71, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 55.</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
         </is>
       </c>
       <c r="AA118" s="4" t="n">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="AB118" s="4" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="AD118" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía regular (nitidez 1,50; textil de 2509 px de lado); colores no identificables (probabilidad 0,45; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,53; bordes cromáticos en el 27 % del textil); textil incompleto (probabilidad 0,08; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura no evidente. Puntaje 34.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía regular (nitidez 1,50; textil de 2509 px de lado); colores no identificables (probabilidad 0,49; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,64; bordes cromáticos en el 27 % del textil); textil incompleto (probabilidad 0,11; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="AA119" s="4" t="n">
-        <v>40.1</v>
+        <v>37.6</v>
       </c>
       <c r="AB119" s="4" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="AD119" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía regular (nitidez 1,07; textil de 2454 px de lado); colores no identificables (probabilidad 0,57; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,59; bordes cromáticos en el 31 % del textil); textil incompleto (probabilidad 0,08; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura repetitiva. Puntaje 40.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía regular (nitidez 1,07; textil de 2454 px de lado); colores no identificables (probabilidad 0,60; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,70; bordes cromáticos en el 31 % del textil); textil incompleto (probabilidad 0,10; toma cerrada, el contorno de la pieza no se ve, el título dice «fragment»); estructura repetitiva. Puntaje 38.</t>
         </is>
       </c>
     </row>
@@ -14431,7 +14431,7 @@
         </is>
       </c>
       <c r="AA120" s="4" t="n">
-        <v>51.6</v>
+        <v>32</v>
       </c>
       <c r="AB120" s="4" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
       </c>
       <c r="AD120" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 3,3): el color no es identificable. Fotografía buena (nitidez 2,24; textil de 650 px de lado); colores no identificables (probabilidad 0,66; 2 colores claramente distintos, 0 tonos, colorido 4); formas visibles (probabilidad 0,74; bordes cromáticos en el 37 % del textil); textil incompleto (probabilidad 0,11; compacidad 0,76, lagunas 2,5 %, el título dice «fragment»); estructura repetitiva. Puntaje 52.</t>
+          <t>Fotografía en blanco y negro (croma 3,3): el color no es identificable. Fotografía buena (nitidez 2,24; textil de 650 px de lado); colores no identificables (probabilidad 0,40; 2 colores claramente distintos, 0 tonos, colorido 4); formas parcialmente visibles (probabilidad 0,59; bordes cromáticos en el 37 % del textil); textil incompleto (probabilidad 0,07; compacidad 0,76, lagunas 2,5 %, el título dice «fragment»); estructura repetitiva. Puntaje 32.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
         </is>
       </c>
       <c r="AA121" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AB121" s="4" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="AD121" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,16; textil de 1388 px de lado); colores no identificables (probabilidad 0,98; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,96; bordes cromáticos en el 58 % del textil); textil completo (probabilidad 0,78; compacidad 0,78, lagunas 1,4 %); estructura repetitiva y simétrica. Puntaje 75.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,16; textil de 1388 px de lado); colores no identificables (probabilidad 0,96; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,96; bordes cromáticos en el 58 % del textil); textil completo (probabilidad 0,80; compacidad 0,78, lagunas 1,4 %); estructura repetitiva y simétrica. Puntaje 86.</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="AA122" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="AB122" s="4" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="AD122" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,70; textil de 1376 px de lado); colores identificables (probabilidad 0,96; 4 colores claramente distintos, 3 tonos, colorido 54); formas visibles (probabilidad 0,92; bordes cromáticos en el 41 % del textil); completitud incierta (probabilidad 0,45; compacidad 0,81, lagunas 0,7 %); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía buena (nitidez 1,70; textil de 1376 px de lado); colores identificables (probabilidad 0,95; 4 colores claramente distintos, 3 tonos, colorido 54); formas visibles (probabilidad 0,93; bordes cromáticos en el 41 % del textil); completitud incierta (probabilidad 0,65; compacidad 0,81, lagunas 0,7 %); estructura no evidente. Puntaje 78.</t>
         </is>
       </c>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="AA123" s="4" t="n">
-        <v>72.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="AB123" s="4" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="AD123" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,13; textil de 2316 px de lado); colores identificables (probabilidad 0,77; 3 colores claramente distintos, 2 tonos, colorido 54); formas visibles (probabilidad 0,76; bordes cromáticos en el 66 % del textil); completitud incierta (probabilidad 0,48; compacidad 0,59, lagunas 15,0 %); estructura no evidente. Puntaje 73.</t>
+          <t>Fotografía regular (nitidez 1,13; textil de 2316 px de lado); colores identificables (probabilidad 0,88; 3 colores claramente distintos, 2 tonos, colorido 54); formas visibles (probabilidad 0,89; bordes cromáticos en el 66 % del textil); textil completo (probabilidad 0,75; compacidad 0,59, lagunas 15,0 %); estructura no evidente. Puntaje 81.</t>
         </is>
       </c>
     </row>
@@ -14855,7 +14855,7 @@
         </is>
       </c>
       <c r="AA124" s="4" t="n">
-        <v>91.3</v>
+        <v>93.3</v>
       </c>
       <c r="AB124" s="4" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
       </c>
       <c r="AD124" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,42; textil de 1478 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 3 tonos, colorido 66); formas visibles (probabilidad 0,98; bordes cromáticos en el 53 % del textil); textil completo (probabilidad 0,89; compacidad 0,85, lagunas 12,6 %); estructura repetitiva y simétrica. Puntaje 91 (imagen de referencia sugerida).</t>
+          <t>Fotografía regular (nitidez 1,42; textil de 1478 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 3 tonos, colorido 66); formas visibles (probabilidad 0,98; bordes cromáticos en el 53 % del textil); textil completo (probabilidad 0,92; compacidad 0,85, lagunas 12,6 %); estructura repetitiva y simétrica. Puntaje 93 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -14957,21 +14957,21 @@
         </is>
       </c>
       <c r="AA125" s="4" t="n">
-        <v>79.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="AB125" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC125" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD125" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,63; textil de 1257 px de lado); colores identificables (probabilidad 0,87; 2 colores claramente distintos, 3 tonos, colorido 53); formas visibles (probabilidad 0,88; bordes cromáticos en el 55 % del textil); textil incompleto (probabilidad 0,28; compacidad 0,61, lagunas 26,0 %); estructura repetitiva. Puntaje 79 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 1,63; textil de 1257 px de lado); colores identificables (probabilidad 0,91; 2 colores claramente distintos, 3 tonos, colorido 53); formas visibles (probabilidad 0,91; bordes cromáticos en el 55 % del textil); textil incompleto (probabilidad 0,37; compacidad 0,61, lagunas 26,0 %); estructura repetitiva. Puntaje 60.</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
         </is>
       </c>
       <c r="AA126" s="4" t="n">
-        <v>29.9</v>
+        <v>33.2</v>
       </c>
       <c r="AB126" s="4" t="inlineStr">
         <is>
@@ -15089,7 +15089,7 @@
       </c>
       <c r="AD126" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,99; textil de 1894 px de lado); colores no identificables (probabilidad 0,38; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,46; bordes cromáticos en el 27 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,79, lagunas 1,8 %); estructura no evidente. Puntaje 30.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,99; textil de 1894 px de lado); colores no identificables (probabilidad 0,37; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,52; bordes cromáticos en el 27 % del textil); textil incompleto (probabilidad 0,19; compacidad 0,79, lagunas 1,8 %); estructura no evidente. Puntaje 33.</t>
         </is>
       </c>
     </row>
@@ -15177,7 +15177,7 @@
         </is>
       </c>
       <c r="AA127" s="4" t="n">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="AB127" s="4" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="AD127" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,80; textil de 846 px de lado); colores identificables (probabilidad 0,97; 4 colores claramente distintos, 3 tonos, colorido 54); formas visibles (probabilidad 0,88; bordes cromáticos en el 40 % del textil); completitud incierta (probabilidad 0,44; compacidad 0,83, lagunas 0,0 %); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía deficiente (nitidez 0,80; textil de 846 px de lado); colores identificables (probabilidad 0,96; 4 colores claramente distintos, 3 tonos, colorido 54); formas visibles (probabilidad 0,87; bordes cromáticos en el 40 % del textil); completitud incierta (probabilidad 0,61; compacidad 0,83, lagunas 0,0 %); estructura no evidente. Puntaje 71.</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
         </is>
       </c>
       <c r="AA128" s="4" t="n">
-        <v>74.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="AB128" s="4" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
       </c>
       <c r="AD128" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,14; textil de 865 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 3 tonos, colorido 57); formas visibles (probabilidad 0,89; bordes cromáticos en el 41 % del textil); completitud incierta (probabilidad 0,54; compacidad 0,84, lagunas 0,0 %); estructura no evidente. Puntaje 74.</t>
+          <t>Fotografía deficiente (nitidez 1,14; textil de 865 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 3 tonos, colorido 57); formas visibles (probabilidad 0,92; bordes cromáticos en el 41 % del textil); textil completo (probabilidad 0,77; compacidad 0,84, lagunas 0,0 %); estructura no evidente. Puntaje 83.</t>
         </is>
       </c>
     </row>
@@ -15381,7 +15381,7 @@
         </is>
       </c>
       <c r="AA129" s="4" t="n">
-        <v>93.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AB129" s="4" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="AD129" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,92; textil de 1117 px de lado); colores identificables (probabilidad 1,00; 4 colores claramente distintos, 3 tonos, colorido 57); formas visibles (probabilidad 0,99; bordes cromáticos en el 61 % del textil); textil completo (probabilidad 0,98; compacidad 0,94, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 93 (imagen de referencia sugerida).</t>
+          <t>Fotografía deficiente (nitidez 0,92; textil de 1117 px de lado); colores identificables (probabilidad 1,00; 4 colores claramente distintos, 3 tonos, colorido 57); formas visibles (probabilidad 0,99; bordes cromáticos en el 61 % del textil); textil completo (probabilidad 0,99; compacidad 0,94, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 98 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -15499,21 +15499,21 @@
         </is>
       </c>
       <c r="AA130" s="4" t="n">
-        <v>50.7</v>
+        <v>18.5</v>
       </c>
       <c r="AB130" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>descartar</t>
         </is>
       </c>
       <c r="AC130" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD130" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 3,07; textil de 3294 px de lado); colores identificables (probabilidad 0,79; 3 colores claramente distintos, 0 tonos, colorido 12); formas visibles (probabilidad 0,77; bordes cromáticos en el 65 % del textil); textil incompleto (probabilidad 0,02; compacidad 0,81, lagunas 0,0 %); estructura no evidente. Puntaje 51.</t>
+          <t>Fotografía buena (nitidez 3,07; textil de 3294 px de lado); colores no identificables (probabilidad 0,35; 3 colores claramente distintos, 0 tonos, colorido 12); formas no visibles (probabilidad 0,35; bordes cromáticos en el 65 % del textil); textil incompleto (probabilidad 0,05; compacidad 0,81, lagunas 0,0 %); estructura no evidente. Puntaje 18.</t>
         </is>
       </c>
     </row>
@@ -15617,7 +15617,7 @@
         </is>
       </c>
       <c r="AA131" s="4" t="n">
-        <v>69.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="AB131" s="4" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="AD131" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,52; textil de 2578 px de lado); colores no identificables (probabilidad 0,90; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,89; bordes cromáticos en el 48 % del textil); completitud incierta (probabilidad 0,67; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 69.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,52; textil de 2578 px de lado); colores no identificables (probabilidad 0,87; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,90; bordes cromáticos en el 48 % del textil); textil completo (probabilidad 0,77; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 84.</t>
         </is>
       </c>
     </row>
@@ -15735,7 +15735,7 @@
         </is>
       </c>
       <c r="AA132" s="4" t="n">
-        <v>73.2</v>
+        <v>91.7</v>
       </c>
       <c r="AB132" s="4" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
       </c>
       <c r="AD132" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 3,02; textil de 2086 px de lado); colores no identificables (probabilidad 0,95; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,96; bordes cromáticos en el 60 % del textil); textil completo (probabilidad 0,79; compacidad 0,90, lagunas 0,9 %); estructura no evidente. Puntaje 73.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 3,02; textil de 2086 px de lado); colores no identificables (probabilidad 0,92; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,96; bordes cromáticos en el 60 % del textil); textil completo (probabilidad 0,87; compacidad 0,90, lagunas 0,9 %); estructura no evidente. Puntaje 92.</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
         </is>
       </c>
       <c r="AA133" s="4" t="n">
-        <v>71.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AB133" s="4" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
       </c>
       <c r="AD133" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 3,62; textil de 1965 px de lado); colores no identificables (probabilidad 0,83; 2 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,93; bordes cromáticos en el 42 % del textil); textil completo (probabilidad 0,72; compacidad 0,84, lagunas 15,8 %); estructura no evidente. Puntaje 72.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 3,62; textil de 1965 px de lado); colores no identificables (probabilidad 0,82; 2 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,94; bordes cromáticos en el 42 % del textil); textil completo (probabilidad 0,84; compacidad 0,84, lagunas 15,8 %); estructura no evidente. Puntaje 88.</t>
         </is>
       </c>
     </row>
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="AA134" s="4" t="n">
-        <v>20.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AB134" s="4" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AD134" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,65; textil de 1912 px de lado); colores no identificables (probabilidad 0,24; 3 colores claramente distintos, 3 tonos, colorido 126); formas no visibles (probabilidad 0,27; bordes cromáticos en el 11 % del textil); textil incompleto (probabilidad 0,23; compacidad 0,93, lagunas 0,0 %); estructura no evidente. Puntaje 20.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,65; textil de 1912 px de lado); colores parcialmente identificables (probabilidad 0,62; 3 colores claramente distintos, 3 tonos, colorido 126); formas parcialmente visibles (probabilidad 0,68; bordes cromáticos en el 11 % del textil); completitud incierta (probabilidad 0,64; compacidad 0,93, lagunas 0,0 %); estructura no evidente. Puntaje 70.</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="AA135" s="4" t="n">
-        <v>78.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AB135" s="4" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="AD135" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 0,94; textil de 3152 px de lado); colores identificables (probabilidad 0,99; 4 colores claramente distintos, 5 tonos, colorido 112); formas visibles (probabilidad 0,98; bordes cromáticos en el 33 % del textil); textil completo (probabilidad 0,91; compacidad 0,88, lagunas 0,0 %); estructura simétrica. Puntaje 79.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 0,94; textil de 3152 px de lado); colores identificables (probabilidad 1,00; 4 colores claramente distintos, 5 tonos, colorido 112); formas visibles (probabilidad 0,99; bordes cromáticos en el 33 % del textil); textil completo (probabilidad 0,97; compacidad 0,88, lagunas 0,0 %); estructura simétrica. Puntaje 97.</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="AA136" s="4" t="n">
-        <v>20.8</v>
+        <v>67</v>
       </c>
       <c r="AB136" s="4" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
       </c>
       <c r="AD136" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,72; textil de 1919 px de lado); colores no identificables (probabilidad 0,27; 3 colores claramente distintos, 2 tonos, colorido 112); formas no visibles (probabilidad 0,27; bordes cromáticos en el 12 % del textil); textil incompleto (probabilidad 0,26; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 21.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,72; textil de 1919 px de lado); colores parcialmente identificables (probabilidad 0,58; 3 colores claramente distintos, 2 tonos, colorido 112); formas parcialmente visibles (probabilidad 0,61; bordes cromáticos en el 12 % del textil); completitud incierta (probabilidad 0,62; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 67.</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="AA137" s="4" t="n">
-        <v>13.8</v>
+        <v>61.5</v>
       </c>
       <c r="AB137" s="4" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="AD137" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,66; textil de 1929 px de lado); colores no identificables (probabilidad 0,15; 3 colores claramente distintos, 3 tonos, colorido 126); formas no visibles (probabilidad 0,18; bordes cromáticos en el 11 % del textil); textil incompleto (probabilidad 0,16; compacidad 0,88, lagunas 0,0 %); estructura no evidente. Puntaje 14.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,66; textil de 1929 px de lado); colores parcialmente identificables (probabilidad 0,47; 3 colores claramente distintos, 3 tonos, colorido 126); formas parcialmente visibles (probabilidad 0,59; bordes cromáticos en el 11 % del textil); completitud incierta (probabilidad 0,54; compacidad 0,88, lagunas 0,0 %); estructura no evidente. Puntaje 61.</t>
         </is>
       </c>
     </row>
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="AA138" s="4" t="n">
-        <v>17.1</v>
+        <v>67</v>
       </c>
       <c r="AB138" s="4" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
       </c>
       <c r="AD138" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,69; textil de 2118 px de lado); colores no identificables (probabilidad 0,18; 3 colores claramente distintos, 3 tonos, colorido 123); formas no visibles (probabilidad 0,24; bordes cromáticos en el 12 % del textil); textil incompleto (probabilidad 0,19; compacidad 0,96, lagunas 0,0 %); estructura no evidente. Puntaje 17.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,69; textil de 2118 px de lado); colores parcialmente identificables (probabilidad 0,56; 3 colores claramente distintos, 3 tonos, colorido 123); formas visibles (probabilidad 0,71; bordes cromáticos en el 12 % del textil); completitud incierta (probabilidad 0,58; compacidad 0,96, lagunas 0,0 %); estructura no evidente. Puntaje 67.</t>
         </is>
       </c>
     </row>
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="AA139" s="4" t="n">
-        <v>20.6</v>
+        <v>70.8</v>
       </c>
       <c r="AB139" s="4" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
       </c>
       <c r="AD139" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,65; textil de 1905 px de lado); colores no identificables (probabilidad 0,23; 3 colores claramente distintos, 3 tonos, colorido 123); formas no visibles (probabilidad 0,27; bordes cromáticos en el 10 % del textil); textil incompleto (probabilidad 0,25; compacidad 0,94, lagunas 0,0 %); estructura no evidente. Puntaje 21.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,65; textil de 1905 px de lado); colores parcialmente identificables (probabilidad 0,60; 3 colores claramente distintos, 3 tonos, colorido 123); formas parcialmente visibles (probabilidad 0,70; bordes cromáticos en el 10 % del textil); completitud incierta (probabilidad 0,66; compacidad 0,94, lagunas 0,0 %); estructura no evidente. Puntaje 71.</t>
         </is>
       </c>
     </row>
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="AA140" s="4" t="n">
-        <v>34.5</v>
+        <v>81.7</v>
       </c>
       <c r="AB140" s="4" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
       </c>
       <c r="AD140" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,72; textil de 1916 px de lado); colores parcialmente identificables (probabilidad 0,46; 3 colores claramente distintos, 3 tonos, colorido 136); formas parcialmente visibles (probabilidad 0,44; bordes cromáticos en el 10 % del textil); completitud incierta (probabilidad 0,43; compacidad 0,94, lagunas 0,0 %); estructura no evidente. Puntaje 35.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,72; textil de 1916 px de lado); colores identificables (probabilidad 0,79; 3 colores claramente distintos, 3 tonos, colorido 136); formas visibles (probabilidad 0,78; bordes cromáticos en el 10 % del textil); textil completo (probabilidad 0,81; compacidad 0,94, lagunas 0,0 %); estructura no evidente. Puntaje 82.</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="AA141" s="4" t="n">
-        <v>9.9</v>
+        <v>60.4</v>
       </c>
       <c r="AB141" s="4" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="AD141" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,76; textil de 2103 px de lado); colores no identificables (probabilidad 0,08; 3 colores claramente distintos, 2 tonos, colorido 120); formas no visibles (probabilidad 0,14; bordes cromáticos en el 12 % del textil); textil incompleto (probabilidad 0,16; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 10.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,76; textil de 2103 px de lado); colores no identificables (probabilidad 0,34; 3 colores claramente distintos, 2 tonos, colorido 120); formas parcialmente visibles (probabilidad 0,57; bordes cromáticos en el 12 % del textil); completitud incierta (probabilidad 0,56; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 60.</t>
         </is>
       </c>
     </row>
@@ -17203,7 +17203,7 @@
         </is>
       </c>
       <c r="AA142" s="4" t="n">
-        <v>23.4</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AB142" s="4" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="AD142" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,82; textil de 2105 px de lado); colores no identificables (probabilidad 0,25; 3 colores claramente distintos, 3 tonos, colorido 112); formas no visibles (probabilidad 0,33; bordes cromáticos en el 14 % del textil); textil incompleto (probabilidad 0,30; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 23.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,82; textil de 2105 px de lado); colores parcialmente identificables (probabilidad 0,60; 3 colores claramente distintos, 3 tonos, colorido 112); formas visibles (probabilidad 0,78; bordes cromáticos en el 14 % del textil); textil completo (probabilidad 0,71; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 76.</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="AA143" s="4" t="n">
-        <v>34.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AB143" s="4" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
       </c>
       <c r="AD143" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,72; textil de 2040 px de lado); colores parcialmente identificables (probabilidad 0,50; 3 colores claramente distintos, 3 tonos, colorido 125); formas parcialmente visibles (probabilidad 0,46; bordes cromáticos en el 12 % del textil); textil incompleto (probabilidad 0,33; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 35.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,72; textil de 2040 px de lado); colores identificables (probabilidad 0,77; 3 colores claramente distintos, 3 tonos, colorido 125); formas visibles (probabilidad 0,76; bordes cromáticos en el 12 % del textil); completitud incierta (probabilidad 0,70; compacidad 0,95, lagunas 0,0 %); estructura no evidente. Puntaje 76.</t>
         </is>
       </c>
     </row>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="AA144" s="4" t="n">
-        <v>68.7</v>
+        <v>94.5</v>
       </c>
       <c r="AB144" s="4" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AD144" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 1,26; textil de 2611 px de lado); colores identificables (probabilidad 0,91; 1 color claramente distinto, 2 tonos, colorido 42); formas visibles (probabilidad 0,91; bordes cromáticos en el 10 % del textil); textil completo (probabilidad 0,93; compacidad 0,79, lagunas 0,0 %); estructura simétrica. Puntaje 69.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 1,26; textil de 2611 px de lado); colores identificables (probabilidad 0,95; 1 color claramente distinto, 2 tonos, colorido 42); formas visibles (probabilidad 0,93; bordes cromáticos en el 10 % del textil); textil completo (probabilidad 0,96; compacidad 0,79, lagunas 0,0 %); estructura simétrica. Puntaje 94.</t>
         </is>
       </c>
     </row>
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="AA145" s="4" t="n">
-        <v>40</v>
+        <v>80.5</v>
       </c>
       <c r="AB145" s="4" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
       </c>
       <c r="AD145" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,47; textil de 3988 px de lado); colores parcialmente identificables (probabilidad 0,66; 6 colores claramente distintos, 2 tonos, colorido 57); formas parcialmente visibles (probabilidad 0,47; bordes cromáticos en el 14 % del textil); textil incompleto (probabilidad 0,24; toma cerrada, el contorno de la pieza no se ve); estructura repetitiva. Puntaje 40.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,47; textil de 3988 px de lado); colores identificables (probabilidad 0,91; 6 colores claramente distintos, 2 tonos, colorido 57); formas visibles (probabilidad 0,87; bordes cromáticos en el 14 % del textil); textil completo (probabilidad 0,75; toma cerrada, el contorno de la pieza no se ve); estructura repetitiva. Puntaje 81.</t>
         </is>
       </c>
     </row>
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="AA146" s="4" t="n">
-        <v>54</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AB146" s="4" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="AD146" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,73; textil de 3181 px de lado); colores parcialmente identificables (probabilidad 0,66; 5 colores claramente distintos, 3 tonos, colorido 57); formas visibles (probabilidad 0,72; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,15; compacidad 0,87, lagunas 13,5 %); estructura no evidente. Puntaje 54.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,73; textil de 3181 px de lado); colores identificables (probabilidad 0,89; 5 colores claramente distintos, 3 tonos, colorido 57); formas visibles (probabilidad 0,93; bordes cromáticos en el 25 % del textil); completitud incierta (probabilidad 0,60; compacidad 0,87, lagunas 13,5 %); estructura no evidente. Puntaje 72.</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="AA147" s="4" t="n">
-        <v>52.9</v>
+        <v>72.7</v>
       </c>
       <c r="AB147" s="4" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="AD147" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 0,95; textil de 1994 px de lado); colores identificables (probabilidad 0,78; 3 colores claramente distintos, 2 tonos, colorido 90); formas parcialmente visibles (probabilidad 0,67; bordes cromáticos en el 14 % del textil); textil incompleto (probabilidad 0,39; compacidad 0,71, lagunas 4,3 %); estructura no evidente. Puntaje 53.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 0,95; textil de 1994 px de lado); colores identificables (probabilidad 0,89; 3 colores claramente distintos, 2 tonos, colorido 90); formas visibles (probabilidad 0,76; bordes cromáticos en el 14 % del textil); completitud incierta (probabilidad 0,66; compacidad 0,71, lagunas 4,3 %); estructura no evidente. Puntaje 73.</t>
         </is>
       </c>
     </row>
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="AA148" s="4" t="n">
-        <v>82.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="AB148" s="4" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="AD148" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,99; textil de 862 px de lado); colores identificables (probabilidad 1,00; 5 colores claramente distintos, 5 tonos, colorido 79); formas visibles (probabilidad 0,99; bordes cromáticos en el 32 % del textil); textil completo (probabilidad 0,83; compacidad 0,98, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 83.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,99; textil de 862 px de lado); colores identificables (probabilidad 1,00; 5 colores claramente distintos, 5 tonos, colorido 79); formas visibles (probabilidad 0,99; bordes cromáticos en el 32 % del textil); textil completo (probabilidad 0,91; compacidad 0,98, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 91.</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="AA149" s="4" t="n">
-        <v>83.3</v>
+        <v>96.5</v>
       </c>
       <c r="AB149" s="4" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="AD149" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 1,07; textil de 2214 px de lado); colores identificables (probabilidad 1,00; 4 colores claramente distintos, 2 tonos, colorido 102); formas visibles (probabilidad 0,97; bordes cromáticos en el 23 % del textil); textil completo (probabilidad 0,97; compacidad 0,60, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 83.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 1,07; textil de 2214 px de lado); colores identificables (probabilidad 1,00; 4 colores claramente distintos, 2 tonos, colorido 102); formas visibles (probabilidad 0,93; bordes cromáticos en el 23 % del textil); textil completo (probabilidad 0,98; compacidad 0,60, lagunas 0,0 %); estructura repetitiva y simétrica. Puntaje 96.</t>
         </is>
       </c>
     </row>
@@ -18339,7 +18339,7 @@
         </is>
       </c>
       <c r="AA150" s="4" t="n">
-        <v>81.8</v>
+        <v>86.3</v>
       </c>
       <c r="AB150" s="4" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="AD150" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 1,08; textil de 727 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 3 tonos, colorido 48); formas visibles (probabilidad 0,93; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,85; compacidad 0,75, lagunas 2,6 %); estructura simétrica. Puntaje 82.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 1,08; textil de 727 px de lado); colores identificables (probabilidad 0,96; 2 colores claramente distintos, 3 tonos, colorido 48); formas visibles (probabilidad 0,90; bordes cromáticos en el 26 % del textil); textil completo (probabilidad 0,84; compacidad 0,75, lagunas 2,6 %); estructura simétrica. Puntaje 86.</t>
         </is>
       </c>
     </row>
@@ -18457,7 +18457,7 @@
         </is>
       </c>
       <c r="AA151" s="4" t="n">
-        <v>29.8</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AB151" s="4" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="AD151" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,37; textil de 3940 px de lado); colores no identificables (probabilidad 0,39; 3 colores claramente distintos, 1 tono, colorido 27); formas no visibles (probabilidad 0,39; bordes cromáticos en el 8 % del textil); textil incompleto (probabilidad 0,27; toma cerrada, el contorno de la pieza no se ve); estructura repetitiva. Puntaje 30.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,37; textil de 3940 px de lado); colores identificables (probabilidad 0,71; 3 colores claramente distintos, 1 tono, colorido 27); formas visibles (probabilidad 0,74; bordes cromáticos en el 8 % del textil); completitud incierta (probabilidad 0,60; toma cerrada, el contorno de la pieza no se ve); estructura repetitiva. Puntaje 66.</t>
         </is>
       </c>
     </row>
@@ -18575,7 +18575,7 @@
         </is>
       </c>
       <c r="AA152" s="4" t="n">
-        <v>72.8</v>
+        <v>93.5</v>
       </c>
       <c r="AB152" s="4" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AD152" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 1,19; textil de 2944 px de lado); colores identificables (probabilidad 0,98; 5 colores claramente distintos, 4 tonos, colorido 76); formas visibles (probabilidad 0,95; bordes cromáticos en el 39 % del textil); completitud incierta (probabilidad 0,69; compacidad 0,89, lagunas 0,0 %); estructura simétrica. Puntaje 73.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía regular (nitidez 1,19; textil de 2944 px de lado); colores identificables (probabilidad 0,99; 5 colores claramente distintos, 4 tonos, colorido 76); formas visibles (probabilidad 0,98; bordes cromáticos en el 39 % del textil); textil completo (probabilidad 0,92; compacidad 0,89, lagunas 0,0 %); estructura simétrica. Puntaje 93.</t>
         </is>
       </c>
     </row>
@@ -18693,7 +18693,7 @@
         </is>
       </c>
       <c r="AA153" s="4" t="n">
-        <v>63.2</v>
+        <v>61.2</v>
       </c>
       <c r="AB153" s="4" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
       </c>
       <c r="AD153" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,39; textil de 910 px de lado); colores no identificables (probabilidad 0,77; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,69; bordes cromáticos en el 56 % del textil); completitud incierta (probabilidad 0,42; compacidad 0,37, lagunas 0,0 %); estructura repetitiva. Puntaje 63.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,39; textil de 910 px de lado); colores no identificables (probabilidad 0,64; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,64; bordes cromáticos en el 56 % del textil); completitud incierta (probabilidad 0,47; compacidad 0,37, lagunas 0,0 %); estructura repetitiva. Puntaje 61.</t>
         </is>
       </c>
     </row>
@@ -18811,21 +18811,21 @@
         </is>
       </c>
       <c r="AA154" s="4" t="n">
-        <v>63.9</v>
+        <v>46.9</v>
       </c>
       <c r="AB154" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC154" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD154" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,88; textil de 1054 px de lado); colores identificables (probabilidad 0,74; 4 colores claramente distintos, 3 tonos, colorido 52); formas visibles (probabilidad 0,75; bordes cromáticos en el 47 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,76, lagunas 18,4 %); estructura no evidente. Puntaje 64.</t>
+          <t>Fotografía deficiente (nitidez 0,88; textil de 1054 px de lado); colores identificables (probabilidad 0,79; 4 colores claramente distintos, 3 tonos, colorido 52); formas visibles (probabilidad 0,83; bordes cromáticos en el 47 % del textil); textil incompleto (probabilidad 0,22; compacidad 0,76, lagunas 18,4 %); estructura no evidente. Puntaje 47.</t>
         </is>
       </c>
     </row>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="AA155" s="4" t="n">
-        <v>60.6</v>
+        <v>48.2</v>
       </c>
       <c r="AB155" s="4" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AD155" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,81; textil de 667 px de lado); colores no identificables (probabilidad 0,72; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,57; bordes cromáticos en el 66 % del textil); textil incompleto (probabilidad 0,31; compacidad 0,19, lagunas 0,0 %); estructura repetitiva. Puntaje 61.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,81; textil de 667 px de lado); colores no identificables (probabilidad 0,52; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,45; bordes cromáticos en el 66 % del textil); textil incompleto (probabilidad 0,33; compacidad 0,19, lagunas 0,0 %); estructura repetitiva. Puntaje 48.</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
         </is>
       </c>
       <c r="AA156" s="4" t="n">
-        <v>57.4</v>
+        <v>39.4</v>
       </c>
       <c r="AB156" s="4" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="AD156" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,22; textil de 577 px de lado); colores no identificables (probabilidad 0,66; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,55; bordes cromáticos en el 68 % del textil); textil incompleto (probabilidad 0,28; compacidad 0,21, lagunas 0,0 %); estructura repetitiva. Puntaje 57.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,22; textil de 577 px de lado); colores no identificables (probabilidad 0,45; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,43; bordes cromáticos en el 68 % del textil); textil incompleto (probabilidad 0,23; compacidad 0,21, lagunas 0,0 %); estructura repetitiva. Puntaje 39.</t>
         </is>
       </c>
     </row>
@@ -19165,7 +19165,7 @@
         </is>
       </c>
       <c r="AA157" s="4" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
       <c r="AB157" s="4" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
       </c>
       <c r="AD157" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,68; textil de 1003 px de lado); colores no identificables (probabilidad 0,65; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,58; bordes cromáticos en el 56 % del textil); textil incompleto (probabilidad 0,39; compacidad 0,41, lagunas 0,3 %); estructura no evidente. Puntaje 59.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,68; textil de 1003 px de lado); colores no identificables (probabilidad 0,53; 3 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,57; bordes cromáticos en el 56 % del textil); completitud incierta (probabilidad 0,49; compacidad 0,41, lagunas 0,3 %); estructura no evidente. Puntaje 58.</t>
         </is>
       </c>
     </row>
@@ -19283,7 +19283,7 @@
         </is>
       </c>
       <c r="AA158" s="4" t="n">
-        <v>69.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="AB158" s="4" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="AD158" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,79; textil de 852 px de lado); colores identificables (probabilidad 0,92; 4 colores claramente distintos, 2 tonos, colorido 63); formas visibles (probabilidad 0,80; bordes cromáticos en el 40 % del textil); completitud incierta (probabilidad 0,47; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 70.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,79; textil de 852 px de lado); colores identificables (probabilidad 0,93; 4 colores claramente distintos, 2 tonos, colorido 63); formas visibles (probabilidad 0,84; bordes cromáticos en el 40 % del textil); completitud incierta (probabilidad 0,64; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 73.</t>
         </is>
       </c>
     </row>
@@ -19401,21 +19401,21 @@
         </is>
       </c>
       <c r="AA159" s="4" t="n">
-        <v>56.5</v>
+        <v>87.8</v>
       </c>
       <c r="AB159" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC159" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD159" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,75; textil de 3808 px de lado); colores identificables (probabilidad 0,77; 3 colores claramente distintos, 1 tono, colorido 44); formas visibles (probabilidad 0,70; bordes cromáticos en el 15 % del textil); textil completo (probabilidad 0,70; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 57.</t>
+          <t>Fotografía deficiente (nitidez 0,75; textil de 3808 px de lado); colores identificables (probabilidad 0,92; 3 colores claramente distintos, 1 tono, colorido 44); formas visibles (probabilidad 0,87; bordes cromáticos en el 15 % del textil); textil completo (probabilidad 0,88; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 88 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -19519,21 +19519,21 @@
         </is>
       </c>
       <c r="AA160" s="4" t="n">
-        <v>50.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AB160" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC160" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD160" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 0,97; textil de 3870 px de lado); colores parcialmente identificables (probabilidad 0,68; 3 colores claramente distintos, 2 tonos, colorido 34); formas parcialmente visibles (probabilidad 0,66; bordes cromáticos en el 18 % del textil); completitud incierta (probabilidad 0,48; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 50.</t>
+          <t>Fotografía regular (nitidez 0,97; textil de 3870 px de lado); colores identificables (probabilidad 0,88; 3 colores claramente distintos, 2 tonos, colorido 34); formas visibles (probabilidad 0,89; bordes cromáticos en el 18 % del textil); textil completo (probabilidad 0,77; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 83.</t>
         </is>
       </c>
     </row>
@@ -19637,7 +19637,7 @@
         </is>
       </c>
       <c r="AA161" s="4" t="n">
-        <v>61.1</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="AB161" s="4" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
       </c>
       <c r="AD161" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,75; textil de 3541 px de lado); colores identificables (probabilidad 0,86; 5 colores claramente distintos, 3 tonos, colorido 52); formas visibles (probabilidad 0,75; bordes cromáticos en el 18 % del textil); completitud incierta (probabilidad 0,50; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 61.</t>
+          <t>Fotografía deficiente (nitidez 0,75; textil de 3541 px de lado); colores identificables (probabilidad 0,96; 5 colores claramente distintos, 3 tonos, colorido 52); formas visibles (probabilidad 0,93; bordes cromáticos en el 18 % del textil); textil completo (probabilidad 0,86; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 89 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -19755,21 +19755,21 @@
         </is>
       </c>
       <c r="AA162" s="4" t="n">
-        <v>50.7</v>
+        <v>78.3</v>
       </c>
       <c r="AB162" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC162" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD162" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,61; textil de 3357 px de lado); colores identificables (probabilidad 0,76; 5 colores claramente distintos, 3 tonos, colorido 52); formas parcialmente visibles (probabilidad 0,63; bordes cromáticos en el 18 % del textil); textil incompleto (probabilidad 0,28; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 51.</t>
+          <t>Fotografía deficiente (nitidez 0,61; textil de 3357 px de lado); colores identificables (probabilidad 0,93; 5 colores claramente distintos, 3 tonos, colorido 52); formas visibles (probabilidad 0,88; bordes cromáticos en el 18 % del textil); textil completo (probabilidad 0,72; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 78.</t>
         </is>
       </c>
     </row>
@@ -19873,7 +19873,7 @@
         </is>
       </c>
       <c r="AA163" s="4" t="n">
-        <v>66.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AB163" s="4" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
       </c>
       <c r="AD163" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,69; textil de 3810 px de lado); colores identificables (probabilidad 0,89; 5 colores claramente distintos, 4 tonos, colorido 51); formas visibles (probabilidad 0,82; bordes cromáticos en el 19 % del textil); completitud incierta (probabilidad 0,52; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 67.</t>
+          <t>Fotografía deficiente (nitidez 0,69; textil de 3810 px de lado); colores identificables (probabilidad 0,98; 5 colores claramente distintos, 4 tonos, colorido 51); formas visibles (probabilidad 0,97; bordes cromáticos en el 19 % del textil); textil completo (probabilidad 0,87; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 90 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -19991,21 +19991,21 @@
         </is>
       </c>
       <c r="AA164" s="4" t="n">
-        <v>56.9</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AB164" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC164" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD164" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,67; textil de 3511 px de lado); colores identificables (probabilidad 0,81; 5 colores claramente distintos, 2 tonos, colorido 45); formas parcialmente visibles (probabilidad 0,69; bordes cromáticos en el 18 % del textil); completitud incierta (probabilidad 0,50; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 57.</t>
+          <t>Fotografía deficiente (nitidez 0,67; textil de 3511 px de lado); colores identificables (probabilidad 0,94; 5 colores claramente distintos, 2 tonos, colorido 45); formas visibles (probabilidad 0,91; bordes cromáticos en el 18 % del textil); textil completo (probabilidad 0,85; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 87 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
         </is>
       </c>
       <c r="AA165" s="4" t="n">
-        <v>64.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="AB165" s="4" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
       </c>
       <c r="AD165" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,66; textil de 3636 px de lado); colores identificables (probabilidad 0,87; 4 colores claramente distintos, 4 tonos, colorido 53); formas visibles (probabilidad 0,81; bordes cromáticos en el 20 % del textil); completitud incierta (probabilidad 0,50; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 65.</t>
+          <t>Fotografía deficiente (nitidez 0,66; textil de 3636 px de lado); colores identificables (probabilidad 0,97; 4 colores claramente distintos, 4 tonos, colorido 53); formas visibles (probabilidad 0,95; bordes cromáticos en el 20 % del textil); textil completo (probabilidad 0,83; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 87 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -20227,21 +20227,21 @@
         </is>
       </c>
       <c r="AA166" s="4" t="n">
-        <v>58.9</v>
+        <v>89.2</v>
       </c>
       <c r="AB166" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC166" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD166" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,79; textil de 3611 px de lado); colores identificables (probabilidad 0,82; 5 colores claramente distintos, 2 tonos, colorido 44); formas visibles (probabilidad 0,70; bordes cromáticos en el 19 % del textil); completitud incierta (probabilidad 0,56; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 59.</t>
+          <t>Fotografía deficiente (nitidez 0,79; textil de 3611 px de lado); colores identificables (probabilidad 0,94; 5 colores claramente distintos, 2 tonos, colorido 44); formas visibles (probabilidad 0,91; bordes cromáticos en el 19 % del textil); textil completo (probabilidad 0,88; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 89 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -20345,7 +20345,7 @@
         </is>
       </c>
       <c r="AA167" s="4" t="n">
-        <v>62.1</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="AB167" s="4" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
       </c>
       <c r="AD167" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,72; textil de 3692 px de lado); colores identificables (probabilidad 0,85; 5 colores claramente distintos, 4 tonos, colorido 52); formas visibles (probabilidad 0,77; bordes cromáticos en el 19 % del textil); completitud incierta (probabilidad 0,44; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 62.</t>
+          <t>Fotografía deficiente (nitidez 0,72; textil de 3692 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 4 tonos, colorido 52); formas visibles (probabilidad 0,95; bordes cromáticos en el 19 % del textil); textil completo (probabilidad 0,84; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 88 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="AA168" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="AB168" s="4" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="AD168" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,68; textil de 3492 px de lado); colores identificables (probabilidad 0,90; 6 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,79; bordes cromáticos en el 20 % del textil); completitud incierta (probabilidad 0,54; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 67.</t>
+          <t>Fotografía deficiente (nitidez 0,68; textil de 3492 px de lado); colores identificables (probabilidad 0,97; 6 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,96; bordes cromáticos en el 20 % del textil); textil completo (probabilidad 0,90; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 91 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="AA169" s="4" t="n">
-        <v>63.5</v>
+        <v>90</v>
       </c>
       <c r="AB169" s="4" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="AD169" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,78; textil de 3542 px de lado); colores identificables (probabilidad 0,87; 5 colores claramente distintos, 3 tonos, colorido 56); formas visibles (probabilidad 0,77; bordes cromáticos en el 22 % del textil); completitud incierta (probabilidad 0,55; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 63.</t>
+          <t>Fotografía deficiente (nitidez 0,78; textil de 3542 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 3 tonos, colorido 56); formas visibles (probabilidad 0,94; bordes cromáticos en el 22 % del textil); textil completo (probabilidad 0,88; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 90 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -20699,21 +20699,21 @@
         </is>
       </c>
       <c r="AA170" s="4" t="n">
-        <v>50.1</v>
+        <v>86</v>
       </c>
       <c r="AB170" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC170" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD170" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,64; textil de 3344 px de lado); colores identificables (probabilidad 0,71; 5 colores claramente distintos, 2 tonos, colorido 52); formas parcialmente visibles (probabilidad 0,59; bordes cromáticos en el 17 % del textil); completitud incierta (probabilidad 0,46; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 50.</t>
+          <t>Fotografía deficiente (nitidez 0,64; textil de 3344 px de lado); colores identificables (probabilidad 0,92; 5 colores claramente distintos, 2 tonos, colorido 52); formas visibles (probabilidad 0,88; bordes cromáticos en el 17 % del textil); textil completo (probabilidad 0,85; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 86 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -20817,21 +20817,21 @@
         </is>
       </c>
       <c r="AA171" s="4" t="n">
-        <v>55.4</v>
+        <v>88.7</v>
       </c>
       <c r="AB171" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC171" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD171" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,77; textil de 3549 px de lado); colores identificables (probabilidad 0,80; 5 colores claramente distintos, 2 tonos, colorido 62); formas parcialmente visibles (probabilidad 0,65; bordes cromáticos en el 19 % del textil); completitud incierta (probabilidad 0,55; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 55.</t>
+          <t>Fotografía deficiente (nitidez 0,77; textil de 3549 px de lado); colores identificables (probabilidad 0,94; 5 colores claramente distintos, 2 tonos, colorido 62); formas visibles (probabilidad 0,89; bordes cromáticos en el 19 % del textil); textil completo (probabilidad 0,88; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 89 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
         </is>
       </c>
       <c r="AA172" s="4" t="n">
-        <v>64.2</v>
+        <v>91.3</v>
       </c>
       <c r="AB172" s="4" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="AD172" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,78; textil de 3524 px de lado); colores identificables (probabilidad 0,89; 6 colores claramente distintos, 3 tonos, colorido 59); formas visibles (probabilidad 0,77; bordes cromáticos en el 23 % del textil); completitud incierta (probabilidad 0,53; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 64.</t>
+          <t>Fotografía deficiente (nitidez 0,78; textil de 3524 px de lado); colores identificables (probabilidad 0,97; 6 colores claramente distintos, 3 tonos, colorido 59); formas visibles (probabilidad 0,95; bordes cromáticos en el 23 % del textil); textil completo (probabilidad 0,90; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 91 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="AA173" s="4" t="n">
-        <v>62.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AB173" s="4" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
       </c>
       <c r="AD173" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,68; textil de 3542 px de lado); colores identificables (probabilidad 0,86; 5 colores claramente distintos, 3 tonos, colorido 52); formas visibles (probabilidad 0,76; bordes cromáticos en el 18 % del textil); completitud incierta (probabilidad 0,52; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 63.</t>
+          <t>Fotografía deficiente (nitidez 0,68; textil de 3542 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 3 tonos, colorido 52); formas visibles (probabilidad 0,94; bordes cromáticos en el 18 % del textil); textil completo (probabilidad 0,87; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 89 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -21171,21 +21171,21 @@
         </is>
       </c>
       <c r="AA174" s="4" t="n">
-        <v>52.6</v>
+        <v>85.5</v>
       </c>
       <c r="AB174" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC174" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD174" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,69; textil de 3681 px de lado); colores identificables (probabilidad 0,78; 6 colores claramente distintos, 3 tonos, colorido 62); formas parcialmente visibles (probabilidad 0,63; bordes cromáticos en el 19 % del textil); textil incompleto (probabilidad 0,35; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 53.</t>
+          <t>Fotografía deficiente (nitidez 0,69; textil de 3681 px de lado); colores identificables (probabilidad 0,94; 6 colores claramente distintos, 3 tonos, colorido 62); formas visibles (probabilidad 0,91; bordes cromáticos en el 19 % del textil); textil completo (probabilidad 0,81; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 85 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -21289,7 +21289,7 @@
         </is>
       </c>
       <c r="AA175" s="4" t="n">
-        <v>62.6</v>
+        <v>90.2</v>
       </c>
       <c r="AB175" s="4" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="AD175" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 0,90; textil de 3610 px de lado); colores identificables (probabilidad 0,86; 5 colores claramente distintos, 3 tonos, colorido 51); formas visibles (probabilidad 0,77; bordes cromáticos en el 21 % del textil); completitud incierta (probabilidad 0,55; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 63.</t>
+          <t>Fotografía regular (nitidez 0,90; textil de 3610 px de lado); colores identificables (probabilidad 0,96; 5 colores claramente distintos, 3 tonos, colorido 51); formas visibles (probabilidad 0,94; bordes cromáticos en el 21 % del textil); textil completo (probabilidad 0,88; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 90 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -21407,21 +21407,21 @@
         </is>
       </c>
       <c r="AA176" s="4" t="n">
-        <v>56.8</v>
+        <v>83.8</v>
       </c>
       <c r="AB176" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC176" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD176" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,73; textil de 3542 px de lado); colores identificables (probabilidad 0,77; 3 colores claramente distintos, 3 tonos, colorido 50); formas visibles (probabilidad 0,73; bordes cromáticos en el 16 % del textil); completitud incierta (probabilidad 0,51; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 57.</t>
+          <t>Fotografía deficiente (nitidez 0,73; textil de 3542 px de lado); colores identificables (probabilidad 0,94; 3 colores claramente distintos, 3 tonos, colorido 50); formas visibles (probabilidad 0,91; bordes cromáticos en el 16 % del textil); textil completo (probabilidad 0,79; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 84.</t>
         </is>
       </c>
     </row>
@@ -21525,7 +21525,7 @@
         </is>
       </c>
       <c r="AA177" s="4" t="n">
-        <v>62.2</v>
+        <v>86.2</v>
       </c>
       <c r="AB177" s="4" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
       </c>
       <c r="AD177" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,59; textil de 3530 px de lado); colores identificables (probabilidad 0,87; 6 colores claramente distintos, 3 tonos, colorido 40); formas visibles (probabilidad 0,76; bordes cromáticos en el 17 % del textil); textil incompleto (probabilidad 0,39; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 62.</t>
+          <t>Fotografía deficiente (nitidez 0,59; textil de 3530 px de lado); colores identificables (probabilidad 0,97; 6 colores claramente distintos, 3 tonos, colorido 40); formas visibles (probabilidad 0,95; bordes cromáticos en el 17 % del textil); textil completo (probabilidad 0,82; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 86 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -21643,21 +21643,21 @@
         </is>
       </c>
       <c r="AA178" s="4" t="n">
-        <v>56.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AB178" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC178" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD178" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,78; textil de 2652 px de lado); colores identificables (probabilidad 0,81; 5 colores claramente distintos, 3 tonos, colorido 53); formas parcialmente visibles (probabilidad 0,64; bordes cromáticos en el 29 % del textil); textil incompleto (probabilidad 0,32; compacidad 0,62, lagunas 0,2 %); estructura simétrica. Puntaje 56.</t>
+          <t>Fotografía deficiente (nitidez 0,78; textil de 2652 px de lado); colores identificables (probabilidad 0,92; 5 colores claramente distintos, 3 tonos, colorido 53); formas visibles (probabilidad 0,87; bordes cromáticos en el 29 % del textil); textil completo (probabilidad 0,74; compacidad 0,62, lagunas 0,2 %); estructura simétrica. Puntaje 81.</t>
         </is>
       </c>
     </row>
@@ -21761,7 +21761,7 @@
         </is>
       </c>
       <c r="AA179" s="4" t="n">
-        <v>67.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="AB179" s="4" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
       </c>
       <c r="AD179" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,72; textil de 3575 px de lado); colores identificables (probabilidad 0,90; 6 colores claramente distintos, 4 tonos, colorido 61); formas visibles (probabilidad 0,81; bordes cromáticos en el 22 % del textil); completitud incierta (probabilidad 0,53; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 68.</t>
+          <t>Fotografía deficiente (nitidez 0,72; textil de 3575 px de lado); colores identificables (probabilidad 0,98; 6 colores claramente distintos, 4 tonos, colorido 61); formas visibles (probabilidad 0,97; bordes cromáticos en el 22 % del textil); textil completo (probabilidad 0,91; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 92 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -21879,21 +21879,21 @@
         </is>
       </c>
       <c r="AA180" s="4" t="n">
-        <v>55.1</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="AB180" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC180" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD180" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,65; textil de 3765 px de lado); colores identificables (probabilidad 0,78; 4 colores claramente distintos, 3 tonos, colorido 55); formas parcialmente visibles (probabilidad 0,69; bordes cromáticos en el 17 % del textil); completitud incierta (probabilidad 0,46; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 55.</t>
+          <t>Fotografía deficiente (nitidez 0,65; textil de 3765 px de lado); colores identificables (probabilidad 0,94; 4 colores claramente distintos, 3 tonos, colorido 55); formas visibles (probabilidad 0,90; bordes cromáticos en el 17 % del textil); textil completo (probabilidad 0,80; toma cerrada, el contorno de la pieza no se ve); estructura no evidente. Puntaje 84.</t>
         </is>
       </c>
     </row>
@@ -21997,21 +21997,21 @@
         </is>
       </c>
       <c r="AA181" s="4" t="n">
-        <v>55.3</v>
+        <v>84.8</v>
       </c>
       <c r="AB181" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC181" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD181" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,33; textil de 3115 px de lado); colores identificables (probabilidad 0,83; 5 colores claramente distintos, 2 tonos, colorido 41); formas visibles (probabilidad 0,73; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,34; compacidad 0,73, lagunas 0,3 %); estructura no evidente. Puntaje 55.</t>
+          <t>Fotografía regular (nitidez 1,33; textil de 3115 px de lado); colores identificables (probabilidad 0,92; 5 colores claramente distintos, 2 tonos, colorido 41); formas visibles (probabilidad 0,90; bordes cromáticos en el 25 % del textil); textil completo (probabilidad 0,78; compacidad 0,73, lagunas 0,3 %); estructura no evidente. Puntaje 85 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -22115,7 +22115,7 @@
         </is>
       </c>
       <c r="AA182" s="4" t="n">
-        <v>63.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AB182" s="4" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
       </c>
       <c r="AD182" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,60; textil de 3935 px de lado); colores identificables (probabilidad 0,86; 5 colores claramente distintos, 3 tonos, colorido 37); formas visibles (probabilidad 0,78; bordes cromáticos en el 13 % del textil); completitud incierta (probabilidad 0,47; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 63.</t>
+          <t>Fotografía deficiente (nitidez 0,60; textil de 3935 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 3 tonos, colorido 37); formas visibles (probabilidad 0,95; bordes cromáticos en el 13 % del textil); textil completo (probabilidad 0,85; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 87 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -22233,21 +22233,21 @@
         </is>
       </c>
       <c r="AA183" s="4" t="n">
-        <v>59.4</v>
+        <v>84.8</v>
       </c>
       <c r="AB183" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="AC183" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD183" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,28; textil de 2368 px de lado); colores identificables (probabilidad 0,87; 5 colores claramente distintos, 2 tonos, colorido 52); formas visibles (probabilidad 0,70; bordes cromáticos en el 43 % del textil); completitud incierta (probabilidad 0,42; compacidad 0,64, lagunas 0,8 %); estructura repetitiva. Puntaje 59.</t>
+          <t>Fotografía regular (nitidez 1,28; textil de 2368 px de lado); colores identificables (probabilidad 0,94; 5 colores claramente distintos, 2 tonos, colorido 52); formas visibles (probabilidad 0,87; bordes cromáticos en el 43 % del textil); textil completo (probabilidad 0,81; compacidad 0,64, lagunas 0,8 %); estructura repetitiva. Puntaje 85 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -22331,7 +22331,7 @@
         </is>
       </c>
       <c r="AA184" s="4" t="n">
-        <v>57.2</v>
+        <v>67.7</v>
       </c>
       <c r="AB184" s="4" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
       </c>
       <c r="AD184" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,60; textil de 1618 px de lado); colores identificables (probabilidad 0,75; 1 color claramente distinto, 2 tonos, colorido 42); formas visibles (probabilidad 0,74; bordes cromáticos en el 30 % del textil); completitud incierta (probabilidad 0,56; compacidad 0,70, lagunas 0,0 %); estructura repetitiva. Puntaje 57.</t>
+          <t>Fotografía buena (nitidez 1,60; textil de 1618 px de lado); colores identificables (probabilidad 0,73; 1 color claramente distinto, 2 tonos, colorido 42); formas visibles (probabilidad 0,74; bordes cromáticos en el 30 % del textil); completitud incierta (probabilidad 0,52; compacidad 0,70, lagunas 0,0 %); estructura repetitiva. Puntaje 68.</t>
         </is>
       </c>
     </row>
@@ -22429,7 +22429,7 @@
         </is>
       </c>
       <c r="AA185" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB185" s="4" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
       </c>
       <c r="AD185" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -22527,7 +22527,7 @@
         </is>
       </c>
       <c r="AA186" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB186" s="4" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
       </c>
       <c r="AD186" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22625,7 @@
         </is>
       </c>
       <c r="AA187" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB187" s="4" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
       </c>
       <c r="AD187" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -22723,7 +22723,7 @@
         </is>
       </c>
       <c r="AA188" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB188" s="4" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AD188" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
         </is>
       </c>
       <c r="AA189" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB189" s="4" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
       </c>
       <c r="AD189" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -22919,7 +22919,7 @@
         </is>
       </c>
       <c r="AA190" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB190" s="4" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
       </c>
       <c r="AD190" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="AA191" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB191" s="4" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="AD191" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -23115,7 +23115,7 @@
         </is>
       </c>
       <c r="AA192" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB192" s="4" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="AD192" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -23213,7 +23213,7 @@
         </is>
       </c>
       <c r="AA193" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB193" s="4" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
       </c>
       <c r="AD193" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -23311,7 +23311,7 @@
         </is>
       </c>
       <c r="AA194" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB194" s="4" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="AD194" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -23409,7 +23409,7 @@
         </is>
       </c>
       <c r="AA195" s="4" t="n">
-        <v>27.9</v>
+        <v>36.4</v>
       </c>
       <c r="AB195" s="4" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
       </c>
       <c r="AD195" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 0 tonos, colorido 0); formas no visibles (probabilidad 0,40; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 28.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía deficiente (nitidez 0,93; textil de 1875 px de lado); colores no identificables (probabilidad 0,42; 2 colores claramente distintos, 0 tonos, colorido 0); formas parcialmente visibles (probabilidad 0,49; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,67, lagunas 2,5 %); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -23523,21 +23523,21 @@
         </is>
       </c>
       <c r="AA196" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="AB196" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC196" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD196" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,07; textil de 1159 px de lado); colores identificables (probabilidad 0,94; 1 color claramente distinto, 1 tono, colorido 11); formas visibles (probabilidad 0,95; bordes cromáticos en el 3 % del textil); textil completo (probabilidad 0,83; compacidad 0,91, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 67.</t>
+          <t>Fotografía buena (nitidez 2,07; textil de 1159 px de lado); colores parcialmente identificables (probabilidad 0,48; 1 color claramente distinto, 1 tono, colorido 11); formas visibles (probabilidad 0,83; bordes cromáticos en el 3 % del textil); completitud incierta (probabilidad 0,43; compacidad 0,91, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 65.</t>
         </is>
       </c>
     </row>
@@ -23637,7 +23637,7 @@
         </is>
       </c>
       <c r="AA197" s="4" t="n">
-        <v>81.7</v>
+        <v>95.5</v>
       </c>
       <c r="AB197" s="4" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
       </c>
       <c r="AD197" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,93; textil de 559 px de lado); colores identificables (probabilidad 1,00; 2 colores claramente distintos, 2 tonos, colorido 107); formas visibles (probabilidad 0,99; bordes cromáticos en el 12 % del textil); textil completo (probabilidad 0,97; compacidad 0,99, lagunas 0,0 %); estructura simétrica. Puntaje 82 (imagen de referencia sugerida).</t>
+          <t>Fotografía deficiente (nitidez 0,93; textil de 559 px de lado); colores identificables (probabilidad 1,00; 2 colores claramente distintos, 2 tonos, colorido 107); formas visibles (probabilidad 0,93; bordes cromáticos en el 12 % del textil); textil completo (probabilidad 0,97; compacidad 0,99, lagunas 0,0 %); estructura simétrica. Puntaje 96 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -23751,21 +23751,21 @@
         </is>
       </c>
       <c r="AA198" s="4" t="n">
-        <v>65.2</v>
+        <v>41</v>
       </c>
       <c r="AB198" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC198" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD198" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,00; textil de 716 px de lado); colores identificables (probabilidad 0,86; 2 colores claramente distintos, 3 tonos, colorido 35); formas visibles (probabilidad 0,82; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,16; compacidad 0,58, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 65.</t>
+          <t>Fotografía deficiente (nitidez 1,00; textil de 716 px de lado); colores identificables (probabilidad 0,90; 2 colores claramente distintos, 3 tonos, colorido 35); formas visibles (probabilidad 0,83; bordes cromáticos en el 33 % del textil); textil incompleto (probabilidad 0,09; compacidad 0,58, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 41.</t>
         </is>
       </c>
     </row>
@@ -23865,7 +23865,7 @@
         </is>
       </c>
       <c r="AA199" s="4" t="n">
-        <v>74.2</v>
+        <v>84.8</v>
       </c>
       <c r="AB199" s="4" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="AD199" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,67; textil de 1689 px de lado); colores identificables (probabilidad 0,97; 7 colores claramente distintos, 3 tonos, colorido 83); formas visibles (probabilidad 0,87; bordes cromáticos en el 61 % del textil); completitud incierta (probabilidad 0,46; compacidad 0,79, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 74.</t>
+          <t>Fotografía buena (nitidez 1,67; textil de 1689 px de lado); colores identificables (probabilidad 0,98; 7 colores claramente distintos, 3 tonos, colorido 83); formas visibles (probabilidad 0,95; bordes cromáticos en el 61 % del textil); textil completo (probabilidad 0,74; compacidad 0,79, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 85 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -23979,7 +23979,7 @@
         </is>
       </c>
       <c r="AA200" s="4" t="n">
-        <v>77.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="AB200" s="4" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="AD200" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,06; textil de 376 px de lado); colores identificables (probabilidad 0,97; 2 colores claramente distintos, 2 tonos, colorido 44); formas visibles (probabilidad 0,96; bordes cromáticos en el 32 % del textil); textil completo (probabilidad 0,71; compacidad 0,91, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 78 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 2,06; textil de 376 px de lado); colores identificables (probabilidad 0,93; 2 colores claramente distintos, 2 tonos, colorido 44); formas visibles (probabilidad 0,88; bordes cromáticos en el 32 % del textil); completitud incierta (probabilidad 0,50; compacidad 0,91, lagunas 0,1 %, el título dice «fragment»); estructura no evidente. Puntaje 70.</t>
         </is>
       </c>
     </row>
@@ -24093,7 +24093,7 @@
         </is>
       </c>
       <c r="AA201" s="4" t="n">
-        <v>74.2</v>
+        <v>38.3</v>
       </c>
       <c r="AB201" s="4" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
       </c>
       <c r="AD201" s="4" t="inlineStr">
         <is>
-          <t>El textil mide 200 px de lado en la imagen institucional (mínimo 300). Fotografía deficiente (nitidez 1,30; textil de 200 px de lado); colores identificables (probabilidad 0,96; 3 colores claramente distintos, 3 tonos, colorido 31); formas visibles (probabilidad 0,90; bordes cromáticos en el 54 % del textil); textil incompleto (probabilidad 0,18; compacidad 0,85, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 74.</t>
+          <t>El textil mide 200 px de lado en la imagen institucional (mínimo 300). Fotografía deficiente (nitidez 1,30; textil de 200 px de lado); colores identificables (probabilidad 0,88; 3 colores claramente distintos, 3 tonos, colorido 31); formas visibles (probabilidad 0,77; bordes cromáticos en el 54 % del textil); textil incompleto (probabilidad 0,07; compacidad 0,85, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 38.</t>
         </is>
       </c>
     </row>
@@ -24207,7 +24207,7 @@
         </is>
       </c>
       <c r="AA202" s="4" t="n">
-        <v>52</v>
+        <v>52.6</v>
       </c>
       <c r="AB202" s="4" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
       </c>
       <c r="AD202" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 0,70; textil de 1499 px de lado); colores parcialmente identificables (probabilidad 0,62; 3 colores claramente distintos, 3 tonos, colorido 38); formas parcialmente visibles (probabilidad 0,68; bordes cromáticos en el 31 % del textil); textil incompleto (probabilidad 0,15; compacidad 0,73, lagunas 3,5 %, el título dice «fragment»); estructura no evidente. Puntaje 52.</t>
+          <t>Fotografía deficiente (nitidez 0,70; textil de 1499 px de lado); colores identificables (probabilidad 0,78; 3 colores claramente distintos, 3 tonos, colorido 38); formas visibles (probabilidad 0,85; bordes cromáticos en el 31 % del textil); textil incompleto (probabilidad 0,25; compacidad 0,73, lagunas 3,5 %, el título dice «fragment»); estructura no evidente. Puntaje 53.</t>
         </is>
       </c>
     </row>
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="AA203" s="4" t="n">
-        <v>64.8</v>
+        <v>86.2</v>
       </c>
       <c r="AB203" s="4" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
       </c>
       <c r="AD203" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,98; textil de 1629 px de lado); colores no identificables (probabilidad 0,89; 2 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,90; bordes cromáticos en el 39 % del textil); completitud incierta (probabilidad 0,67; compacidad 0,98, lagunas 0,0 %); estructura no evidente. Puntaje 65.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 1,98; textil de 1629 px de lado); colores no identificables (probabilidad 0,91; 2 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,93; bordes cromáticos en el 39 % del textil); textil completo (probabilidad 0,81; compacidad 0,98, lagunas 0,0 %); estructura no evidente. Puntaje 86.</t>
         </is>
       </c>
     </row>
@@ -24435,7 +24435,7 @@
         </is>
       </c>
       <c r="AA204" s="4" t="n">
-        <v>73.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AB204" s="4" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
       </c>
       <c r="AD204" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,70; textil de 2169 px de lado); colores no identificables (probabilidad 0,97; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,98; bordes cromáticos en el 43 % del textil); textil completo (probabilidad 0,91; compacidad 0,96, lagunas 0,0 %); estructura no evidente. Puntaje 74.</t>
+          <t>Fotografía en blanco y negro (croma 0,0): el color no es identificable. Fotografía buena (nitidez 2,70; textil de 2169 px de lado); colores no identificables (probabilidad 0,95; 3 colores claramente distintos, 0 tonos, colorido 0); formas visibles (probabilidad 0,98; bordes cromáticos en el 43 % del textil); textil completo (probabilidad 0,95; compacidad 0,96, lagunas 0,0 %); estructura no evidente. Puntaje 95.</t>
         </is>
       </c>
     </row>
@@ -24549,7 +24549,7 @@
         </is>
       </c>
       <c r="AA205" s="4" t="n">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="AB205" s="4" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AD205" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,30; textil de 715 px de lado); colores identificables (probabilidad 0,97; 3 colores claramente distintos, 2 tonos, colorido 38); formas visibles (probabilidad 0,95; bordes cromáticos en el 48 % del textil); textil completo (probabilidad 0,78; compacidad 0,79, lagunas 3,2 %); estructura no evidente. Puntaje 81 (imagen de referencia sugerida).</t>
+          <t>Fotografía buena (nitidez 2,30; textil de 715 px de lado); colores identificables (probabilidad 0,93; 3 colores claramente distintos, 2 tonos, colorido 38); formas visibles (probabilidad 0,92; bordes cromáticos en el 48 % del textil); textil completo (probabilidad 0,82; compacidad 0,79, lagunas 3,2 %); estructura no evidente. Puntaje 87 (imagen de referencia sugerida).</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
         </is>
       </c>
       <c r="AA206" s="4" t="n">
-        <v>67.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="AB206" s="4" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
       </c>
       <c r="AD206" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,19; textil de 1176 px de lado); colores identificables (probabilidad 0,85; 2 colores claramente distintos, 2 tonos, colorido 31); formas visibles (probabilidad 0,82; bordes cromáticos en el 38 % del textil); completitud incierta (probabilidad 0,51; compacidad 0,73, lagunas 0,4 %); estructura no evidente. Puntaje 68.</t>
+          <t>Fotografía regular (nitidez 1,19; textil de 1176 px de lado); colores identificables (probabilidad 0,82; 2 colores claramente distintos, 2 tonos, colorido 31); formas visibles (probabilidad 0,82; bordes cromáticos en el 38 % del textil); completitud incierta (probabilidad 0,55; compacidad 0,73, lagunas 0,4 %); estructura no evidente. Puntaje 70.</t>
         </is>
       </c>
     </row>
@@ -24777,7 +24777,7 @@
         </is>
       </c>
       <c r="AA207" s="4" t="n">
-        <v>46.7</v>
+        <v>44.9</v>
       </c>
       <c r="AB207" s="4" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
       </c>
       <c r="AD207" s="4" t="inlineStr">
         <is>
-          <t>Fotografía en blanco y negro (croma 2,6): el color no es identificable. Fotografía regular (nitidez 1,17; textil de 995 px de lado); colores no identificables (probabilidad 0,58; 3 colores claramente distintos, 0 tonos, colorido 3); formas parcialmente visibles (probabilidad 0,57; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,71, lagunas 3,0 %); estructura no evidente. Puntaje 47.</t>
+          <t>Fotografía en blanco y negro (croma 2,6): el color no es identificable. Fotografía regular (nitidez 1,17; textil de 995 px de lado); colores no identificables (probabilidad 0,45; 3 colores claramente distintos, 0 tonos, colorido 3); formas parcialmente visibles (probabilidad 0,54; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,29; compacidad 0,71, lagunas 3,0 %); estructura no evidente. Puntaje 45.</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
         </is>
       </c>
       <c r="AA208" s="4" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="AB208" s="4" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
       </c>
       <c r="AD208" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,83; textil de 1045 px de lado); colores identificables (probabilidad 0,72; 1 color claramente distinto, 2 tonos, colorido 35); formas parcialmente visibles (probabilidad 0,67; bordes cromáticos en el 24 % del textil); textil incompleto (probabilidad 0,39; compacidad 0,51, lagunas 0,0 %); estructura no evidente. Puntaje 53.</t>
+          <t>Fotografía buena (nitidez 1,83; textil de 1045 px de lado); colores parcialmente identificables (probabilidad 0,64; 1 color claramente distinto, 2 tonos, colorido 35); formas parcialmente visibles (probabilidad 0,53; bordes cromáticos en el 24 % del textil); textil incompleto (probabilidad 0,39; compacidad 0,51, lagunas 0,0 %); estructura no evidente. Puntaje 54.</t>
         </is>
       </c>
     </row>
@@ -25005,21 +25005,21 @@
         </is>
       </c>
       <c r="AA209" s="4" t="n">
-        <v>56.4</v>
+        <v>31.4</v>
       </c>
       <c r="AB209" s="4" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>descartar</t>
         </is>
       </c>
       <c r="AC209" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>puntaje</t>
         </is>
       </c>
       <c r="AD209" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,03; textil de 1621 px de lado); colores no identificables (probabilidad 0,14; 1 color claramente distinto, 2 tonos, colorido 22); formas parcialmente visibles (probabilidad 0,59; bordes cromáticos en el 17 % del textil); textil incompleto (probabilidad 0,05; compacidad 0,78, lagunas 58,1 %); estructura no evidente. Puntaje 56.</t>
+          <t>Fotografía regular (nitidez 1,03; textil de 1621 px de lado); colores no identificables (probabilidad 0,28; 1 color claramente distinto, 2 tonos, colorido 22); formas parcialmente visibles (probabilidad 0,69; bordes cromáticos en el 17 % del textil); textil incompleto (probabilidad 0,12; compacidad 0,78, lagunas 58,1 %); estructura no evidente. Puntaje 31.</t>
         </is>
       </c>
     </row>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="AA210" s="4" t="n">
-        <v>35.1</v>
+        <v>19.1</v>
       </c>
       <c r="AB210" s="4" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
       </c>
       <c r="AD210" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,89; textil de 711 px de lado); colores parcialmente identificables (probabilidad 0,54; 2 colores claramente distintos, 2 tonos, colorido 36); formas no visibles (probabilidad 0,39; bordes cromáticos en el 39 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,33, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 35.</t>
+          <t>Fotografía buena (nitidez 1,89; textil de 711 px de lado); colores no identificables (probabilidad 0,37; 2 colores claramente distintos, 2 tonos, colorido 36); formas no visibles (probabilidad 0,22; bordes cromáticos en el 39 % del textil); textil incompleto (probabilidad 0,06; compacidad 0,33, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 19.</t>
         </is>
       </c>
     </row>
@@ -25233,7 +25233,7 @@
         </is>
       </c>
       <c r="AA211" s="4" t="n">
-        <v>39.9</v>
+        <v>27.6</v>
       </c>
       <c r="AB211" s="4" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
       </c>
       <c r="AD211" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 1,93; textil de 805 px de lado); colores parcialmente identificables (probabilidad 0,56; 2 colores claramente distintos, 2 tonos, colorido 31); formas parcialmente visibles (probabilidad 0,45; bordes cromáticos en el 41 % del textil); textil incompleto (probabilidad 0,11; compacidad 0,37, lagunas 0,2 %, el título dice «fragment»); estructura no evidente. Puntaje 40.</t>
+          <t>Fotografía buena (nitidez 1,93; textil de 805 px de lado); colores parcialmente identificables (probabilidad 0,47; 2 colores claramente distintos, 2 tonos, colorido 31); formas no visibles (probabilidad 0,35; bordes cromáticos en el 41 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,37, lagunas 0,2 %, el título dice «fragment»); estructura no evidente. Puntaje 28.</t>
         </is>
       </c>
     </row>
@@ -25347,7 +25347,7 @@
         </is>
       </c>
       <c r="AA212" s="4" t="n">
-        <v>51.7</v>
+        <v>38</v>
       </c>
       <c r="AB212" s="4" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="AD212" s="4" t="inlineStr">
         <is>
-          <t>Fotografía buena (nitidez 2,47; textil de 710 px de lado); colores identificables (probabilidad 0,74; 3 colores claramente distintos, 2 tonos, colorido 30); formas parcialmente visibles (probabilidad 0,59; bordes cromáticos en el 43 % del textil); textil incompleto (probabilidad 0,18; compacidad 0,39, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 52.</t>
+          <t>Fotografía buena (nitidez 2,47; textil de 710 px de lado); colores parcialmente identificables (probabilidad 0,62; 3 colores claramente distintos, 2 tonos, colorido 30); formas parcialmente visibles (probabilidad 0,47; bordes cromáticos en el 43 % del textil); textil incompleto (probabilidad 0,14; compacidad 0,39, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 38.</t>
         </is>
       </c>
     </row>
@@ -25482,7 +25482,7 @@
         </is>
       </c>
       <c r="AA213" s="4" t="n">
-        <v>47</v>
+        <v>31.3</v>
       </c>
       <c r="AB213" s="4" t="inlineStr">
         <is>
@@ -25491,12 +25491,12 @@
       </c>
       <c r="AC213" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>posible_figurilla</t>
         </is>
       </c>
       <c r="AD213" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,12; textil de 716 px de lado); colores parcialmente identificables (probabilidad 0,62; 3 colores claramente distintos, 3 tonos, colorido 37); formas parcialmente visibles (probabilidad 0,51; bordes cromáticos en el 28 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,46, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 47.</t>
+          <t>El título sugiere una figurilla («Figure»): confirmar si es un textil o un objeto tridimensional. Fotografía regular (nitidez 1,12; textil de 716 px de lado); colores parcialmente identificables (probabilidad 0,62; 3 colores claramente distintos, 3 tonos, colorido 37); formas parcialmente visibles (probabilidad 0,51; bordes cromáticos en el 28 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,46, lagunas 0,0 %, el título dice «fragment»); estructura no evidente. Puntaje 31.</t>
         </is>
       </c>
     </row>
@@ -25617,21 +25617,21 @@
         </is>
       </c>
       <c r="AA214" s="4" t="n">
-        <v>41.4</v>
+        <v>24.8</v>
       </c>
       <c r="AB214" s="4" t="inlineStr">
         <is>
-          <t>descartar</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC214" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>posible_figurilla</t>
         </is>
       </c>
       <c r="AD214" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,06; textil de 696 px de lado); colores parcialmente identificables (probabilidad 0,46; 2 colores claramente distintos, 2 tonos, colorido 38); formas parcialmente visibles (probabilidad 0,45; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,54, lagunas 5,7 %, el título dice «fragment»); estructura no evidente. Puntaje 41.</t>
+          <t>El título sugiere una figurilla («Figure»): confirmar si es un textil o un objeto tridimensional. Fotografía deficiente (nitidez 1,06; textil de 696 px de lado); colores parcialmente identificables (probabilidad 0,45; 2 colores claramente distintos, 2 tonos, colorido 38); formas parcialmente visibles (probabilidad 0,41; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,06; compacidad 0,54, lagunas 5,7 %, el título dice «fragment»); estructura no evidente. Puntaje 25.</t>
         </is>
       </c>
     </row>
@@ -25752,21 +25752,21 @@
         </is>
       </c>
       <c r="AA215" s="4" t="n">
-        <v>38.7</v>
+        <v>26.4</v>
       </c>
       <c r="AB215" s="4" t="inlineStr">
         <is>
-          <t>descartar</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC215" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>posible_figurilla</t>
         </is>
       </c>
       <c r="AD215" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,02; textil de 700 px de lado); colores parcialmente identificables (probabilidad 0,51; 3 colores claramente distintos, 2 tonos, colorido 38); formas no visibles (probabilidad 0,39; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,46, lagunas 0,4 %, el título dice «fragment»); estructura no evidente. Puntaje 39.</t>
+          <t>El título sugiere una figurilla («Figure»): confirmar si es un textil o un objeto tridimensional. Fotografía deficiente (nitidez 1,02; textil de 700 px de lado); colores parcialmente identificables (probabilidad 0,48; 3 colores claramente distintos, 2 tonos, colorido 38); formas no visibles (probabilidad 0,37; bordes cromáticos en el 25 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,46, lagunas 0,4 %, el título dice «fragment»); estructura no evidente. Puntaje 26.</t>
         </is>
       </c>
     </row>
@@ -25887,21 +25887,21 @@
         </is>
       </c>
       <c r="AA216" s="4" t="n">
-        <v>36.2</v>
+        <v>26.8</v>
       </c>
       <c r="AB216" s="4" t="inlineStr">
         <is>
-          <t>descartar</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC216" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>posible_figurilla</t>
         </is>
       </c>
       <c r="AD216" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,05; textil de 724 px de lado); colores parcialmente identificables (probabilidad 0,47; 3 colores claramente distintos, 2 tonos, colorido 40); formas no visibles (probabilidad 0,38; bordes cromáticos en el 27 % del textil); textil incompleto (probabilidad 0,07; compacidad 0,49, lagunas 0,5 %, el título dice «fragment»); estructura no evidente. Puntaje 36.</t>
+          <t>El título sugiere una figurilla («Figure»): confirmar si es un textil o un objeto tridimensional. Fotografía deficiente (nitidez 1,05; textil de 724 px de lado); colores parcialmente identificables (probabilidad 0,47; 3 colores claramente distintos, 2 tonos, colorido 40); formas no visibles (probabilidad 0,40; bordes cromáticos en el 27 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,49, lagunas 0,5 %, el título dice «fragment»); estructura no evidente. Puntaje 27.</t>
         </is>
       </c>
     </row>
@@ -26022,7 +26022,7 @@
         </is>
       </c>
       <c r="AA217" s="4" t="n">
-        <v>48</v>
+        <v>30.8</v>
       </c>
       <c r="AB217" s="4" t="inlineStr">
         <is>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="AC217" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>posible_figurilla</t>
         </is>
       </c>
       <c r="AD217" s="4" t="inlineStr">
         <is>
-          <t>Fotografía deficiente (nitidez 1,05; textil de 713 px de lado); colores parcialmente identificables (probabilidad 0,59; 2 colores claramente distintos, 3 tonos, colorido 42); formas parcialmente visibles (probabilidad 0,52; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,10; compacidad 0,44, lagunas 1,4 %, el título dice «fragment»); estructura no evidente. Puntaje 48.</t>
+          <t>El título sugiere una figurilla («Figure»): confirmar si es un textil o un objeto tridimensional. Fotografía deficiente (nitidez 1,05; textil de 713 px de lado); colores parcialmente identificables (probabilidad 0,60; 2 colores claramente distintos, 3 tonos, colorido 42); formas parcialmente visibles (probabilidad 0,50; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,44, lagunas 1,4 %, el título dice «fragment»); estructura no evidente. Puntaje 31.</t>
         </is>
       </c>
     </row>
@@ -26157,7 +26157,7 @@
         </is>
       </c>
       <c r="AA218" s="4" t="n">
-        <v>50.9</v>
+        <v>35.9</v>
       </c>
       <c r="AB218" s="4" t="inlineStr">
         <is>
@@ -26166,12 +26166,12 @@
       </c>
       <c r="AC218" s="4" t="inlineStr">
         <is>
-          <t>zona_intermedia</t>
+          <t>posible_figurilla</t>
         </is>
       </c>
       <c r="AD218" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,14; textil de 706 px de lado); colores parcialmente identificables (probabilidad 0,70; 4 colores claramente distintos, 3 tonos, colorido 37); formas parcialmente visibles (probabilidad 0,55; bordes cromáticos en el 24 % del textil); textil incompleto (probabilidad 0,08; compacidad 0,50, lagunas 1,0 %, el título dice «fragment»); estructura no evidente. Puntaje 51.</t>
+          <t>El título sugiere una figurilla («Figure»): confirmar si es un textil o un objeto tridimensional. Fotografía regular (nitidez 1,14; textil de 706 px de lado); colores identificables (probabilidad 0,70; 4 colores claramente distintos, 3 tonos, colorido 37); formas parcialmente visibles (probabilidad 0,58; bordes cromáticos en el 24 % del textil); textil incompleto (probabilidad 0,10; compacidad 0,50, lagunas 1,0 %, el título dice «fragment»); estructura no evidente. Puntaje 36.</t>
         </is>
       </c>
     </row>
@@ -26287,7 +26287,7 @@
         </is>
       </c>
       <c r="AA219" s="4" t="n">
-        <v>44.3</v>
+        <v>83.7</v>
       </c>
       <c r="AB219" s="4" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
       </c>
       <c r="AD219" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,33; textil de 3328 px de lado); colores parcialmente identificables (probabilidad 0,62; 4 colores claramente distintos, 2 tonos, colorido 59); formas parcialmente visibles (probabilidad 0,51; bordes cromáticos en el 6 % del textil); completitud incierta (probabilidad 0,51; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 44.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,33; textil de 3328 px de lado); colores identificables (probabilidad 0,90; 4 colores claramente distintos, 2 tonos, colorido 59); formas visibles (probabilidad 0,83; bordes cromáticos en el 6 % del textil); textil completo (probabilidad 0,85; toma cerrada, el contorno de la pieza no se ve); estructura simétrica. Puntaje 84.</t>
         </is>
       </c>
     </row>
@@ -26422,7 +26422,7 @@
         </is>
       </c>
       <c r="AA220" s="4" t="n">
-        <v>68.3</v>
+        <v>54.4</v>
       </c>
       <c r="AB220" s="4" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
       </c>
       <c r="AD220" s="4" t="inlineStr">
         <is>
-          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,68; textil de 510 px de lado); colores identificables (probabilidad 0,97; 5 colores claramente distintos, 3 tonos, colorido 55); formas visibles (probabilidad 0,90; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,20; compacidad 0,90, lagunas 1,2 %); estructura no evidente. Puntaje 68.</t>
+          <t>Los metadatos registran plumas: los textiles con plumaria quedan fuera del estudio. Fotografía deficiente (nitidez 0,68; textil de 510 px de lado); colores identificables (probabilidad 0,93; 5 colores claramente distintos, 3 tonos, colorido 55); formas visibles (probabilidad 0,82; bordes cromáticos en el 30 % del textil); textil incompleto (probabilidad 0,32; compacidad 0,90, lagunas 1,2 %); estructura no evidente. Puntaje 54.</t>
         </is>
       </c>
     </row>
@@ -26557,21 +26557,21 @@
         </is>
       </c>
       <c r="AA221" s="4" t="n">
-        <v>70.3</v>
+        <v>60.9</v>
       </c>
       <c r="AB221" s="4" t="inlineStr">
         <is>
-          <t>principal</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="AC221" s="4" t="inlineStr">
         <is>
-          <t>puntaje</t>
+          <t>zona_intermedia</t>
         </is>
       </c>
       <c r="AD221" s="4" t="inlineStr">
         <is>
-          <t>Fotografía regular (nitidez 1,11; textil de 1717 px de lado); colores identificables (probabilidad 0,78; 4 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,79; bordes cromáticos en el 24 % del textil); textil incompleto (probabilidad 0,17; compacidad 0,57, lagunas 21,5 %); estructura no evidente. Puntaje 70.</t>
+          <t>Fotografía regular (nitidez 1,11; textil de 1717 px de lado); colores identificables (probabilidad 0,94; 4 colores claramente distintos, 3 tonos, colorido 46); formas visibles (probabilidad 0,92; bordes cromáticos en el 24 % del textil); completitud incierta (probabilidad 0,46; compacidad 0,57, lagunas 21,5 %); estructura no evidente. Puntaje 61.</t>
         </is>
       </c>
     </row>
